--- a/data/evaluation/evidence_quality_test.xlsx
+++ b/data/evaluation/evidence_quality_test.xlsx
@@ -8559,17 +8559,17 @@
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>RELOC_005</t>
+          <t>PLUS1_002</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>东方财富网 / 腾讯新闻</t>
+          <t>东方财富网（转界面新闻）</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="F156" s="2" t="inlineStr">
@@ -8594,7 +8594,7 @@
       </c>
       <c r="L156" s="2" t="inlineStr">
         <is>
-          <t>https://finance.eastmoney.com/a/202407163131488556.html</t>
+          <t>https://finance.eastmoney.com/a/202507023446498365.html</t>
         </is>
       </c>
     </row>
@@ -8819,17 +8819,17 @@
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>RELOC_005</t>
+          <t>PLUS1_002</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>东方财富网 / 腾讯新闻</t>
+          <t>东方财富网（转界面新闻）</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="F161" s="2" t="inlineStr">
@@ -8854,7 +8854,7 @@
       </c>
       <c r="L161" s="2" t="inlineStr">
         <is>
-          <t>https://finance.eastmoney.com/a/202407163131488556.html</t>
+          <t>https://finance.eastmoney.com/a/202507023446498365.html</t>
         </is>
       </c>
     </row>

--- a/data/evaluation/evidence_quality_test.xlsx
+++ b/data/evaluation/evidence_quality_test.xlsx
@@ -603,22 +603,22 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>RETURN_004</t>
+          <t>RETURN_001</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>36氪 / 财新网</t>
+          <t>恩捷股份公告（经东方财富网 / 央广网报道）</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G3" s="2" t="n">
@@ -638,7 +638,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixin.com/2024-10-28/102250409.html</t>
+          <t>https://finance.eastmoney.com/a/202605223746866215.html</t>
         </is>
       </c>
     </row>
@@ -655,22 +655,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>RETURN_001</t>
+          <t>RETURN_004</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>恩捷股份公告（经东方财富网 / 央广网报道）</t>
+          <t>36氪 / 财新网</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="G4" s="2" t="n">
@@ -690,7 +690,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>https://finance.eastmoney.com/a/202605223746866215.html</t>
+          <t>https://www.caixin.com/2024-10-28/102250409.html</t>
         </is>
       </c>
     </row>
@@ -863,22 +863,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>RETURN_004</t>
+          <t>RETURN_001</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>36氪 / 财新网</t>
+          <t>恩捷股份公告（经东方财富网 / 央广网报道）</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
@@ -898,7 +898,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixin.com/2024-10-28/102250409.html</t>
+          <t>https://finance.eastmoney.com/a/202605223746866215.html</t>
         </is>
       </c>
     </row>
@@ -915,22 +915,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>RETURN_001</t>
+          <t>RETURN_004</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>恩捷股份公告（经东方财富网 / 央广网报道）</t>
+          <t>36氪 / 财新网</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
@@ -950,7 +950,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>https://finance.eastmoney.com/a/202605223746866215.html</t>
+          <t>https://www.caixin.com/2024-10-28/102250409.html</t>
         </is>
       </c>
     </row>
@@ -2839,17 +2839,17 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>RELOC_006</t>
+          <t>RETURN_002</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>澎湃新闻</t>
+          <t>新浪科技 / 中关村在线</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>2024-02-28</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -2874,7 +2874,7 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>https://www.thepaper.cn/newsDetail_forward_26493905</t>
+          <t>https://finance.sina.com.cn/tech/roll/2025-07-03/doc-infeerfp4024842.shtml</t>
         </is>
       </c>
     </row>
@@ -3099,17 +3099,17 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>RELOC_006</t>
+          <t>RETURN_002</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>澎湃新闻</t>
+          <t>新浪科技 / 中关村在线</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>2024-02-28</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -3134,7 +3134,7 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>https://www.thepaper.cn/newsDetail_forward_26493905</t>
+          <t>https://finance.sina.com.cn/tech/roll/2025-07-03/doc-infeerfp4024842.shtml</t>
         </is>
       </c>
     </row>
@@ -5439,17 +5439,17 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>RELOC_008</t>
+          <t>RETURN_002</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>和讯网 / 网易</t>
+          <t>新浪科技 / 中关村在线</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>https://futures.hexun.com/2024-04-08/212465761.html</t>
+          <t>https://finance.sina.com.cn/tech/roll/2025-07-03/doc-infeerfp4024842.shtml</t>
         </is>
       </c>
     </row>
@@ -5699,17 +5699,17 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>RELOC_008</t>
+          <t>RETURN_002</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>和讯网 / 网易</t>
+          <t>新浪科技 / 中关村在线</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>https://futures.hexun.com/2024-04-08/212465761.html</t>
+          <t>https://finance.sina.com.cn/tech/roll/2025-07-03/doc-infeerfp4024842.shtml</t>
         </is>
       </c>
     </row>
@@ -5803,17 +5803,17 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>RETURN_004</t>
+          <t>PLUS1_003</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>36氪 / 财新网</t>
+          <t>凤凰科技（转路透社）</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
@@ -5838,7 +5838,7 @@
       </c>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixin.com/2024-10-28/102250409.html</t>
+          <t>https://otomotif.antaranews.com/berita/5724273/pabrik-byd-di-subang-resmi-beroperasi-dan-serap-5000-pekerja-lokal</t>
         </is>
       </c>
     </row>
@@ -5855,22 +5855,22 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>PLUS1_003</t>
+          <t>RELOC_001</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>凤凰科技（转路透社）</t>
+          <t>东方财富网（转比亚迪官方）</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>2025-01-22</t>
+          <t>2024-07-04</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G104" s="2" t="n">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>https://tech.ifeng.com/c/8gLk1Msnjan</t>
+          <t>https://finance.eastmoney.com/a/202407043122188760.html</t>
         </is>
       </c>
     </row>
@@ -5907,22 +5907,22 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>RELOC_001</t>
+          <t>RETURN_004</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>东方财富网（转比亚迪官方）</t>
+          <t>36氪 / 财新网</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>2024-07-04</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="G105" s="2" t="n">
@@ -5942,7 +5942,7 @@
       </c>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>https://finance.eastmoney.com/a/202407043122188760.html</t>
+          <t>https://www.caixin.com/2024-10-28/102250409.html</t>
         </is>
       </c>
     </row>
@@ -5959,17 +5959,17 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>RELOC_008</t>
+          <t>RETURN_002</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>和讯网 / 网易</t>
+          <t>新浪科技 / 中关村在线</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
@@ -5994,7 +5994,7 @@
       </c>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>https://futures.hexun.com/2024-04-08/212465761.html</t>
+          <t>https://finance.sina.com.cn/tech/roll/2025-07-03/doc-infeerfp4024842.shtml</t>
         </is>
       </c>
     </row>
@@ -6063,17 +6063,17 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>RETURN_004</t>
+          <t>PLUS1_003</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>36氪 / 财新网</t>
+          <t>凤凰科技（转路透社）</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
@@ -6098,7 +6098,7 @@
       </c>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixin.com/2024-10-28/102250409.html</t>
+          <t>https://otomotif.antaranews.com/berita/5724273/pabrik-byd-di-subang-resmi-beroperasi-dan-serap-5000-pekerja-lokal</t>
         </is>
       </c>
     </row>
@@ -6115,22 +6115,22 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>PLUS1_003</t>
+          <t>RELOC_001</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>凤凰科技（转路透社）</t>
+          <t>东方财富网（转比亚迪官方）</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>2025-01-22</t>
+          <t>2024-07-04</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G109" s="2" t="n">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="L109" s="2" t="inlineStr">
         <is>
-          <t>https://tech.ifeng.com/c/8gLk1Msnjan</t>
+          <t>https://finance.eastmoney.com/a/202407043122188760.html</t>
         </is>
       </c>
     </row>
@@ -6167,22 +6167,22 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>RELOC_001</t>
+          <t>RETURN_004</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>东方财富网（转比亚迪官方）</t>
+          <t>36氪 / 财新网</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>2024-07-04</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="G110" s="2" t="n">
@@ -6202,7 +6202,7 @@
       </c>
       <c r="L110" s="2" t="inlineStr">
         <is>
-          <t>https://finance.eastmoney.com/a/202407043122188760.html</t>
+          <t>https://www.caixin.com/2024-10-28/102250409.html</t>
         </is>
       </c>
     </row>
@@ -6219,17 +6219,17 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>RELOC_008</t>
+          <t>RETURN_002</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>和讯网 / 网易</t>
+          <t>新浪科技 / 中关村在线</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
@@ -6254,7 +6254,7 @@
       </c>
       <c r="L111" s="2" t="inlineStr">
         <is>
-          <t>https://futures.hexun.com/2024-04-08/212465761.html</t>
+          <t>https://finance.sina.com.cn/tech/roll/2025-07-03/doc-infeerfp4024842.shtml</t>
         </is>
       </c>
     </row>
@@ -6999,17 +6999,17 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>RELOC_003</t>
+          <t>RETURN_002</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>澎湃新闻 / 盖世汽车社区</t>
+          <t>新浪科技 / 中关村在线</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>2022-11-19</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
@@ -7034,7 +7034,7 @@
       </c>
       <c r="L126" s="2" t="inlineStr">
         <is>
-          <t>https://m.thepaper.cn/newsDetail_forward_20810032</t>
+          <t>https://finance.sina.com.cn/tech/roll/2025-07-03/doc-infeerfp4024842.shtml</t>
         </is>
       </c>
     </row>
@@ -7259,17 +7259,17 @@
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>RELOC_003</t>
+          <t>RETURN_002</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>澎湃新闻 / 盖世汽车社区</t>
+          <t>新浪科技 / 中关村在线</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>2022-11-19</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="L131" s="2" t="inlineStr">
         <is>
-          <t>https://m.thepaper.cn/newsDetail_forward_20810032</t>
+          <t>https://finance.sina.com.cn/tech/roll/2025-07-03/doc-infeerfp4024842.shtml</t>
         </is>
       </c>
     </row>
@@ -7415,17 +7415,17 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>RETURN_003</t>
+          <t>RETURN_002</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>路透社（经环球网 / 新浪转载）</t>
+          <t>新浪科技 / 中关村在线</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr">
@@ -7450,7 +7450,7 @@
       </c>
       <c r="L134" s="2" t="inlineStr">
         <is>
-          <t>https://3w.huanqiu.com/a/de583b/4TE5JD6omnj</t>
+          <t>https://finance.sina.com.cn/tech/roll/2025-07-03/doc-infeerfp4024842.shtml</t>
         </is>
       </c>
     </row>
@@ -7467,17 +7467,17 @@
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>RETURN_002</t>
+          <t>RETURN_003</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>新浪科技 / 中关村在线</t>
+          <t>路透社（经环球网 / 新浪转载）</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F135" s="2" t="inlineStr">
@@ -7502,7 +7502,7 @@
       </c>
       <c r="L135" s="2" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/tech/roll/2025-07-03/doc-infeerfp4024842.shtml</t>
+          <t>https://3w.huanqiu.com/a/de583b/4TE5JD6omnj</t>
         </is>
       </c>
     </row>
@@ -7675,17 +7675,17 @@
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>RETURN_003</t>
+          <t>RETURN_002</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>路透社（经环球网 / 新浪转载）</t>
+          <t>新浪科技 / 中关村在线</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="F139" s="2" t="inlineStr">
@@ -7710,7 +7710,7 @@
       </c>
       <c r="L139" s="2" t="inlineStr">
         <is>
-          <t>https://3w.huanqiu.com/a/de583b/4TE5JD6omnj</t>
+          <t>https://finance.sina.com.cn/tech/roll/2025-07-03/doc-infeerfp4024842.shtml</t>
         </is>
       </c>
     </row>
@@ -7727,17 +7727,17 @@
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>RETURN_002</t>
+          <t>RETURN_003</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>新浪科技 / 中关村在线</t>
+          <t>路透社（经环球网 / 新浪转载）</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr">
@@ -7762,7 +7762,7 @@
       </c>
       <c r="L140" s="2" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/tech/roll/2025-07-03/doc-infeerfp4024842.shtml</t>
+          <t>https://3w.huanqiu.com/a/de583b/4TE5JD6omnj</t>
         </is>
       </c>
     </row>
@@ -8975,17 +8975,17 @@
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>RETURN_003</t>
+          <t>RETURN_002</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>路透社（经环球网 / 新浪转载）</t>
+          <t>新浪科技 / 中关村在线</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="F164" s="2" t="inlineStr">
@@ -9010,7 +9010,7 @@
       </c>
       <c r="L164" s="2" t="inlineStr">
         <is>
-          <t>https://3w.huanqiu.com/a/de583b/4TE5JD6omnj</t>
+          <t>https://finance.sina.com.cn/tech/roll/2025-07-03/doc-infeerfp4024842.shtml</t>
         </is>
       </c>
     </row>
@@ -9027,17 +9027,17 @@
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>RETURN_002</t>
+          <t>RETURN_003</t>
         </is>
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>新浪科技 / 中关村在线</t>
+          <t>路透社（经环球网 / 新浪转载）</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F165" s="2" t="inlineStr">
@@ -9062,7 +9062,7 @@
       </c>
       <c r="L165" s="2" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/tech/roll/2025-07-03/doc-infeerfp4024842.shtml</t>
+          <t>https://3w.huanqiu.com/a/de583b/4TE5JD6omnj</t>
         </is>
       </c>
     </row>
@@ -9235,17 +9235,17 @@
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>RETURN_003</t>
+          <t>RETURN_002</t>
         </is>
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>路透社（经环球网 / 新浪转载）</t>
+          <t>新浪科技 / 中关村在线</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="F169" s="2" t="inlineStr">
@@ -9270,7 +9270,7 @@
       </c>
       <c r="L169" s="2" t="inlineStr">
         <is>
-          <t>https://3w.huanqiu.com/a/de583b/4TE5JD6omnj</t>
+          <t>https://finance.sina.com.cn/tech/roll/2025-07-03/doc-infeerfp4024842.shtml</t>
         </is>
       </c>
     </row>
@@ -9287,17 +9287,17 @@
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>RETURN_002</t>
+          <t>RETURN_003</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>新浪科技 / 中关村在线</t>
+          <t>路透社（经环球网 / 新浪转载）</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F170" s="2" t="inlineStr">
@@ -9322,7 +9322,7 @@
       </c>
       <c r="L170" s="2" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/tech/roll/2025-07-03/doc-infeerfp4024842.shtml</t>
+          <t>https://3w.huanqiu.com/a/de583b/4TE5JD6omnj</t>
         </is>
       </c>
     </row>
@@ -10831,7 +10831,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2025-01-22</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -10861,7 +10861,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>https://tech.ifeng.com/c/8gLk1Msnjan</t>
+          <t>https://otomotif.antaranews.com/berita/5724273/pabrik-byd-di-subang-resmi-beroperasi-dan-serap-5000-pekerja-lokal</t>
         </is>
       </c>
       <c r="K26" s="2" t="n">
@@ -14081,12 +14081,12 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>在西爪哇省苏邦工业园区建设印尼工厂，总投资约 10 亿美元，规划年产能 15 万辆，计划 2025 年底前竣工；与泰国工厂共同构成东南亚双基地，中国产能保留。</t>
+          <t>在西爪哇省苏邦 Smartpolitan 工业园区建设印尼工厂，投资约 16 万亿印尼盾（约 10 亿美元），最大年产能 15 万辆；2026-09-03 正式投产启用，为比亚迪全球第 13 座整车工厂。与泰国工厂共同构成东南亚双基地，中国产能保留。</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>NEWS_015</t>
+          <t>NEWS_015; NEWS_024; NEWS_025</t>
         </is>
       </c>
       <c r="E52" s="2" t="n">
@@ -14094,7 +14094,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>凤凰科技</t>
+          <t>ANTARA（印尼国家通讯社）; 凤凰科技</t>
         </is>
       </c>
       <c r="G52" s="2" t="n">
@@ -14119,12 +14119,12 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>本地生产规避印尼整车进口关税，获得电动车补贴资格。</t>
+          <t>本地生产规避印尼整车进口关税并满足本地化率（TKDN）要求，保住电动车激励资格；工厂投资约 16 万亿印尼盾。</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>NEWS_015</t>
+          <t>NEWS_015; NEWS_024; NEWS_025</t>
         </is>
       </c>
       <c r="E53" s="2" t="n">
@@ -14132,7 +14132,7 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>凤凰科技</t>
+          <t>ANTARA（印尼国家通讯社）; 凤凰科技</t>
         </is>
       </c>
       <c r="G53" s="2" t="n">
@@ -14157,12 +14157,12 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>截至 2025 年报道仍处于建设阶段，预计 2025 年底竣工（结果待验证）。</t>
+          <t>2026-09-03 正式投产，最大年产能 15 万辆，投产后实际产量约 1 万辆/月；启用仪式同场下线印尼本地生产的第 10 万辆整车。</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>NEWS_015</t>
+          <t>NEWS_015; NEWS_024; NEWS_025</t>
         </is>
       </c>
       <c r="E54" s="2" t="n">
@@ -14170,7 +14170,7 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>凤凰科技</t>
+          <t>ANTARA（印尼国家通讯社）; 凤凰科技</t>
         </is>
       </c>
       <c r="G54" s="2" t="n">
@@ -14195,12 +14195,12 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>以本地生产进入印尼市场，直接与日系品牌竞争。</t>
+          <t>2026-09 起停止整车进口、全面转为本地生产，以本地化进入印尼市场并与日系品牌竞争。</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>NEWS_015</t>
+          <t>NEWS_015; NEWS_024; NEWS_025</t>
         </is>
       </c>
       <c r="E55" s="2" t="n">
@@ -14208,7 +14208,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>凤凰科技</t>
+          <t>ANTARA（印尼国家通讯社）; 凤凰科技</t>
         </is>
       </c>
       <c r="G55" s="2" t="n">
@@ -14238,7 +14238,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>NEWS_015</t>
+          <t>NEWS_015; NEWS_024; NEWS_025</t>
         </is>
       </c>
       <c r="E56" s="2" t="n">
@@ -14246,7 +14246,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>凤凰科技</t>
+          <t>ANTARA（印尼国家通讯社）; 凤凰科技</t>
         </is>
       </c>
       <c r="G56" s="2" t="n">
@@ -14461,7 +14461,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>计划在越南北部（太原省）投资约 40 亿美元建设芯片测试与封装工厂，分阶段实施；中国西安等既有基地继续运营，形成'韩国 + 中国 + 越南'的多地产能结构。</t>
+          <t>计划在越南北部（太原省）投资约 15 亿美元建设芯片测试与封装工厂（已见报道的初始项目）。媒体另称可能追加约 25 亿美元的第二工厂投资——该项为条件性后续计划，尚未确认实施，不能与初始项目合并为单一'约 40 亿美元'已确定项目。中国西安等既有基地继续运营，形成'韩国 + 中国 + 越南'的多地产能结构。</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -14537,7 +14537,7 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>截至 2026 年仍为投资计划阶段（结果待验证）。</t>
+          <t>截至 2026 年 10 月仍为投资计划阶段，未见公司正式公告确认实施或落地产能。</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -14841,7 +14841,7 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>2025 年 7 月及 12 月，富士康两度从印度工厂撤回中国大陆工程师与技术团队，部分产能与订单回流中国大陆；印度的组装布局并未取消，但节奏明显放缓。</t>
+          <t>2025 年 7 月及 12 月，富士康两度要求/撤回其印度工厂的中国大陆工程师与技术团队（彭博社等报道）。印度的组装布局并未取消，但推进节奏明显放缓。注：现有证据仅支持'工程团队撤回、工程支持减弱'，不足以证明订单或产能已实际回流中国。</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -14879,7 +14879,7 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>撤回技术人员降低了印度工厂的爬坡效率，短期成本上升；中国基地继续承担高难度工序。</t>
+          <t>撤回技术人员降低了印度工厂的爬坡效率，短期成本上升；高难度工序仍由中国基地承担。</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -14917,7 +14917,7 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>印度工厂良率与产能爬坡受阻，中国大陆产能利用率回升。</t>
+          <t>印度工厂工程支持减弱、本地良率与产能爬坡受阻（有报道支持）；中国大陆产能利用率是否回升尚无直接证据，待验证。</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -14993,7 +14993,7 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>验证了'关键工序与工程能力仍在中国'的结构性依赖。</t>
+          <t>印证了'关键工序与工程能力仍依赖中国'的结构性依赖（有报道支持）。</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">

--- a/data/evaluation/evidence_quality_test.xlsx
+++ b/data/evaluation/evidence_quality_test.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Citation Test'!$A$1:$L$171</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Corpus Citation Coverage'!$A$1:$L$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Corpus Citation Coverage'!$A$1:$L$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Conclusion Audit'!$A$1:$H$86</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -546,22 +546,22 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>比亚迪 BYD：Operational Risk</t>
+          <t>比亚迪 BYD：Market Access Risk</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>RELOC_001</t>
+          <t>MOFCOM_001</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>东方财富网（转比亚迪官方）</t>
+          <t>商务部、海关总署</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>2024-07-04</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -586,7 +586,7 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>https://finance.eastmoney.com/a/202407043122188760.html</t>
+          <t>https://www.mofcom.gov.cn/zwgk/zcfb/art/2025/art_c03d1e511b2b486e829d68e8f1422aff.html</t>
         </is>
       </c>
     </row>
@@ -603,22 +603,22 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>RETURN_001</t>
+          <t>CASE_004</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>恩捷股份公告（经东方财富网 / 央广网报道）</t>
+          <t>国盛证券（经腾讯新闻转载）</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2025-11-30</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="G3" s="2" t="n">
@@ -638,7 +638,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>https://finance.eastmoney.com/a/202605223746866215.html</t>
+          <t>https://news.qq.com/rain/a/20251130A04A7P00</t>
         </is>
       </c>
     </row>
@@ -655,17 +655,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>RETURN_004</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>36氪 / 财新网</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixin.com/2024-10-28/102250409.html</t>
+          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
         </is>
       </c>
     </row>
@@ -702,27 +702,27 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>比亚迪 BYD：Operational Risk</t>
+          <t>比亚迪 BYD：Regulatory Risk</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>RELOC_003</t>
+          <t>MOFCOM_001</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>澎湃新闻 / 盖世汽车社区</t>
+          <t>商务部、海关总署</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2022-11-19</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G5" s="2" t="n">
@@ -742,7 +742,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>https://m.thepaper.cn/newsDetail_forward_20810032</t>
+          <t>https://www.mofcom.gov.cn/zwgk/zcfb/art/2025/art_c03d1e511b2b486e829d68e8f1422aff.html</t>
         </is>
       </c>
     </row>
@@ -754,27 +754,27 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>比亚迪 BYD：Operational Risk</t>
+          <t>比亚迪 BYD：Supply Chain Risk</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>RELOC_006</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>澎湃新闻</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2024-02-28</t>
+          <t>持续更新</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
@@ -794,7 +794,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>https://www.thepaper.cn/newsDetail_forward_26493905</t>
+          <t>https://comtradeplus.un.org</t>
         </is>
       </c>
     </row>
@@ -811,22 +811,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>RELOC_001</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>东方财富网（转比亚迪官方）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2024-07-04</t>
+          <t>持续更新</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G7" s="2" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>https://finance.eastmoney.com/a/202407043122188760.html</t>
+          <t>https://comtradeplus.un.org</t>
         </is>
       </c>
     </row>
@@ -863,22 +863,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>RETURN_001</t>
+          <t>CASE_004</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>恩捷股份公告（经东方财富网 / 央广网报道）</t>
+          <t>国盛证券（经腾讯新闻转载）</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2025-11-30</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
@@ -898,7 +898,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>https://finance.eastmoney.com/a/202605223746866215.html</t>
+          <t>https://news.qq.com/rain/a/20251130A04A7P00</t>
         </is>
       </c>
     </row>
@@ -915,17 +915,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>RETURN_004</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>36氪 / 财新网</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -950,7 +950,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixin.com/2024-10-28/102250409.html</t>
+          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
         </is>
       </c>
     </row>
@@ -962,27 +962,27 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>比亚迪 BYD：Supply Chain Risk</t>
+          <t>比亚迪 BYD：Trade Risk</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>RELOC_003</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>澎湃新闻 / 盖世汽车社区</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2022-11-19</t>
+          <t>持续更新</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G10" s="2" t="n">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>https://m.thepaper.cn/newsDetail_forward_20810032</t>
+          <t>https://comtradeplus.un.org</t>
         </is>
       </c>
     </row>
@@ -1014,27 +1014,27 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>比亚迪 BYD：Supply Chain Risk</t>
+          <t>比亚迪 BYD：Trade Risk</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>RELOC_006</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>澎湃新闻</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2024-02-28</t>
+          <t>持续更新</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G11" s="2" t="n">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>https://www.thepaper.cn/newsDetail_forward_26493905</t>
+          <t>https://comtradeplus.un.org</t>
         </is>
       </c>
     </row>
@@ -1066,22 +1066,22 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>长安汽车 Changan Automobile：Operational Risk</t>
+          <t>长安汽车 Changan Automobile：Market Access Risk</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>RELOC_002</t>
+          <t>MOFCOM_001</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>易车 / 证券之星（投资者互动平台）</t>
+          <t>商务部、海关总署</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>https://news.yiche.com/hao/wenzhang/100585175/</t>
+          <t>https://www.mofcom.gov.cn/zwgk/zcfb/art/2025/art_c03d1e511b2b486e829d68e8f1422aff.html</t>
         </is>
       </c>
     </row>
@@ -1123,22 +1123,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>RETURN_001</t>
+          <t>CASE_004</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>恩捷股份公告（经东方财富网 / 央广网报道）</t>
+          <t>国盛证券（经腾讯新闻转载）</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2025-11-30</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="G13" s="2" t="n">
@@ -1158,7 +1158,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>https://finance.eastmoney.com/a/202605223746866215.html</t>
+          <t>https://news.qq.com/rain/a/20251130A04A7P00</t>
         </is>
       </c>
     </row>
@@ -1175,17 +1175,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>RELOC_003</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>澎湃新闻 / 盖世汽车社区</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2022-11-19</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1210,7 +1210,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>https://m.thepaper.cn/newsDetail_forward_20810032</t>
+          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
         </is>
       </c>
     </row>
@@ -1222,27 +1222,27 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>长安汽车 Changan Automobile：Operational Risk</t>
+          <t>长安汽车 Changan Automobile：Regulatory Risk</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>RETURN_004</t>
+          <t>MOFCOM_001</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>36氪 / 财新网</t>
+          <t>商务部、海关总署</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G15" s="2" t="n">
@@ -1262,7 +1262,7 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixin.com/2024-10-28/102250409.html</t>
+          <t>https://www.mofcom.gov.cn/zwgk/zcfb/art/2025/art_c03d1e511b2b486e829d68e8f1422aff.html</t>
         </is>
       </c>
     </row>
@@ -1274,27 +1274,27 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>长安汽车 Changan Automobile：Operational Risk</t>
+          <t>长安汽车 Changan Automobile：Supply Chain Risk</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>RELOC_006</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>澎湃新闻</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2024-02-28</t>
+          <t>持续更新</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G16" s="2" t="n">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>https://www.thepaper.cn/newsDetail_forward_26493905</t>
+          <t>https://comtradeplus.un.org</t>
         </is>
       </c>
     </row>
@@ -1331,22 +1331,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>RELOC_002</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>易车 / 证券之星（投资者互动平台）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>持续更新</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G17" s="2" t="n">
@@ -1366,7 +1366,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>https://news.yiche.com/hao/wenzhang/100585175/</t>
+          <t>https://comtradeplus.un.org</t>
         </is>
       </c>
     </row>
@@ -1383,22 +1383,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>RETURN_001</t>
+          <t>CASE_004</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>恩捷股份公告（经东方财富网 / 央广网报道）</t>
+          <t>国盛证券（经腾讯新闻转载）</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2025-11-30</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="G18" s="2" t="n">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>https://finance.eastmoney.com/a/202605223746866215.html</t>
+          <t>https://news.qq.com/rain/a/20251130A04A7P00</t>
         </is>
       </c>
     </row>
@@ -1435,17 +1435,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>RELOC_003</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>澎湃新闻 / 盖世汽车社区</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2022-11-19</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>https://m.thepaper.cn/newsDetail_forward_20810032</t>
+          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
         </is>
       </c>
     </row>
@@ -1482,27 +1482,27 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>长安汽车 Changan Automobile：Supply Chain Risk</t>
+          <t>长安汽车 Changan Automobile：Trade Risk</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>RETURN_004</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>36氪 / 财新网</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>持续更新</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G20" s="2" t="n">
@@ -1522,7 +1522,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixin.com/2024-10-28/102250409.html</t>
+          <t>https://comtradeplus.un.org</t>
         </is>
       </c>
     </row>
@@ -1534,27 +1534,27 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>长安汽车 Changan Automobile：Supply Chain Risk</t>
+          <t>长安汽车 Changan Automobile：Trade Risk</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>RELOC_006</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>澎湃新闻</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2024-02-28</t>
+          <t>持续更新</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G21" s="2" t="n">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>https://www.thepaper.cn/newsDetail_forward_26493905</t>
+          <t>https://comtradeplus.un.org</t>
         </is>
       </c>
     </row>
@@ -1586,27 +1586,27 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>国轩高科 Gotion High-Tech：Operational Risk</t>
+          <t>国轩高科 Gotion High-Tech：Market Access Risk</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>RELOC_003</t>
+          <t>MOFCOM_001</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>澎湃新闻 / 盖世汽车社区</t>
+          <t>商务部、海关总署</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2022-11-19</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G22" s="2" t="n">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>https://m.thepaper.cn/newsDetail_forward_20810032</t>
+          <t>https://www.mofcom.gov.cn/zwgk/zcfb/art/2025/art_c03d1e511b2b486e829d68e8f1422aff.html</t>
         </is>
       </c>
     </row>
@@ -1643,22 +1643,22 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>RETURN_001</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>恩捷股份公告（经东方财富网 / 央广网报道）</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="G23" s="2" t="n">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>https://finance.eastmoney.com/a/202605223746866215.html</t>
+          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
         </is>
       </c>
     </row>
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>RELOC_005</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>东方财富网 / 腾讯新闻</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>https://finance.eastmoney.com/a/202407163131488556.html</t>
+          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
         </is>
       </c>
     </row>
@@ -1742,27 +1742,27 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>国轩高科 Gotion High-Tech：Operational Risk</t>
+          <t>国轩高科 Gotion High-Tech：Regulatory Risk</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>RETURN_004</t>
+          <t>MOFCOM_001</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>36氪 / 财新网</t>
+          <t>商务部、海关总署</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G25" s="2" t="n">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixin.com/2024-10-28/102250409.html</t>
+          <t>https://www.mofcom.gov.cn/zwgk/zcfb/art/2025/art_c03d1e511b2b486e829d68e8f1422aff.html</t>
         </is>
       </c>
     </row>
@@ -1794,27 +1794,27 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>国轩高科 Gotion High-Tech：Operational Risk</t>
+          <t>国轩高科 Gotion High-Tech：Supply Chain Risk</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>RELOC_008</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>和讯网 / 网易</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>持续更新</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G26" s="2" t="n">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>https://futures.hexun.com/2024-04-08/212465761.html</t>
+          <t>https://comtradeplus.un.org</t>
         </is>
       </c>
     </row>
@@ -1851,22 +1851,22 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>RELOC_003</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>澎湃新闻 / 盖世汽车社区</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2022-11-19</t>
+          <t>持续更新</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G27" s="2" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>https://m.thepaper.cn/newsDetail_forward_20810032</t>
+          <t>https://comtradeplus.un.org</t>
         </is>
       </c>
     </row>
@@ -1903,22 +1903,22 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>RETURN_001</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>恩捷股份公告（经东方财富网 / 央广网报道）</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="G28" s="2" t="n">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>https://finance.eastmoney.com/a/202605223746866215.html</t>
+          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
         </is>
       </c>
     </row>
@@ -1955,17 +1955,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>RELOC_005</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>东方财富网 / 腾讯新闻</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -1990,7 +1990,7 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>https://finance.eastmoney.com/a/202407163131488556.html</t>
+          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
         </is>
       </c>
     </row>
@@ -2002,27 +2002,27 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>国轩高科 Gotion High-Tech：Supply Chain Risk</t>
+          <t>国轩高科 Gotion High-Tech：Trade Risk</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>RETURN_004</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>36氪 / 财新网</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>持续更新</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G30" s="2" t="n">
@@ -2042,7 +2042,7 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixin.com/2024-10-28/102250409.html</t>
+          <t>https://comtradeplus.un.org</t>
         </is>
       </c>
     </row>
@@ -2054,27 +2054,27 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>国轩高科 Gotion High-Tech：Supply Chain Risk</t>
+          <t>国轩高科 Gotion High-Tech：Trade Risk</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>RELOC_008</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>和讯网 / 网易</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>持续更新</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G31" s="2" t="n">
@@ -2094,7 +2094,7 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>https://futures.hexun.com/2024-04-08/212465761.html</t>
+          <t>https://comtradeplus.un.org</t>
         </is>
       </c>
     </row>
@@ -2106,27 +2106,27 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>亿纬锂能 EVE Energy：Operational Risk</t>
+          <t>亿纬锂能 EVE Energy：Market Access Risk</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>RELOC_004</t>
+          <t>MOFCOM_001</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>新浪财经</t>
+          <t>商务部、海关总署</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G32" s="2" t="n">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/roll/2026-02-06/doc-inhkwssf2073873.shtml</t>
+          <t>https://www.mofcom.gov.cn/zwgk/zcfb/art/2025/art_c03d1e511b2b486e829d68e8f1422aff.html</t>
         </is>
       </c>
     </row>
@@ -2163,22 +2163,22 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>RETURN_001</t>
+          <t>CASE_007</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>恩捷股份公告（经东方财富网 / 央广网报道）</t>
+          <t>C114通信网</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="G33" s="2" t="n">
@@ -2198,7 +2198,7 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>https://finance.eastmoney.com/a/202605223746866215.html</t>
+          <t>https://www.c114.com.cn/other/241/a1307528.html</t>
         </is>
       </c>
     </row>
@@ -2215,17 +2215,17 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>RETURN_004</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>36氪 / 财新网</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixin.com/2024-10-28/102250409.html</t>
+          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
         </is>
       </c>
     </row>
@@ -2262,27 +2262,27 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>亿纬锂能 EVE Energy：Operational Risk</t>
+          <t>亿纬锂能 EVE Energy：Regulatory Risk</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>RELOC_003</t>
+          <t>MOFCOM_001</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>澎湃新闻 / 盖世汽车社区</t>
+          <t>商务部、海关总署</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>2022-11-19</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G35" s="2" t="n">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>https://m.thepaper.cn/newsDetail_forward_20810032</t>
+          <t>https://www.mofcom.gov.cn/zwgk/zcfb/art/2025/art_c03d1e511b2b486e829d68e8f1422aff.html</t>
         </is>
       </c>
     </row>
@@ -2319,22 +2319,22 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>RELOC_004</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>新浪财经</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>持续更新</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G36" s="2" t="n">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/roll/2026-02-06/doc-inhkwssf2073873.shtml</t>
+          <t>https://comtradeplus.un.org</t>
         </is>
       </c>
     </row>
@@ -2371,22 +2371,22 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>RETURN_001</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>恩捷股份公告（经东方财富网 / 央广网报道）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>持续更新</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G37" s="2" t="n">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>https://finance.eastmoney.com/a/202605223746866215.html</t>
+          <t>https://comtradeplus.un.org</t>
         </is>
       </c>
     </row>
@@ -2423,17 +2423,17 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>RETURN_004</t>
+          <t>CASE_007</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>36氪 / 财新网</t>
+          <t>C114通信网</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2458,7 +2458,7 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixin.com/2024-10-28/102250409.html</t>
+          <t>https://www.c114.com.cn/other/241/a1307528.html</t>
         </is>
       </c>
     </row>
@@ -2475,22 +2475,22 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>TRD_001</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>持续更新</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="G39" s="2" t="n">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org</t>
+          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
         </is>
       </c>
     </row>
@@ -2522,27 +2522,27 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>亿纬锂能 EVE Energy：Supply Chain Risk</t>
+          <t>亿纬锂能 EVE Energy：Trade Risk</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>RELOC_003</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>澎湃新闻 / 盖世汽车社区</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>2022-11-19</t>
+          <t>持续更新</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G40" s="2" t="n">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>https://m.thepaper.cn/newsDetail_forward_20810032</t>
+          <t>https://comtradeplus.un.org</t>
         </is>
       </c>
     </row>
@@ -2579,7 +2579,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>TRD_001</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -2626,27 +2626,27 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>欣旺达 Sunwoda：Operational Risk</t>
+          <t>欣旺达 Sunwoda：Market Access Risk</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>RELOC_005</t>
+          <t>MOFCOM_001</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>东方财富网 / 腾讯新闻</t>
+          <t>商务部、海关总署</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G42" s="2" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>https://finance.eastmoney.com/a/202407163131488556.html</t>
+          <t>https://www.mofcom.gov.cn/zwgk/zcfb/art/2025/art_c03d1e511b2b486e829d68e8f1422aff.html</t>
         </is>
       </c>
     </row>
@@ -2683,17 +2683,17 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>RELOC_003</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>澎湃新闻 / 盖世汽车社区</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>2022-11-19</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>https://m.thepaper.cn/newsDetail_forward_20810032</t>
+          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
         </is>
       </c>
     </row>
@@ -2735,22 +2735,22 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>RETURN_001</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>恩捷股份公告（经东方财富网 / 央广网报道）</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="G44" s="2" t="n">
@@ -2770,7 +2770,7 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>https://finance.eastmoney.com/a/202605223746866215.html</t>
+          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
         </is>
       </c>
     </row>
@@ -2782,27 +2782,27 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>欣旺达 Sunwoda：Operational Risk</t>
+          <t>欣旺达 Sunwoda：Regulatory Risk</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>RETURN_004</t>
+          <t>MOFCOM_001</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>36氪 / 财新网</t>
+          <t>商务部、海关总署</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G45" s="2" t="n">
@@ -2822,7 +2822,7 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixin.com/2024-10-28/102250409.html</t>
+          <t>https://www.mofcom.gov.cn/zwgk/zcfb/art/2025/art_c03d1e511b2b486e829d68e8f1422aff.html</t>
         </is>
       </c>
     </row>
@@ -2834,27 +2834,27 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>欣旺达 Sunwoda：Operational Risk</t>
+          <t>欣旺达 Sunwoda：Supply Chain Risk</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>RETURN_002</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>新浪科技 / 中关村在线</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>持续更新</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G46" s="2" t="n">
@@ -2874,7 +2874,7 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/tech/roll/2025-07-03/doc-infeerfp4024842.shtml</t>
+          <t>https://comtradeplus.un.org</t>
         </is>
       </c>
     </row>
@@ -2891,22 +2891,22 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>RELOC_005</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>东方财富网 / 腾讯新闻</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>持续更新</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G47" s="2" t="n">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>https://finance.eastmoney.com/a/202407163131488556.html</t>
+          <t>https://comtradeplus.un.org</t>
         </is>
       </c>
     </row>
@@ -2943,17 +2943,17 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>RELOC_003</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>澎湃新闻 / 盖世汽车社区</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>2022-11-19</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -2978,7 +2978,7 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>https://m.thepaper.cn/newsDetail_forward_20810032</t>
+          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
         </is>
       </c>
     </row>
@@ -2995,22 +2995,22 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>RETURN_001</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>恩捷股份公告（经东方财富网 / 央广网报道）</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="G49" s="2" t="n">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>https://finance.eastmoney.com/a/202605223746866215.html</t>
+          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
         </is>
       </c>
     </row>
@@ -3042,27 +3042,27 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>欣旺达 Sunwoda：Supply Chain Risk</t>
+          <t>欣旺达 Sunwoda：Trade Risk</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>RETURN_004</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>36氪 / 财新网</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>持续更新</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G50" s="2" t="n">
@@ -3082,7 +3082,7 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixin.com/2024-10-28/102250409.html</t>
+          <t>https://comtradeplus.un.org</t>
         </is>
       </c>
     </row>
@@ -3094,27 +3094,27 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>欣旺达 Sunwoda：Supply Chain Risk</t>
+          <t>欣旺达 Sunwoda：Trade Risk</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>RETURN_002</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>新浪科技 / 中关村在线</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>持续更新</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G51" s="2" t="n">
@@ -3134,7 +3134,7 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/tech/roll/2025-07-03/doc-infeerfp4024842.shtml</t>
+          <t>https://comtradeplus.un.org</t>
         </is>
       </c>
     </row>
@@ -3146,27 +3146,27 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>蜂巢能源 SVOLT：Operational Risk</t>
+          <t>蜂巢能源 SVOLT：Market Access Risk</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>RETURN_004</t>
+          <t>MOFCOM_001</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>36氪 / 财新网</t>
+          <t>商务部、海关总署</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G52" s="2" t="n">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixin.com/2024-10-28/102250409.html</t>
+          <t>https://www.mofcom.gov.cn/zwgk/zcfb/art/2025/art_c03d1e511b2b486e829d68e8f1422aff.html</t>
         </is>
       </c>
     </row>
@@ -3203,17 +3203,17 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>RELOC_006</t>
+          <t>CASE_004</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>澎湃新闻</t>
+          <t>国盛证券（经腾讯新闻转载）</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>2024-02-28</t>
+          <t>2025-11-30</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -3238,7 +3238,7 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>https://www.thepaper.cn/newsDetail_forward_26493905</t>
+          <t>https://news.qq.com/rain/a/20251130A04A7P00</t>
         </is>
       </c>
     </row>
@@ -3255,22 +3255,22 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>RETURN_001</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>恩捷股份公告（经东方财富网 / 央广网报道）</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="G54" s="2" t="n">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>https://finance.eastmoney.com/a/202605223746866215.html</t>
+          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
         </is>
       </c>
     </row>
@@ -3302,27 +3302,27 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>蜂巢能源 SVOLT：Operational Risk</t>
+          <t>蜂巢能源 SVOLT：Regulatory Risk</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>RELOC_003</t>
+          <t>MOFCOM_001</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>澎湃新闻 / 盖世汽车社区</t>
+          <t>商务部、海关总署</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>2022-11-19</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G55" s="2" t="n">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>https://m.thepaper.cn/newsDetail_forward_20810032</t>
+          <t>https://www.mofcom.gov.cn/zwgk/zcfb/art/2025/art_c03d1e511b2b486e829d68e8f1422aff.html</t>
         </is>
       </c>
     </row>
@@ -3354,27 +3354,27 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>蜂巢能源 SVOLT：Operational Risk</t>
+          <t>蜂巢能源 SVOLT：Supply Chain Risk</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>RELOC_008</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>和讯网 / 网易</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>持续更新</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G56" s="2" t="n">
@@ -3394,7 +3394,7 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>https://futures.hexun.com/2024-04-08/212465761.html</t>
+          <t>https://comtradeplus.un.org</t>
         </is>
       </c>
     </row>
@@ -3411,22 +3411,22 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>RETURN_004</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>36氪 / 财新网</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>持续更新</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G57" s="2" t="n">
@@ -3446,7 +3446,7 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixin.com/2024-10-28/102250409.html</t>
+          <t>https://comtradeplus.un.org</t>
         </is>
       </c>
     </row>
@@ -3463,17 +3463,17 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>RELOC_006</t>
+          <t>CASE_004</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>澎湃新闻</t>
+          <t>国盛证券（经腾讯新闻转载）</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>2024-02-28</t>
+          <t>2025-11-30</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>https://www.thepaper.cn/newsDetail_forward_26493905</t>
+          <t>https://news.qq.com/rain/a/20251130A04A7P00</t>
         </is>
       </c>
     </row>
@@ -3515,22 +3515,22 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>RETURN_001</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>恩捷股份公告（经东方财富网 / 央广网报道）</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="G59" s="2" t="n">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>https://finance.eastmoney.com/a/202605223746866215.html</t>
+          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
         </is>
       </c>
     </row>
@@ -3562,27 +3562,27 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>蜂巢能源 SVOLT：Supply Chain Risk</t>
+          <t>蜂巢能源 SVOLT：Trade Risk</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>RELOC_003</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>澎湃新闻 / 盖世汽车社区</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>2022-11-19</t>
+          <t>持续更新</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G60" s="2" t="n">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>https://m.thepaper.cn/newsDetail_forward_20810032</t>
+          <t>https://comtradeplus.un.org</t>
         </is>
       </c>
     </row>
@@ -3614,27 +3614,27 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>蜂巢能源 SVOLT：Supply Chain Risk</t>
+          <t>蜂巢能源 SVOLT：Trade Risk</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>RELOC_008</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>和讯网 / 网易</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>持续更新</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G61" s="2" t="n">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>https://futures.hexun.com/2024-04-08/212465761.html</t>
+          <t>https://comtradeplus.un.org</t>
         </is>
       </c>
     </row>
@@ -3666,27 +3666,27 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>华友钴业 Huayou Cobalt：Operational Risk</t>
+          <t>华友钴业 Huayou Cobalt：Market Access Risk</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>RELOC_007</t>
+          <t>MOFCOM_001</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>新浪财经</t>
+          <t>商务部、海关总署</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G62" s="2" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/stock/relnews/cn/2024-04-12/doc-inarqawt9056004.shtml</t>
+          <t>https://www.mofcom.gov.cn/zwgk/zcfb/art/2025/art_c03d1e511b2b486e829d68e8f1422aff.html</t>
         </is>
       </c>
     </row>
@@ -3723,22 +3723,22 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>RETURN_001</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>恩捷股份公告（经东方财富网 / 央广网报道）</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="G63" s="2" t="n">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>https://finance.eastmoney.com/a/202605223746866215.html</t>
+          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
         </is>
       </c>
     </row>
@@ -3775,17 +3775,17 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>RELOC_003</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>澎湃新闻 / 盖世汽车社区</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>2022-11-19</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -3810,7 +3810,7 @@
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>https://m.thepaper.cn/newsDetail_forward_20810032</t>
+          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
         </is>
       </c>
     </row>
@@ -3822,27 +3822,27 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>华友钴业 Huayou Cobalt：Operational Risk</t>
+          <t>华友钴业 Huayou Cobalt：Regulatory Risk</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>RELOC_008</t>
+          <t>MOFCOM_001</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>和讯网 / 网易</t>
+          <t>商务部、海关总署</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G65" s="2" t="n">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>https://futures.hexun.com/2024-04-08/212465761.html</t>
+          <t>https://www.mofcom.gov.cn/zwgk/zcfb/art/2025/art_c03d1e511b2b486e829d68e8f1422aff.html</t>
         </is>
       </c>
     </row>
@@ -3874,27 +3874,27 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>华友钴业 Huayou Cobalt：Operational Risk</t>
+          <t>华友钴业 Huayou Cobalt：Supply Chain Risk</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>RETURN_004</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>36氪 / 财新网</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>持续更新</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G66" s="2" t="n">
@@ -3914,7 +3914,7 @@
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixin.com/2024-10-28/102250409.html</t>
+          <t>https://comtradeplus.un.org</t>
         </is>
       </c>
     </row>
@@ -3931,22 +3931,22 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>RELOC_007</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>新浪财经</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>持续更新</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G67" s="2" t="n">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/stock/relnews/cn/2024-04-12/doc-inarqawt9056004.shtml</t>
+          <t>https://comtradeplus.un.org</t>
         </is>
       </c>
     </row>
@@ -3983,22 +3983,22 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>RETURN_001</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>恩捷股份公告（经东方财富网 / 央广网报道）</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="G68" s="2" t="n">
@@ -4018,7 +4018,7 @@
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>https://finance.eastmoney.com/a/202605223746866215.html</t>
+          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
         </is>
       </c>
     </row>
@@ -4035,17 +4035,17 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>RELOC_003</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>澎湃新闻 / 盖世汽车社区</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>2022-11-19</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>https://m.thepaper.cn/newsDetail_forward_20810032</t>
+          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
         </is>
       </c>
     </row>
@@ -4082,27 +4082,27 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>华友钴业 Huayou Cobalt：Supply Chain Risk</t>
+          <t>华友钴业 Huayou Cobalt：Trade Risk</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>RELOC_008</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>和讯网 / 网易</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>持续更新</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G70" s="2" t="n">
@@ -4122,7 +4122,7 @@
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>https://futures.hexun.com/2024-04-08/212465761.html</t>
+          <t>https://comtradeplus.un.org</t>
         </is>
       </c>
     </row>
@@ -4134,27 +4134,27 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>华友钴业 Huayou Cobalt：Supply Chain Risk</t>
+          <t>华友钴业 Huayou Cobalt：Trade Risk</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>RETURN_004</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>36氪 / 财新网</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>持续更新</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G71" s="2" t="n">
@@ -4174,7 +4174,7 @@
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixin.com/2024-10-28/102250409.html</t>
+          <t>https://comtradeplus.un.org</t>
         </is>
       </c>
     </row>
@@ -4186,27 +4186,27 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>中伟股份 CNGR Advanced Material：Operational Risk</t>
+          <t>中伟股份 CNGR Advanced Material：Market Access Risk</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>RELOC_008</t>
+          <t>MOFCOM_001</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>和讯网 / 网易</t>
+          <t>商务部、海关总署</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G72" s="2" t="n">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>https://futures.hexun.com/2024-04-08/212465761.html</t>
+          <t>https://www.mofcom.gov.cn/zwgk/zcfb/art/2025/art_c03d1e511b2b486e829d68e8f1422aff.html</t>
         </is>
       </c>
     </row>
@@ -4243,22 +4243,22 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>RETURN_001</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>恩捷股份公告（经东方财富网 / 央广网报道）</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="G73" s="2" t="n">
@@ -4278,7 +4278,7 @@
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>https://finance.eastmoney.com/a/202605223746866215.html</t>
+          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
         </is>
       </c>
     </row>
@@ -4295,17 +4295,17 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>RELOC_003</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>澎湃新闻 / 盖世汽车社区</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>2022-11-19</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -4330,7 +4330,7 @@
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>https://m.thepaper.cn/newsDetail_forward_20810032</t>
+          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
         </is>
       </c>
     </row>
@@ -4342,27 +4342,27 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>中伟股份 CNGR Advanced Material：Operational Risk</t>
+          <t>中伟股份 CNGR Advanced Material：Regulatory Risk</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>RETURN_004</t>
+          <t>MOFCOM_001</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>36氪 / 财新网</t>
+          <t>商务部、海关总署</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G75" s="2" t="n">
@@ -4382,7 +4382,7 @@
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixin.com/2024-10-28/102250409.html</t>
+          <t>https://www.mofcom.gov.cn/zwgk/zcfb/art/2025/art_c03d1e511b2b486e829d68e8f1422aff.html</t>
         </is>
       </c>
     </row>
@@ -4394,27 +4394,27 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>中伟股份 CNGR Advanced Material：Operational Risk</t>
+          <t>中伟股份 CNGR Advanced Material：Supply Chain Risk</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>RELOC_007</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>新浪财经</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>持续更新</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G76" s="2" t="n">
@@ -4434,7 +4434,7 @@
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/stock/relnews/cn/2024-04-12/doc-inarqawt9056004.shtml</t>
+          <t>https://comtradeplus.un.org</t>
         </is>
       </c>
     </row>
@@ -4451,22 +4451,22 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>RELOC_008</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>和讯网 / 网易</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>持续更新</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G77" s="2" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>https://futures.hexun.com/2024-04-08/212465761.html</t>
+          <t>https://comtradeplus.un.org</t>
         </is>
       </c>
     </row>
@@ -4503,22 +4503,22 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>RETURN_001</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>恩捷股份公告（经东方财富网 / 央广网报道）</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="G78" s="2" t="n">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>https://finance.eastmoney.com/a/202605223746866215.html</t>
+          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
         </is>
       </c>
     </row>
@@ -4555,17 +4555,17 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>RELOC_003</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>澎湃新闻 / 盖世汽车社区</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>2022-11-19</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -4590,7 +4590,7 @@
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>https://m.thepaper.cn/newsDetail_forward_20810032</t>
+          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
         </is>
       </c>
     </row>
@@ -4602,27 +4602,27 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>中伟股份 CNGR Advanced Material：Supply Chain Risk</t>
+          <t>中伟股份 CNGR Advanced Material：Trade Risk</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>RETURN_004</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>36氪 / 财新网</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>持续更新</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G80" s="2" t="n">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixin.com/2024-10-28/102250409.html</t>
+          <t>https://comtradeplus.un.org</t>
         </is>
       </c>
     </row>
@@ -4654,27 +4654,27 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>中伟股份 CNGR Advanced Material：Supply Chain Risk</t>
+          <t>中伟股份 CNGR Advanced Material：Trade Risk</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>RELOC_007</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>新浪财经</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>持续更新</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G81" s="2" t="n">
@@ -4694,7 +4694,7 @@
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/stock/relnews/cn/2024-04-12/doc-inarqawt9056004.shtml</t>
+          <t>https://comtradeplus.un.org</t>
         </is>
       </c>
     </row>
@@ -4706,27 +4706,27 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>宁德时代 CATL：Operational Risk</t>
+          <t>宁德时代 CATL：Market Access Risk</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>PLUS1_001</t>
+          <t>CASE_010</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>每日经济新闻 / 搜狐网</t>
+          <t>美国白宫（经律所解读）</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G82" s="2" t="n">
@@ -4746,7 +4746,7 @@
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>https://www.nbd.com.cn/articles/2026-09-22/4589059.html</t>
+          <t>https://www.alvarezandmarsal.com/node/97806</t>
         </is>
       </c>
     </row>
@@ -4763,17 +4763,17 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>PLUS1_002</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>东方财富网（转界面新闻）</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -4798,7 +4798,7 @@
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>https://finance.eastmoney.com/a/202507023446498365.html</t>
+          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
         </is>
       </c>
     </row>
@@ -4815,22 +4815,22 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>RETURN_001</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>恩捷股份公告（经东方财富网 / 央广网报道）</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="G84" s="2" t="n">
@@ -4850,7 +4850,7 @@
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>https://finance.eastmoney.com/a/202605223746866215.html</t>
+          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
         </is>
       </c>
     </row>
@@ -4867,17 +4867,17 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>RETURN_004</t>
+          <t>CASE_004</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>36氪 / 财新网</t>
+          <t>国盛证券（经腾讯新闻转载）</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2025-11-30</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -4902,7 +4902,7 @@
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixin.com/2024-10-28/102250409.html</t>
+          <t>https://news.qq.com/rain/a/20251130A04A7P00</t>
         </is>
       </c>
     </row>
@@ -4919,17 +4919,17 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>RELOC_004</t>
+          <t>CASE_007</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>新浪财经</t>
+          <t>C114通信网</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -4954,7 +4954,7 @@
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/roll/2026-02-06/doc-inhkwssf2073873.shtml</t>
+          <t>https://www.c114.com.cn/other/241/a1307528.html</t>
         </is>
       </c>
     </row>
@@ -4971,17 +4971,17 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>PLUS1_001</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>每日经济新闻 / 搜狐网</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -5006,7 +5006,7 @@
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>https://www.nbd.com.cn/articles/2026-09-22/4589059.html</t>
+          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
         </is>
       </c>
     </row>
@@ -5023,17 +5023,17 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>PLUS1_002</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>东方财富网（转界面新闻）</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
@@ -5058,7 +5058,7 @@
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>https://finance.eastmoney.com/a/202507023446498365.html</t>
+          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
         </is>
       </c>
     </row>
@@ -5075,22 +5075,22 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>RETURN_001</t>
+          <t>CASE_004</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>恩捷股份公告（经东方财富网 / 央广网报道）</t>
+          <t>国盛证券（经腾讯新闻转载）</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2025-11-30</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="G89" s="2" t="n">
@@ -5110,7 +5110,7 @@
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>https://finance.eastmoney.com/a/202605223746866215.html</t>
+          <t>https://news.qq.com/rain/a/20251130A04A7P00</t>
         </is>
       </c>
     </row>
@@ -5127,17 +5127,17 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>RETURN_004</t>
+          <t>CASE_007</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>36氪 / 财新网</t>
+          <t>C114通信网</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
@@ -5162,7 +5162,7 @@
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixin.com/2024-10-28/102250409.html</t>
+          <t>https://www.c114.com.cn/other/241/a1307528.html</t>
         </is>
       </c>
     </row>
@@ -5174,27 +5174,27 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>宁德时代 CATL：Supply Chain Risk</t>
+          <t>宁德时代 CATL：Trade Risk</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>RELOC_004</t>
+          <t>CASE_010</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>新浪财经</t>
+          <t>美国白宫（经律所解读）</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G91" s="2" t="n">
@@ -5214,7 +5214,7 @@
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/roll/2026-02-06/doc-inhkwssf2073873.shtml</t>
+          <t>https://www.alvarezandmarsal.com/node/97806</t>
         </is>
       </c>
     </row>
@@ -5226,27 +5226,27 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>宁德时代 CATL：Operational Risk</t>
+          <t>宁德时代 CATL：Market Access Risk</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>PLUS1_002</t>
+          <t>CASE_010</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>东方财富网（转界面新闻）</t>
+          <t>美国白宫（经律所解读）</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G92" s="2" t="n">
@@ -5266,7 +5266,7 @@
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>https://finance.eastmoney.com/a/202507023446498365.html</t>
+          <t>https://www.alvarezandmarsal.com/node/97806</t>
         </is>
       </c>
     </row>
@@ -5283,17 +5283,17 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>PLUS1_001</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>每日经济新闻 / 搜狐网</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
@@ -5318,7 +5318,7 @@
       </c>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>https://www.nbd.com.cn/articles/2026-09-22/4589059.html</t>
+          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
         </is>
       </c>
     </row>
@@ -5335,22 +5335,22 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>RETURN_001</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>恩捷股份公告（经东方财富网 / 央广网报道）</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="G94" s="2" t="n">
@@ -5370,7 +5370,7 @@
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>https://finance.eastmoney.com/a/202605223746866215.html</t>
+          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
         </is>
       </c>
     </row>
@@ -5387,17 +5387,17 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>RETURN_004</t>
+          <t>CASE_004</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>36氪 / 财新网</t>
+          <t>国盛证券（经腾讯新闻转载）</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2025-11-30</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
@@ -5422,7 +5422,7 @@
       </c>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixin.com/2024-10-28/102250409.html</t>
+          <t>https://news.qq.com/rain/a/20251130A04A7P00</t>
         </is>
       </c>
     </row>
@@ -5439,17 +5439,17 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>RETURN_002</t>
+          <t>CASE_007</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>新浪科技 / 中关村在线</t>
+          <t>C114通信网</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/tech/roll/2025-07-03/doc-infeerfp4024842.shtml</t>
+          <t>https://www.c114.com.cn/other/241/a1307528.html</t>
         </is>
       </c>
     </row>
@@ -5491,17 +5491,17 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>PLUS1_002</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>东方财富网（转界面新闻）</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>https://finance.eastmoney.com/a/202507023446498365.html</t>
+          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
         </is>
       </c>
     </row>
@@ -5543,17 +5543,17 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>PLUS1_001</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>每日经济新闻 / 搜狐网</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
@@ -5578,7 +5578,7 @@
       </c>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>https://www.nbd.com.cn/articles/2026-09-22/4589059.html</t>
+          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
         </is>
       </c>
     </row>
@@ -5595,22 +5595,22 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>RETURN_001</t>
+          <t>CASE_004</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>恩捷股份公告（经东方财富网 / 央广网报道）</t>
+          <t>国盛证券（经腾讯新闻转载）</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2025-11-30</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="G99" s="2" t="n">
@@ -5630,7 +5630,7 @@
       </c>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>https://finance.eastmoney.com/a/202605223746866215.html</t>
+          <t>https://news.qq.com/rain/a/20251130A04A7P00</t>
         </is>
       </c>
     </row>
@@ -5647,17 +5647,17 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>RETURN_004</t>
+          <t>CASE_007</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>36氪 / 财新网</t>
+          <t>C114通信网</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
@@ -5682,7 +5682,7 @@
       </c>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixin.com/2024-10-28/102250409.html</t>
+          <t>https://www.c114.com.cn/other/241/a1307528.html</t>
         </is>
       </c>
     </row>
@@ -5694,27 +5694,27 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>宁德时代 CATL：Supply Chain Risk</t>
+          <t>宁德时代 CATL：Trade Risk</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>RETURN_002</t>
+          <t>CASE_010</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>新浪科技 / 中关村在线</t>
+          <t>美国白宫（经律所解读）</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G101" s="2" t="n">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/tech/roll/2025-07-03/doc-infeerfp4024842.shtml</t>
+          <t>https://www.alvarezandmarsal.com/node/97806</t>
         </is>
       </c>
     </row>
@@ -5746,22 +5746,22 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>比亚迪 BYD：Operational Risk</t>
+          <t>比亚迪 BYD：Market Access Risk</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>RETURN_001</t>
+          <t>CASE_010</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>恩捷股份公告（经东方财富网 / 央广网报道）</t>
+          <t>美国白宫（经律所解读）</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
@@ -5786,7 +5786,7 @@
       </c>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>https://finance.eastmoney.com/a/202605223746866215.html</t>
+          <t>https://www.alvarezandmarsal.com/node/97806</t>
         </is>
       </c>
     </row>
@@ -5803,17 +5803,17 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>PLUS1_003</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>凤凰科技（转路透社）</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
@@ -5838,7 +5838,7 @@
       </c>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>https://otomotif.antaranews.com/berita/5724273/pabrik-byd-di-subang-resmi-beroperasi-dan-serap-5000-pekerja-lokal</t>
+          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
         </is>
       </c>
     </row>
@@ -5855,22 +5855,22 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>RELOC_001</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>东方财富网（转比亚迪官方）</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>2024-07-04</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="G104" s="2" t="n">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>https://finance.eastmoney.com/a/202407043122188760.html</t>
+          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
         </is>
       </c>
     </row>
@@ -5907,17 +5907,17 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>RETURN_004</t>
+          <t>CASE_004</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>36氪 / 财新网</t>
+          <t>国盛证券（经腾讯新闻转载）</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2025-11-30</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
@@ -5942,7 +5942,7 @@
       </c>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixin.com/2024-10-28/102250409.html</t>
+          <t>https://news.qq.com/rain/a/20251130A04A7P00</t>
         </is>
       </c>
     </row>
@@ -5959,17 +5959,17 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>RETURN_002</t>
+          <t>CASE_007</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>新浪科技 / 中关村在线</t>
+          <t>C114通信网</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
@@ -5994,7 +5994,7 @@
       </c>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/tech/roll/2025-07-03/doc-infeerfp4024842.shtml</t>
+          <t>https://www.c114.com.cn/other/241/a1307528.html</t>
         </is>
       </c>
     </row>
@@ -6011,22 +6011,22 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>RETURN_001</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>恩捷股份公告（经东方财富网 / 央广网报道）</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="G107" s="2" t="n">
@@ -6046,7 +6046,7 @@
       </c>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t>https://finance.eastmoney.com/a/202605223746866215.html</t>
+          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
         </is>
       </c>
     </row>
@@ -6063,17 +6063,17 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>PLUS1_003</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>凤凰科技（转路透社）</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
@@ -6098,7 +6098,7 @@
       </c>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t>https://otomotif.antaranews.com/berita/5724273/pabrik-byd-di-subang-resmi-beroperasi-dan-serap-5000-pekerja-lokal</t>
+          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
         </is>
       </c>
     </row>
@@ -6115,22 +6115,22 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>RELOC_001</t>
+          <t>CASE_004</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>东方财富网（转比亚迪官方）</t>
+          <t>国盛证券（经腾讯新闻转载）</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>2024-07-04</t>
+          <t>2025-11-30</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="G109" s="2" t="n">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="L109" s="2" t="inlineStr">
         <is>
-          <t>https://finance.eastmoney.com/a/202407043122188760.html</t>
+          <t>https://news.qq.com/rain/a/20251130A04A7P00</t>
         </is>
       </c>
     </row>
@@ -6167,17 +6167,17 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>RETURN_004</t>
+          <t>CASE_007</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>36氪 / 财新网</t>
+          <t>C114通信网</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
@@ -6202,7 +6202,7 @@
       </c>
       <c r="L110" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixin.com/2024-10-28/102250409.html</t>
+          <t>https://www.c114.com.cn/other/241/a1307528.html</t>
         </is>
       </c>
     </row>
@@ -6214,27 +6214,27 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>比亚迪 BYD：Supply Chain Risk</t>
+          <t>比亚迪 BYD：Trade Risk</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>RETURN_002</t>
+          <t>CASE_010</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>新浪科技 / 中关村在线</t>
+          <t>美国白宫（经律所解读）</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G111" s="2" t="n">
@@ -6254,7 +6254,7 @@
       </c>
       <c r="L111" s="2" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/tech/roll/2025-07-03/doc-infeerfp4024842.shtml</t>
+          <t>https://www.alvarezandmarsal.com/node/97806</t>
         </is>
       </c>
     </row>
@@ -6318,22 +6318,22 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>晶科能源 JinkoSolar：Operational Risk</t>
+          <t>晶科能源 JinkoSolar：Market Access Risk</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>RETURN_001</t>
+          <t>CASE_003</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>恩捷股份公告（经东方财富网 / 央广网报道）</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2023-08-18</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr">
@@ -6358,7 +6358,7 @@
       </c>
       <c r="L113" s="2" t="inlineStr">
         <is>
-          <t>https://finance.eastmoney.com/a/202605223746866215.html</t>
+          <t>https://www.internationaltradeinsights.com/2023/08/commerce-issues-final-determination-on-circumvention-of-solar-cells-and-modules-from-cambodia-malaysia-thailand-and-vietnam/</t>
         </is>
       </c>
     </row>
@@ -6370,27 +6370,27 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>晶科能源 JinkoSolar：Operational Risk</t>
+          <t>晶科能源 JinkoSolar：Market Access Risk</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>RETURN_004</t>
+          <t>WH_002</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>36氪 / 财新网</t>
+          <t>美国白宫贸易与制造业政策办公室</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G114" s="2" t="n">
@@ -6410,7 +6410,7 @@
       </c>
       <c r="L114" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixin.com/2024-10-28/102250409.html</t>
+          <t>https://www.whitehouse.gov/wp-content/uploads/2026/08/The-Great-Transshipment-Scam.pdf</t>
         </is>
       </c>
     </row>
@@ -6422,27 +6422,27 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>晶科能源 JinkoSolar：Operational Risk</t>
+          <t>晶科能源 JinkoSolar：Supply Chain Risk</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>RELOC_004</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>新浪财经</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>持续更新</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G115" s="2" t="n">
@@ -6462,7 +6462,7 @@
       </c>
       <c r="L115" s="2" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/roll/2026-02-06/doc-inhkwssf2073873.shtml</t>
+          <t>https://comtradeplus.un.org</t>
         </is>
       </c>
     </row>
@@ -6479,22 +6479,22 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>RETURN_001</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>恩捷股份公告（经东方财富网 / 央广网报道）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>持续更新</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G116" s="2" t="n">
@@ -6514,7 +6514,7 @@
       </c>
       <c r="L116" s="2" t="inlineStr">
         <is>
-          <t>https://finance.eastmoney.com/a/202605223746866215.html</t>
+          <t>https://comtradeplus.un.org</t>
         </is>
       </c>
     </row>
@@ -6526,27 +6526,27 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>晶科能源 JinkoSolar：Supply Chain Risk</t>
+          <t>晶科能源 JinkoSolar：Trade Risk</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>RETURN_004</t>
+          <t>CASE_010</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>36氪 / 财新网</t>
+          <t>美国白宫（经律所解读）</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G117" s="2" t="n">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="L117" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixin.com/2024-10-28/102250409.html</t>
+          <t>https://www.alvarezandmarsal.com/node/97806</t>
         </is>
       </c>
     </row>
@@ -6578,27 +6578,27 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>晶科能源 JinkoSolar：Supply Chain Risk</t>
+          <t>晶科能源 JinkoSolar：Trade Risk</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>TRD_001</t>
+          <t>CASE_003</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>持续更新</t>
+          <t>2023-08-18</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G118" s="2" t="n">
@@ -6618,7 +6618,7 @@
       </c>
       <c r="L118" s="2" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org</t>
+          <t>https://www.internationaltradeinsights.com/2023/08/commerce-issues-final-determination-on-circumvention-of-solar-cells-and-modules-from-cambodia-malaysia-thailand-and-vietnam/</t>
         </is>
       </c>
     </row>
@@ -6630,27 +6630,27 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>晶科能源 JinkoSolar：Supply Chain Risk</t>
+          <t>晶科能源 JinkoSolar：Trade Risk</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>RELOC_004</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>新浪财经</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>持续更新</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G119" s="2" t="n">
@@ -6670,7 +6670,7 @@
       </c>
       <c r="L119" s="2" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/roll/2026-02-06/doc-inhkwssf2073873.shtml</t>
+          <t>https://comtradeplus.un.org</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>CASE_010</t>
+          <t>WH_002</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>美国白宫（经律所解读）</t>
+          <t>美国白宫贸易与制造业政策办公室</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
@@ -6722,7 +6722,7 @@
       </c>
       <c r="L120" s="2" t="inlineStr">
         <is>
-          <t>https://www.alvarezandmarsal.com/node/97806</t>
+          <t>https://www.whitehouse.gov/wp-content/uploads/2026/08/The-Great-Transshipment-Scam.pdf</t>
         </is>
       </c>
     </row>
@@ -6739,7 +6739,7 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>TRD_001</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
@@ -6786,27 +6786,27 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>三星电子 Samsung Electronics：Operational Risk</t>
+          <t>三星电子 Samsung Electronics：Market Access Risk</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>PLUS1_005</t>
+          <t>CASE_010</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>新浪财经 / 东方财富网</t>
+          <t>美国白宫（经律所解读）</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G122" s="2" t="n">
@@ -6826,7 +6826,7 @@
       </c>
       <c r="L122" s="2" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/stock/t/2026-05-27/doc-inhzikrs0845798.shtml</t>
+          <t>https://www.alvarezandmarsal.com/node/97806</t>
         </is>
       </c>
     </row>
@@ -6843,22 +6843,22 @@
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>RETURN_001</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>恩捷股份公告（经东方财富网 / 央广网报道）</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="G123" s="2" t="n">
@@ -6878,7 +6878,7 @@
       </c>
       <c r="L123" s="2" t="inlineStr">
         <is>
-          <t>https://finance.eastmoney.com/a/202605223746866215.html</t>
+          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
         </is>
       </c>
     </row>
@@ -6895,17 +6895,17 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>RETURN_004</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>36氪 / 财新网</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="L124" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixin.com/2024-10-28/102250409.html</t>
+          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
         </is>
       </c>
     </row>
@@ -6942,22 +6942,22 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>三星电子 Samsung Electronics：Operational Risk</t>
+          <t>三星电子 Samsung Electronics：Supply Chain Risk</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>RELOC_005</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>东方财富网 / 腾讯新闻</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr">
@@ -6982,7 +6982,7 @@
       </c>
       <c r="L125" s="2" t="inlineStr">
         <is>
-          <t>https://finance.eastmoney.com/a/202407163131488556.html</t>
+          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
         </is>
       </c>
     </row>
@@ -6994,27 +6994,27 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>三星电子 Samsung Electronics：Operational Risk</t>
+          <t>三星电子 Samsung Electronics：Supply Chain Risk</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>RETURN_002</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>新浪科技 / 中关村在线</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>持续更新</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G126" s="2" t="n">
@@ -7034,7 +7034,7 @@
       </c>
       <c r="L126" s="2" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/tech/roll/2025-07-03/doc-infeerfp4024842.shtml</t>
+          <t>https://comtradeplus.un.org</t>
         </is>
       </c>
     </row>
@@ -7051,17 +7051,17 @@
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>PLUS1_005</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>新浪财经 / 东方财富网</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr">
@@ -7086,7 +7086,7 @@
       </c>
       <c r="L127" s="2" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/stock/t/2026-05-27/doc-inhzikrs0845798.shtml</t>
+          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
         </is>
       </c>
     </row>
@@ -7103,22 +7103,22 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>RETURN_001</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>恩捷股份公告（经东方财富网 / 央广网报道）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>持续更新</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G128" s="2" t="n">
@@ -7138,7 +7138,7 @@
       </c>
       <c r="L128" s="2" t="inlineStr">
         <is>
-          <t>https://finance.eastmoney.com/a/202605223746866215.html</t>
+          <t>https://comtradeplus.un.org</t>
         </is>
       </c>
     </row>
@@ -7150,27 +7150,27 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>三星电子 Samsung Electronics：Supply Chain Risk</t>
+          <t>三星电子 Samsung Electronics：Trade Risk</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>RETURN_004</t>
+          <t>CASE_010</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>36氪 / 财新网</t>
+          <t>美国白宫（经律所解读）</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G129" s="2" t="n">
@@ -7190,7 +7190,7 @@
       </c>
       <c r="L129" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixin.com/2024-10-28/102250409.html</t>
+          <t>https://www.alvarezandmarsal.com/node/97806</t>
         </is>
       </c>
     </row>
@@ -7202,27 +7202,27 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>三星电子 Samsung Electronics：Supply Chain Risk</t>
+          <t>三星电子 Samsung Electronics：Trade Risk</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>RELOC_005</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>东方财富网 / 腾讯新闻</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>持续更新</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G130" s="2" t="n">
@@ -7242,7 +7242,7 @@
       </c>
       <c r="L130" s="2" t="inlineStr">
         <is>
-          <t>https://finance.eastmoney.com/a/202407163131488556.html</t>
+          <t>https://comtradeplus.un.org</t>
         </is>
       </c>
     </row>
@@ -7254,27 +7254,27 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>三星电子 Samsung Electronics：Supply Chain Risk</t>
+          <t>三星电子 Samsung Electronics：Trade Risk</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>RETURN_002</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>新浪科技 / 中关村在线</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>持续更新</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G131" s="2" t="n">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="L131" s="2" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/tech/roll/2025-07-03/doc-infeerfp4024842.shtml</t>
+          <t>https://comtradeplus.un.org</t>
         </is>
       </c>
     </row>
@@ -7306,22 +7306,22 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>恩捷股份 Yunnan Energy New Material (Semcorp)：Operational Risk</t>
+          <t>恩捷股份 Yunnan Energy New Material (Semcorp)：Market Access Risk</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>RETURN_001</t>
+          <t>WH_002</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>恩捷股份公告（经东方财富网 / 央广网报道）</t>
+          <t>美国白宫贸易与制造业政策办公室</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr">
@@ -7346,7 +7346,7 @@
       </c>
       <c r="L132" s="2" t="inlineStr">
         <is>
-          <t>https://finance.eastmoney.com/a/202605223746866215.html</t>
+          <t>https://www.whitehouse.gov/wp-content/uploads/2026/08/The-Great-Transshipment-Scam.pdf</t>
         </is>
       </c>
     </row>
@@ -7363,17 +7363,17 @@
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>RETURN_004</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>36氪 / 财新网</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F133" s="2" t="inlineStr">
@@ -7398,7 +7398,7 @@
       </c>
       <c r="L133" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixin.com/2024-10-28/102250409.html</t>
+          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
         </is>
       </c>
     </row>
@@ -7415,17 +7415,17 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>RETURN_002</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>新浪科技 / 中关村在线</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr">
@@ -7450,7 +7450,7 @@
       </c>
       <c r="L134" s="2" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/tech/roll/2025-07-03/doc-infeerfp4024842.shtml</t>
+          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
         </is>
       </c>
     </row>
@@ -7467,17 +7467,17 @@
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>RETURN_003</t>
+          <t>CASE_004</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>路透社（经环球网 / 新浪转载）</t>
+          <t>国盛证券（经腾讯新闻转载）</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2025-11-30</t>
         </is>
       </c>
       <c r="F135" s="2" t="inlineStr">
@@ -7502,7 +7502,7 @@
       </c>
       <c r="L135" s="2" t="inlineStr">
         <is>
-          <t>https://3w.huanqiu.com/a/de583b/4TE5JD6omnj</t>
+          <t>https://news.qq.com/rain/a/20251130A04A7P00</t>
         </is>
       </c>
     </row>
@@ -7514,22 +7514,22 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>恩捷股份 Yunnan Energy New Material (Semcorp)：Operational Risk</t>
+          <t>恩捷股份 Yunnan Energy New Material (Semcorp)：Supply Chain Risk</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>RELOC_008</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>和讯网 / 网易</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F136" s="2" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="L136" s="2" t="inlineStr">
         <is>
-          <t>https://futures.hexun.com/2024-04-08/212465761.html</t>
+          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
         </is>
       </c>
     </row>
@@ -7571,22 +7571,22 @@
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>RETURN_001</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>恩捷股份公告（经东方财富网 / 央广网报道）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>持续更新</t>
         </is>
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G137" s="2" t="n">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="L137" s="2" t="inlineStr">
         <is>
-          <t>https://finance.eastmoney.com/a/202605223746866215.html</t>
+          <t>https://comtradeplus.un.org</t>
         </is>
       </c>
     </row>
@@ -7623,17 +7623,17 @@
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>RETURN_004</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>36氪 / 财新网</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr">
@@ -7658,7 +7658,7 @@
       </c>
       <c r="L138" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixin.com/2024-10-28/102250409.html</t>
+          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
         </is>
       </c>
     </row>
@@ -7675,17 +7675,17 @@
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>RETURN_002</t>
+          <t>CASE_004</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>新浪科技 / 中关村在线</t>
+          <t>国盛证券（经腾讯新闻转载）</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-11-30</t>
         </is>
       </c>
       <c r="F139" s="2" t="inlineStr">
@@ -7710,7 +7710,7 @@
       </c>
       <c r="L139" s="2" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/tech/roll/2025-07-03/doc-infeerfp4024842.shtml</t>
+          <t>https://news.qq.com/rain/a/20251130A04A7P00</t>
         </is>
       </c>
     </row>
@@ -7722,27 +7722,27 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>恩捷股份 Yunnan Energy New Material (Semcorp)：Supply Chain Risk</t>
+          <t>恩捷股份 Yunnan Energy New Material (Semcorp)：Trade Risk</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>RETURN_003</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>路透社（经环球网 / 新浪转载）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>持续更新</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G140" s="2" t="n">
@@ -7762,7 +7762,7 @@
       </c>
       <c r="L140" s="2" t="inlineStr">
         <is>
-          <t>https://3w.huanqiu.com/a/de583b/4TE5JD6omnj</t>
+          <t>https://comtradeplus.un.org</t>
         </is>
       </c>
     </row>
@@ -7774,27 +7774,27 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>恩捷股份 Yunnan Energy New Material (Semcorp)：Supply Chain Risk</t>
+          <t>恩捷股份 Yunnan Energy New Material (Semcorp)：Trade Risk</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>RELOC_008</t>
+          <t>WH_002</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>和讯网 / 网易</t>
+          <t>美国白宫贸易与制造业政策办公室</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G141" s="2" t="n">
@@ -7814,7 +7814,7 @@
       </c>
       <c r="L141" s="2" t="inlineStr">
         <is>
-          <t>https://futures.hexun.com/2024-04-08/212465761.html</t>
+          <t>https://www.whitehouse.gov/wp-content/uploads/2026/08/The-Great-Transshipment-Scam.pdf</t>
         </is>
       </c>
     </row>
@@ -7826,22 +7826,22 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>富士康 Foxconn / 苹果 Apple（供应链）：Operational Risk</t>
+          <t>富士康 Foxconn / 苹果 Apple（供应链）：Market Access Risk</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>RETURN_001</t>
+          <t>WH_002</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>恩捷股份公告（经东方财富网 / 央广网报道）</t>
+          <t>美国白宫贸易与制造业政策办公室</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr">
@@ -7866,7 +7866,7 @@
       </c>
       <c r="L142" s="2" t="inlineStr">
         <is>
-          <t>https://finance.eastmoney.com/a/202605223746866215.html</t>
+          <t>https://www.whitehouse.gov/wp-content/uploads/2026/08/The-Great-Transshipment-Scam.pdf</t>
         </is>
       </c>
     </row>
@@ -7883,17 +7883,17 @@
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>RETURN_002</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>新浪科技 / 中关村在线</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F143" s="2" t="inlineStr">
@@ -7918,7 +7918,7 @@
       </c>
       <c r="L143" s="2" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/tech/roll/2025-07-03/doc-infeerfp4024842.shtml</t>
+          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
         </is>
       </c>
     </row>
@@ -7935,17 +7935,17 @@
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>RETURN_004</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>36氪 / 财新网</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="F144" s="2" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="L144" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixin.com/2024-10-28/102250409.html</t>
+          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
         </is>
       </c>
     </row>
@@ -7987,17 +7987,17 @@
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>RETURN_003</t>
+          <t>CASE_004</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>路透社（经环球网 / 新浪转载）</t>
+          <t>国盛证券（经腾讯新闻转载）</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2025-11-30</t>
         </is>
       </c>
       <c r="F145" s="2" t="inlineStr">
@@ -8022,7 +8022,7 @@
       </c>
       <c r="L145" s="2" t="inlineStr">
         <is>
-          <t>https://3w.huanqiu.com/a/de583b/4TE5JD6omnj</t>
+          <t>https://news.qq.com/rain/a/20251130A04A7P00</t>
         </is>
       </c>
     </row>
@@ -8034,22 +8034,22 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>富士康 Foxconn / 苹果 Apple（供应链）：Operational Risk</t>
+          <t>富士康 Foxconn / 苹果 Apple（供应链）：Supply Chain Risk</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>RELOC_005</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>东方财富网 / 腾讯新闻</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F146" s="2" t="inlineStr">
@@ -8074,7 +8074,7 @@
       </c>
       <c r="L146" s="2" t="inlineStr">
         <is>
-          <t>https://finance.eastmoney.com/a/202407163131488556.html</t>
+          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
         </is>
       </c>
     </row>
@@ -8091,22 +8091,22 @@
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>RETURN_001</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>恩捷股份公告（经东方财富网 / 央广网报道）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>持续更新</t>
         </is>
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G147" s="2" t="n">
@@ -8126,7 +8126,7 @@
       </c>
       <c r="L147" s="2" t="inlineStr">
         <is>
-          <t>https://finance.eastmoney.com/a/202605223746866215.html</t>
+          <t>https://comtradeplus.un.org</t>
         </is>
       </c>
     </row>
@@ -8143,17 +8143,17 @@
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>RETURN_002</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>新浪科技 / 中关村在线</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="F148" s="2" t="inlineStr">
@@ -8178,7 +8178,7 @@
       </c>
       <c r="L148" s="2" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/tech/roll/2025-07-03/doc-infeerfp4024842.shtml</t>
+          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
         </is>
       </c>
     </row>
@@ -8195,17 +8195,17 @@
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>RETURN_004</t>
+          <t>CASE_004</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>36氪 / 财新网</t>
+          <t>国盛证券（经腾讯新闻转载）</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2025-11-30</t>
         </is>
       </c>
       <c r="F149" s="2" t="inlineStr">
@@ -8230,7 +8230,7 @@
       </c>
       <c r="L149" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixin.com/2024-10-28/102250409.html</t>
+          <t>https://news.qq.com/rain/a/20251130A04A7P00</t>
         </is>
       </c>
     </row>
@@ -8242,27 +8242,27 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>富士康 Foxconn / 苹果 Apple（供应链）：Supply Chain Risk</t>
+          <t>富士康 Foxconn / 苹果 Apple（供应链）：Trade Risk</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>RETURN_003</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>路透社（经环球网 / 新浪转载）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>持续更新</t>
         </is>
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G150" s="2" t="n">
@@ -8282,7 +8282,7 @@
       </c>
       <c r="L150" s="2" t="inlineStr">
         <is>
-          <t>https://3w.huanqiu.com/a/de583b/4TE5JD6omnj</t>
+          <t>https://comtradeplus.un.org</t>
         </is>
       </c>
     </row>
@@ -8294,27 +8294,27 @@
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>富士康 Foxconn / 苹果 Apple（供应链）：Supply Chain Risk</t>
+          <t>富士康 Foxconn / 苹果 Apple（供应链）：Trade Risk</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>RELOC_005</t>
+          <t>WH_002</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>东方财富网 / 腾讯新闻</t>
+          <t>美国白宫贸易与制造业政策办公室</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G151" s="2" t="n">
@@ -8334,7 +8334,7 @@
       </c>
       <c r="L151" s="2" t="inlineStr">
         <is>
-          <t>https://finance.eastmoney.com/a/202407163131488556.html</t>
+          <t>https://www.whitehouse.gov/wp-content/uploads/2026/08/The-Great-Transshipment-Scam.pdf</t>
         </is>
       </c>
     </row>
@@ -8346,22 +8346,22 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>制造业外迁企业（行业层面）：Operational Risk</t>
+          <t>制造业外迁企业（行业层面）：Market Access Risk</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>RETURN_001</t>
+          <t>WH_002</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>恩捷股份公告（经东方财富网 / 央广网报道）</t>
+          <t>美国白宫贸易与制造业政策办公室</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="F152" s="2" t="inlineStr">
@@ -8386,7 +8386,7 @@
       </c>
       <c r="L152" s="2" t="inlineStr">
         <is>
-          <t>https://finance.eastmoney.com/a/202605223746866215.html</t>
+          <t>https://www.whitehouse.gov/wp-content/uploads/2026/08/The-Great-Transshipment-Scam.pdf</t>
         </is>
       </c>
     </row>
@@ -8403,12 +8403,12 @@
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>RETURN_003</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>路透社（经环球网 / 新浪转载）</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
@@ -8438,7 +8438,7 @@
       </c>
       <c r="L153" s="2" t="inlineStr">
         <is>
-          <t>https://3w.huanqiu.com/a/de583b/4TE5JD6omnj</t>
+          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
         </is>
       </c>
     </row>
@@ -8455,17 +8455,17 @@
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>RETURN_004</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>36氪 / 财新网</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="F154" s="2" t="inlineStr">
@@ -8490,7 +8490,7 @@
       </c>
       <c r="L154" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixin.com/2024-10-28/102250409.html</t>
+          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
         </is>
       </c>
     </row>
@@ -8507,17 +8507,17 @@
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>RETURN_002</t>
+          <t>CASE_004</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>新浪科技 / 中关村在线</t>
+          <t>国盛证券（经腾讯新闻转载）</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-11-30</t>
         </is>
       </c>
       <c r="F155" s="2" t="inlineStr">
@@ -8542,7 +8542,7 @@
       </c>
       <c r="L155" s="2" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/tech/roll/2025-07-03/doc-infeerfp4024842.shtml</t>
+          <t>https://news.qq.com/rain/a/20251130A04A7P00</t>
         </is>
       </c>
     </row>
@@ -8554,22 +8554,22 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>制造业外迁企业（行业层面）：Operational Risk</t>
+          <t>制造业外迁企业（行业层面）：Supply Chain Risk</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>PLUS1_002</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>东方财富网（转界面新闻）</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F156" s="2" t="inlineStr">
@@ -8594,7 +8594,7 @@
       </c>
       <c r="L156" s="2" t="inlineStr">
         <is>
-          <t>https://finance.eastmoney.com/a/202507023446498365.html</t>
+          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
         </is>
       </c>
     </row>
@@ -8611,22 +8611,22 @@
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>RETURN_001</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>恩捷股份公告（经东方财富网 / 央广网报道）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>持续更新</t>
         </is>
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G157" s="2" t="n">
@@ -8646,7 +8646,7 @@
       </c>
       <c r="L157" s="2" t="inlineStr">
         <is>
-          <t>https://finance.eastmoney.com/a/202605223746866215.html</t>
+          <t>https://comtradeplus.un.org</t>
         </is>
       </c>
     </row>
@@ -8663,17 +8663,17 @@
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>RETURN_003</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>路透社（经环球网 / 新浪转载）</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="F158" s="2" t="inlineStr">
@@ -8698,7 +8698,7 @@
       </c>
       <c r="L158" s="2" t="inlineStr">
         <is>
-          <t>https://3w.huanqiu.com/a/de583b/4TE5JD6omnj</t>
+          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
         </is>
       </c>
     </row>
@@ -8715,17 +8715,17 @@
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>RETURN_004</t>
+          <t>CASE_004</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>36氪 / 财新网</t>
+          <t>国盛证券（经腾讯新闻转载）</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2025-11-30</t>
         </is>
       </c>
       <c r="F159" s="2" t="inlineStr">
@@ -8750,7 +8750,7 @@
       </c>
       <c r="L159" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixin.com/2024-10-28/102250409.html</t>
+          <t>https://news.qq.com/rain/a/20251130A04A7P00</t>
         </is>
       </c>
     </row>
@@ -8762,27 +8762,27 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>制造业外迁企业（行业层面）：Supply Chain Risk</t>
+          <t>制造业外迁企业（行业层面）：Trade Risk</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>RETURN_002</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>新浪科技 / 中关村在线</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>持续更新</t>
         </is>
       </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G160" s="2" t="n">
@@ -8802,7 +8802,7 @@
       </c>
       <c r="L160" s="2" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/tech/roll/2025-07-03/doc-infeerfp4024842.shtml</t>
+          <t>https://comtradeplus.un.org</t>
         </is>
       </c>
     </row>
@@ -8814,27 +8814,27 @@
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>制造业外迁企业（行业层面）：Supply Chain Risk</t>
+          <t>制造业外迁企业（行业层面）：Trade Risk</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>PLUS1_002</t>
+          <t>WH_002</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>东方财富网（转界面新闻）</t>
+          <t>美国白宫贸易与制造业政策办公室</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G161" s="2" t="n">
@@ -8854,7 +8854,7 @@
       </c>
       <c r="L161" s="2" t="inlineStr">
         <is>
-          <t>https://finance.eastmoney.com/a/202507023446498365.html</t>
+          <t>https://www.whitehouse.gov/wp-content/uploads/2026/08/The-Great-Transshipment-Scam.pdf</t>
         </is>
       </c>
     </row>
@@ -8866,22 +8866,22 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>蜂巢能源 SVOLT（欧洲业务）：Operational Risk</t>
+          <t>蜂巢能源 SVOLT（欧洲业务）：Market Access Risk</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>RETURN_001</t>
+          <t>WH_002</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>恩捷股份公告（经东方财富网 / 央广网报道）</t>
+          <t>美国白宫贸易与制造业政策办公室</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="F162" s="2" t="inlineStr">
@@ -8906,7 +8906,7 @@
       </c>
       <c r="L162" s="2" t="inlineStr">
         <is>
-          <t>https://finance.eastmoney.com/a/202605223746866215.html</t>
+          <t>https://www.whitehouse.gov/wp-content/uploads/2026/08/The-Great-Transshipment-Scam.pdf</t>
         </is>
       </c>
     </row>
@@ -8923,17 +8923,17 @@
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>RETURN_004</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>36氪 / 财新网</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F163" s="2" t="inlineStr">
@@ -8958,7 +8958,7 @@
       </c>
       <c r="L163" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixin.com/2024-10-28/102250409.html</t>
+          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
         </is>
       </c>
     </row>
@@ -8975,17 +8975,17 @@
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>RETURN_002</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>新浪科技 / 中关村在线</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="F164" s="2" t="inlineStr">
@@ -9010,7 +9010,7 @@
       </c>
       <c r="L164" s="2" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/tech/roll/2025-07-03/doc-infeerfp4024842.shtml</t>
+          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
         </is>
       </c>
     </row>
@@ -9027,17 +9027,17 @@
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>RETURN_003</t>
+          <t>CASE_004</t>
         </is>
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>路透社（经环球网 / 新浪转载）</t>
+          <t>国盛证券（经腾讯新闻转载）</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2025-11-30</t>
         </is>
       </c>
       <c r="F165" s="2" t="inlineStr">
@@ -9062,7 +9062,7 @@
       </c>
       <c r="L165" s="2" t="inlineStr">
         <is>
-          <t>https://3w.huanqiu.com/a/de583b/4TE5JD6omnj</t>
+          <t>https://news.qq.com/rain/a/20251130A04A7P00</t>
         </is>
       </c>
     </row>
@@ -9074,22 +9074,22 @@
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>蜂巢能源 SVOLT（欧洲业务）：Operational Risk</t>
+          <t>蜂巢能源 SVOLT（欧洲业务）：Supply Chain Risk</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>RELOC_006</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>澎湃新闻</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>2024-02-28</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F166" s="2" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="L166" s="2" t="inlineStr">
         <is>
-          <t>https://www.thepaper.cn/newsDetail_forward_26493905</t>
+          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
         </is>
       </c>
     </row>
@@ -9131,22 +9131,22 @@
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>RETURN_001</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>恩捷股份公告（经东方财富网 / 央广网报道）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>持续更新</t>
         </is>
       </c>
       <c r="F167" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G167" s="2" t="n">
@@ -9166,7 +9166,7 @@
       </c>
       <c r="L167" s="2" t="inlineStr">
         <is>
-          <t>https://finance.eastmoney.com/a/202605223746866215.html</t>
+          <t>https://comtradeplus.un.org</t>
         </is>
       </c>
     </row>
@@ -9183,17 +9183,17 @@
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>RETURN_004</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>36氪 / 财新网</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="F168" s="2" t="inlineStr">
@@ -9218,7 +9218,7 @@
       </c>
       <c r="L168" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixin.com/2024-10-28/102250409.html</t>
+          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
         </is>
       </c>
     </row>
@@ -9235,17 +9235,17 @@
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>RETURN_002</t>
+          <t>CASE_004</t>
         </is>
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>新浪科技 / 中关村在线</t>
+          <t>国盛证券（经腾讯新闻转载）</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-11-30</t>
         </is>
       </c>
       <c r="F169" s="2" t="inlineStr">
@@ -9270,7 +9270,7 @@
       </c>
       <c r="L169" s="2" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/tech/roll/2025-07-03/doc-infeerfp4024842.shtml</t>
+          <t>https://news.qq.com/rain/a/20251130A04A7P00</t>
         </is>
       </c>
     </row>
@@ -9282,27 +9282,27 @@
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>蜂巢能源 SVOLT（欧洲业务）：Supply Chain Risk</t>
+          <t>蜂巢能源 SVOLT（欧洲业务）：Trade Risk</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>RETURN_003</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>路透社（经环球网 / 新浪转载）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>持续更新</t>
         </is>
       </c>
       <c r="F170" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G170" s="2" t="n">
@@ -9322,7 +9322,7 @@
       </c>
       <c r="L170" s="2" t="inlineStr">
         <is>
-          <t>https://3w.huanqiu.com/a/de583b/4TE5JD6omnj</t>
+          <t>https://comtradeplus.un.org</t>
         </is>
       </c>
     </row>
@@ -9334,27 +9334,27 @@
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>蜂巢能源 SVOLT（欧洲业务）：Supply Chain Risk</t>
+          <t>蜂巢能源 SVOLT（欧洲业务）：Trade Risk</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>RELOC_006</t>
+          <t>WH_002</t>
         </is>
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>澎湃新闻</t>
+          <t>美国白宫贸易与制造业政策办公室</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>2024-02-28</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="F171" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G171" s="2" t="n">
@@ -9374,7 +9374,7 @@
       </c>
       <c r="L171" s="2" t="inlineStr">
         <is>
-          <t>https://www.thepaper.cn/newsDetail_forward_26493905</t>
+          <t>https://www.whitehouse.gov/wp-content/uploads/2026/08/The-Great-Transshipment-Scam.pdf</t>
         </is>
       </c>
     </row>
@@ -9390,7 +9390,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L48"/>
+  <dimension ref="A1:L31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -10704,52 +10704,52 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>PLUS1_001</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>宁德时代 CATL：China + 1 战略（多地区混合布局）</t>
+          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>每日经济新闻 / 搜狐网</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>持续更新</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>EV_Battery</t>
+          <t>Electronics_Manufacturing</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Case Study</t>
+          <t>Trade Data</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Supply Chain Risk; Operational Risk</t>
+          <t>Trade Risk; Supply Chain Risk</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>https://www.nbd.com.cn/articles/2026-09-22/4589059.html</t>
+          <t>https://comtradeplus.un.org</t>
         </is>
       </c>
       <c r="K24" s="2" t="n">
@@ -10760,52 +10760,52 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>PLUS1_002</t>
+          <t>TRD_002</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>宁德时代 CATL：China + 1 战略（多地区混合布局）</t>
+          <t>美国自越南、泰国、马来西亚、柬埔寨进口光伏组件HS 854140，2018–2025年度</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>东方财富网（转界面新闻）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>持续更新</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>EV_Battery</t>
+          <t>Energy_Storage</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Case Study</t>
+          <t>Trade Data</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>Supply Chain Risk; Operational Risk</t>
+          <t>Trade Risk; Supply Chain Risk</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>https://finance.eastmoney.com/a/202507023446498365.html</t>
+          <t>https://comtradeplus.un.org</t>
         </is>
       </c>
       <c r="K25" s="2" t="n">
@@ -10816,52 +10816,52 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>PLUS1_003</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>比亚迪 BYD：China + 1 战略（多地区混合布局）</t>
+          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>凤凰科技（转路透社）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>持续更新</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Electronics_Manufacturing</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Case Study</t>
+          <t>Trade Data</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Supply Chain Risk; Operational Risk</t>
+          <t>Trade Risk; Supply Chain Risk</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>https://otomotif.antaranews.com/berita/5724273/pabrik-byd-di-subang-resmi-beroperasi-dan-serap-5000-pekerja-lokal</t>
+          <t>https://comtradeplus.un.org</t>
         </is>
       </c>
       <c r="K26" s="2" t="n">
@@ -10872,52 +10872,52 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>PLUS1_004</t>
+          <t>UNCTAD_001</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>晶科能源 JinkoSolar：China + 1 战略（多地区混合布局）</t>
+          <t>World Investment Report 2026: International Investment in a Turbulent Era</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>东方财富财富号</t>
+          <t>联合国贸易和发展会议（UNCTAD）</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Energy_Storage</t>
+          <t>EV_Battery</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Case Study</t>
+          <t>Industry Report</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>Supply Chain Risk; Operational Risk</t>
+          <t>Political Risk; Regulatory Risk</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>https://caifuhao.eastmoney.com/news/20260225153639217944650</t>
+          <t>https://unctad.org/publication/world-investment-report-2026</t>
         </is>
       </c>
       <c r="K27" s="2" t="n">
@@ -10928,52 +10928,52 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>PLUS1_005</t>
+          <t>WEF_001</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>三星电子 Samsung Electronics：China + 1 战略（多地区混合布局）</t>
+          <t>Global Risks Report 2026（全球风险报告2026，第21版）</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>新浪财经 / 东方财富网</t>
+          <t>世界经济论坛（WEF）</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Electronics_Manufacturing</t>
+          <t>EV_Battery</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Case Study</t>
+          <t>Industry Report</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Supply Chain Risk; Operational Risk</t>
+          <t>Political Risk; Trade Risk</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>https://finance.sina.com.cn/stock/t/2026-05-27/doc-inhzikrs0845798.shtml</t>
+          <t>https://www.weforum.org/publications/global-risks-report-2026</t>
         </is>
       </c>
       <c r="K28" s="2" t="n">
@@ -10984,22 +10984,22 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>RELOC_001</t>
+          <t>WH_001</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>比亚迪 BYD：中国 → 东南亚转移（多地区混合布局）</t>
+          <t>Executive Order 14411: Strengthening Customs Enforcement（加强海关执法行政令）</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>东方财富网（转比亚迪官方）</t>
+          <t>美国白宫</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2024-07-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -11009,27 +11009,27 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>EV_Battery</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Case Study</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>Supply Chain Risk; Operational Risk</t>
+          <t>Trade Risk; Market Access Risk</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>https://finance.eastmoney.com/a/202407043122188760.html</t>
+          <t>https://www.govinfo.gov/content/pkg/FR-2026-06-10/pdf/2026-11595.pdf</t>
         </is>
       </c>
       <c r="K29" s="2" t="n">
@@ -11040,22 +11040,22 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>RELOC_002</t>
+          <t>WH_002</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>长安汽车 Changan Automobile：中国 → 东南亚转移（多地区混合布局）</t>
+          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告）</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>易车 / 证券之星（投资者互动平台）</t>
+          <t>美国白宫贸易与制造业政策办公室</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -11065,27 +11065,27 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>EV_Battery</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Case Study</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>Supply Chain Risk; Operational Risk</t>
+          <t>Trade Risk; Market Access Risk</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>https://news.yiche.com/hao/wenzhang/100585175/</t>
+          <t>https://www.whitehouse.gov/wp-content/uploads/2026/08/The-Great-Transshipment-Scam.pdf</t>
         </is>
       </c>
       <c r="K30" s="2" t="n">
@@ -11096,27 +11096,27 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>RELOC_003</t>
+          <t>WTO_001</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>国轩高科 Gotion High-Tech：中国 → 东南亚转移（多地区混合布局）</t>
+          <t>Global Trade Outlook and Statistics（2026年3月版）</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>澎湃新闻 / 盖世汽车社区</t>
+          <t>世界贸易组织（WTO）</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>2022-11-19</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -11126,22 +11126,22 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Case Study</t>
+          <t>Industry Report</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>Supply Chain Risk; Operational Risk</t>
+          <t>Trade Risk; Supply Chain Risk</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>https://m.thepaper.cn/newsDetail_forward_20810032</t>
+          <t>https://www.astrid-online.it/static/upload/wto-/wto-global-trade-outlook-2026.pdf</t>
         </is>
       </c>
       <c r="K31" s="2" t="n">
@@ -11149,960 +11149,8 @@
       </c>
       <c r="L31" s="2" t="inlineStr"/>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>RELOC_004</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>亿纬锂能 EVE Energy：中国 → 东南亚转移（多地区混合布局）</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>新浪财经</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>EV_Battery</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>供应链布局</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>Case Study</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>Supply Chain Risk; Operational Risk</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>https://finance.sina.com.cn/roll/2026-02-06/doc-inhkwssf2073873.shtml</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L32" s="2" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>RELOC_005</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>欣旺达 Sunwoda：中国 → 东南亚转移（多地区混合布局）</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>东方财富网 / 腾讯新闻</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>2024-07-16</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>EV_Battery</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>供应链布局</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>Case Study</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>Supply Chain Risk; Operational Risk</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>https://finance.eastmoney.com/a/202407163131488556.html</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L33" s="2" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>RELOC_006</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>蜂巢能源 SVOLT：中国 → 东南亚转移（多地区混合布局）</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>澎湃新闻</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>2024-02-28</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>EV_Battery</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>供应链布局</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>Case Study</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>Supply Chain Risk; Operational Risk</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>https://www.thepaper.cn/newsDetail_forward_26493905</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L34" s="2" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>RELOC_007</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>华友钴业 Huayou Cobalt：中国 → 东南亚转移（多地区混合布局）</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>新浪财经</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>2024-04-12</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>Battery_Materials</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>供应链布局</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>Case Study</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>Supply Chain Risk; Operational Risk</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>https://finance.sina.com.cn/stock/relnews/cn/2024-04-12/doc-inarqawt9056004.shtml</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L35" s="2" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>RELOC_008</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>中伟股份 CNGR Advanced Material：中国 → 东南亚转移（多地区混合布局）</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>和讯网 / 网易</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>2024-04-08</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>Battery_Materials</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>供应链布局</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>Case Study</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>Supply Chain Risk; Operational Risk</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>https://futures.hexun.com/2024-04-08/212465761.html</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L36" s="2" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>RETURN_001</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>恩捷股份 Yunnan Energy New Material (Semcorp)：重新评估 / 回流中国（提高中国生产比例）</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>恩捷股份公告（经东方财富网 / 央广网报道）</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>Battery_Materials</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>供应链布局</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>Case Study</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>Supply Chain Risk; Operational Risk</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>https://finance.eastmoney.com/a/202605223746866215.html</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L37" s="2" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>RETURN_002</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>富士康 Foxconn / 苹果 Apple（供应链）：重新评估 / 回流中国（提高中国生产比例）</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>新浪科技 / 中关村在线</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>2025-07-03</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>Electronics_Manufacturing</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>供应链布局</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>Case Study</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>Supply Chain Risk; Operational Risk</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>https://finance.sina.com.cn/tech/roll/2025-07-03/doc-infeerfp4024842.shtml</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L38" s="2" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>RETURN_003</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>制造业外迁企业（行业层面）：重新评估 / 回流中国（提高中国生产比例）</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>路透社（经环球网 / 新浪转载）</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>General_Manufacturing</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>供应链布局</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>Case Study</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>Supply Chain Risk; Operational Risk</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>https://3w.huanqiu.com/a/de583b/4TE5JD6omnj</t>
-        </is>
-      </c>
-      <c r="K39" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L39" s="2" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>RETURN_004</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>蜂巢能源 SVOLT（欧洲业务）：重新评估 / 回流中国（维持现有海外布局（收缩新增））</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>36氪 / 财新网</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>2024-10-28</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>EV_Battery</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>供应链布局</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>Case Study</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>Supply Chain Risk; Operational Risk</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>https://www.caixin.com/2024-10-28/102250409.html</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L40" s="2" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>TRD_001</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>持续更新</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>Electronics_Manufacturing</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>贸易流</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>Trade Data</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>Trade Risk; Supply Chain Risk</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>https://comtradeplus.un.org</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L41" s="2" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>TRD_002</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>美国自越南、泰国、马来西亚、柬埔寨进口光伏组件HS 854140，2018–2025年度</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>持续更新</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>Energy_Storage</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>贸易流</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>Trade Data</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>Trade Risk; Supply Chain Risk</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>https://comtradeplus.un.org</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L42" s="2" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>TRD_003</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>持续更新</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>Electronics_Manufacturing</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>贸易流</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>Trade Data</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>Trade Risk; Supply Chain Risk</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>https://comtradeplus.un.org</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L43" s="2" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>UNCTAD_001</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>World Investment Report 2026: International Investment in a Turbulent Era</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>联合国贸易和发展会议（UNCTAD）</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>EV_Battery</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>对外投资</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>Industry Report</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>Political Risk; Regulatory Risk</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>https://unctad.org/publication/world-investment-report-2026</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L44" s="2" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>WEF_001</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>Global Risks Report 2026（全球风险报告2026，第21版）</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>世界经济论坛（WEF）</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>2026-01-14</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>EV_Battery</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>宏观风险</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>Industry Report</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>Political Risk; Trade Risk</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>https://www.weforum.org/publications/global-risks-report-2026</t>
-        </is>
-      </c>
-      <c r="K45" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L45" s="2" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>WH_001</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>Executive Order 14411: Strengthening Customs Enforcement（加强海关执法行政令）</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>美国白宫</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>EV_Battery</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>原产地与转运</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>Policy</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>Trade Risk; Market Access Risk</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>https://www.govinfo.gov/content/pkg/FR-2026-06-10/pdf/2026-11595.pdf</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L46" s="2" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>WH_002</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告）</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>美国白宫贸易与制造业政策办公室</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>EV_Battery</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>原产地与转运</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>Policy</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>Trade Risk; Market Access Risk</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>https://www.whitehouse.gov/wp-content/uploads/2026/08/The-Great-Transshipment-Scam.pdf</t>
-        </is>
-      </c>
-      <c r="K47" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L47" s="2" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>WTO_001</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>Global Trade Outlook and Statistics（2026年3月版）</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>世界贸易组织（WTO）</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>EV_Battery</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>贸易流</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>Industry Report</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>Trade Risk; Supply Chain Risk</t>
-        </is>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>https://www.astrid-online.it/static/upload/wto-/wto-global-trade-outlook-2026.pdf</t>
-        </is>
-      </c>
-      <c r="K48" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L48" s="2" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:L48"/>
+  <autoFilter ref="A1:L31"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -15487,7 +14535,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>

--- a/data/evaluation/evidence_quality_test.xlsx
+++ b/data/evaluation/evidence_quality_test.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Citation Test'!$A$1:$L$171</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Corpus Citation Coverage'!$A$1:$L$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Corpus Citation Coverage'!$A$1:$L$37</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Conclusion Audit'!$A$1:$H$86</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -551,17 +551,17 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>MOFCOM_001</t>
+          <t>EU_003</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>商务部、海关总署</t>
+          <t>欧盟委员会（EUR-Lex / Official Journal）</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -586,7 +586,7 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>https://www.mofcom.gov.cn/zwgk/zcfb/art/2025/art_c03d1e511b2b486e829d68e8f1422aff.html</t>
+          <t>https://eur-lex.europa.eu/legal-content/EN/TXT/?uri=CELEX%3A32024R2754</t>
         </is>
       </c>
     </row>
@@ -702,27 +702,27 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>比亚迪 BYD：Regulatory Risk</t>
+          <t>比亚迪 BYD：Supply Chain Risk</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>MOFCOM_001</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>商务部、海关总署</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>持续更新</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G5" s="2" t="n">
@@ -742,7 +742,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>https://www.mofcom.gov.cn/zwgk/zcfb/art/2025/art_c03d1e511b2b486e829d68e8f1422aff.html</t>
+          <t>https://comtradeplus.un.org</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>TRD_001</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -811,22 +811,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>CASE_004</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>国盛证券（经腾讯新闻转载）</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>持续更新</t>
+          <t>2025-11-30</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="G7" s="2" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org</t>
+          <t>https://news.qq.com/rain/a/20251130A04A7P00</t>
         </is>
       </c>
     </row>
@@ -863,17 +863,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>CASE_004</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>国盛证券（经腾讯新闻转载）</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>https://news.qq.com/rain/a/20251130A04A7P00</t>
+          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
         </is>
       </c>
     </row>
@@ -910,27 +910,27 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>比亚迪 BYD：Supply Chain Risk</t>
+          <t>比亚迪 BYD：Trade Risk</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>持续更新</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
@@ -950,7 +950,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
+          <t>https://comtradeplus.un.org</t>
         </is>
       </c>
     </row>
@@ -967,22 +967,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>TRD_001</t>
+          <t>EU_003</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>欧盟委员会（EUR-Lex / Official Journal）</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>持续更新</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G10" s="2" t="n">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org</t>
+          <t>https://eur-lex.europa.eu/legal-content/EN/TXT/?uri=CELEX%3A32024R2754</t>
         </is>
       </c>
     </row>
@@ -1066,27 +1066,27 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>长安汽车 Changan Automobile：Market Access Risk</t>
+          <t>长安汽车 Changan Automobile：Operational Risk</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>MOFCOM_001</t>
+          <t>CASE_004</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>商务部、海关总署</t>
+          <t>国盛证券（经腾讯新闻转载）</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2025-11-30</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="G12" s="2" t="n">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>https://www.mofcom.gov.cn/zwgk/zcfb/art/2025/art_c03d1e511b2b486e829d68e8f1422aff.html</t>
+          <t>https://news.qq.com/rain/a/20251130A04A7P00</t>
         </is>
       </c>
     </row>
@@ -1123,17 +1123,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>CASE_004</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>国盛证券（经腾讯新闻转载）</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1158,7 +1158,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>https://news.qq.com/rain/a/20251130A04A7P00</t>
+          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
         </is>
       </c>
     </row>
@@ -1175,17 +1175,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1210,7 +1210,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
+          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
         </is>
       </c>
     </row>
@@ -1222,27 +1222,27 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>长安汽车 Changan Automobile：Regulatory Risk</t>
+          <t>长安汽车 Changan Automobile：Supply Chain Risk</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>MOFCOM_001</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>商务部、海关总署</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>持续更新</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G15" s="2" t="n">
@@ -1262,7 +1262,7 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>https://www.mofcom.gov.cn/zwgk/zcfb/art/2025/art_c03d1e511b2b486e829d68e8f1422aff.html</t>
+          <t>https://comtradeplus.un.org</t>
         </is>
       </c>
     </row>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>TRD_001</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1331,22 +1331,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>CASE_004</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>国盛证券（经腾讯新闻转载）</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>持续更新</t>
+          <t>2025-11-30</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="G17" s="2" t="n">
@@ -1366,7 +1366,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org</t>
+          <t>https://news.qq.com/rain/a/20251130A04A7P00</t>
         </is>
       </c>
     </row>
@@ -1383,17 +1383,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>CASE_004</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>国盛证券（经腾讯新闻转载）</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>https://news.qq.com/rain/a/20251130A04A7P00</t>
+          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
         </is>
       </c>
     </row>
@@ -1435,17 +1435,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
+          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
         </is>
       </c>
     </row>
@@ -1586,27 +1586,27 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>国轩高科 Gotion High-Tech：Market Access Risk</t>
+          <t>国轩高科 Gotion High-Tech：Operational Risk</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>MOFCOM_001</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>商务部、海关总署</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="G22" s="2" t="n">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>https://www.mofcom.gov.cn/zwgk/zcfb/art/2025/art_c03d1e511b2b486e829d68e8f1422aff.html</t>
+          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
         </is>
       </c>
     </row>
@@ -1643,17 +1643,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
+          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
         </is>
       </c>
     </row>
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>CASE_008</t>
+          <t>CASE_004</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>中国基金报</t>
+          <t>国盛证券（经腾讯新闻转载）</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2024-07-14</t>
+          <t>2025-11-30</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
+          <t>https://news.qq.com/rain/a/20251130A04A7P00</t>
         </is>
       </c>
     </row>
@@ -1742,27 +1742,27 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>国轩高科 Gotion High-Tech：Regulatory Risk</t>
+          <t>国轩高科 Gotion High-Tech：Supply Chain Risk</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>MOFCOM_001</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>商务部、海关总署</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>持续更新</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G25" s="2" t="n">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>https://www.mofcom.gov.cn/zwgk/zcfb/art/2025/art_c03d1e511b2b486e829d68e8f1422aff.html</t>
+          <t>https://comtradeplus.un.org</t>
         </is>
       </c>
     </row>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>TRD_001</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1851,22 +1851,22 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>持续更新</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="G27" s="2" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org</t>
+          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
         </is>
       </c>
     </row>
@@ -1903,17 +1903,17 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
+          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
         </is>
       </c>
     </row>
@@ -1955,17 +1955,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>CASE_008</t>
+          <t>CASE_004</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>中国基金报</t>
+          <t>国盛证券（经腾讯新闻转载）</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2024-07-14</t>
+          <t>2025-11-30</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -1990,7 +1990,7 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
+          <t>https://news.qq.com/rain/a/20251130A04A7P00</t>
         </is>
       </c>
     </row>
@@ -2106,27 +2106,27 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>亿纬锂能 EVE Energy：Market Access Risk</t>
+          <t>亿纬锂能 EVE Energy：Operational Risk</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>MOFCOM_001</t>
+          <t>CASE_007</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>商务部、海关总署</t>
+          <t>C114通信网</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="G32" s="2" t="n">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>https://www.mofcom.gov.cn/zwgk/zcfb/art/2025/art_c03d1e511b2b486e829d68e8f1422aff.html</t>
+          <t>https://www.c114.com.cn/other/241/a1307528.html</t>
         </is>
       </c>
     </row>
@@ -2163,17 +2163,17 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>CASE_007</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>C114通信网</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -2198,7 +2198,7 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>https://www.c114.com.cn/other/241/a1307528.html</t>
+          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
         </is>
       </c>
     </row>
@@ -2215,17 +2215,17 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
+          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
         </is>
       </c>
     </row>
@@ -2262,27 +2262,27 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>亿纬锂能 EVE Energy：Regulatory Risk</t>
+          <t>亿纬锂能 EVE Energy：Supply Chain Risk</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>MOFCOM_001</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>商务部、海关总署</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>持续更新</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G35" s="2" t="n">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>https://www.mofcom.gov.cn/zwgk/zcfb/art/2025/art_c03d1e511b2b486e829d68e8f1422aff.html</t>
+          <t>https://comtradeplus.un.org</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>TRD_001</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -2371,22 +2371,22 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>CASE_007</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>C114通信网</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>持续更新</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="G37" s="2" t="n">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org</t>
+          <t>https://www.c114.com.cn/other/241/a1307528.html</t>
         </is>
       </c>
     </row>
@@ -2423,17 +2423,17 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>CASE_007</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>C114通信网</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2458,7 +2458,7 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>https://www.c114.com.cn/other/241/a1307528.html</t>
+          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
         </is>
       </c>
     </row>
@@ -2475,17 +2475,17 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
+          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
         </is>
       </c>
     </row>
@@ -2626,27 +2626,27 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>欣旺达 Sunwoda：Market Access Risk</t>
+          <t>欣旺达 Sunwoda：Operational Risk</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>MOFCOM_001</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>商务部、海关总署</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="G42" s="2" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>https://www.mofcom.gov.cn/zwgk/zcfb/art/2025/art_c03d1e511b2b486e829d68e8f1422aff.html</t>
+          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
         </is>
       </c>
     </row>
@@ -2683,17 +2683,17 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
+          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
         </is>
       </c>
     </row>
@@ -2735,17 +2735,17 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>CASE_008</t>
+          <t>CASE_004</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>中国基金报</t>
+          <t>国盛证券（经腾讯新闻转载）</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>2024-07-14</t>
+          <t>2025-11-30</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -2770,7 +2770,7 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
+          <t>https://news.qq.com/rain/a/20251130A04A7P00</t>
         </is>
       </c>
     </row>
@@ -2782,27 +2782,27 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>欣旺达 Sunwoda：Regulatory Risk</t>
+          <t>欣旺达 Sunwoda：Supply Chain Risk</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>MOFCOM_001</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>商务部、海关总署</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>持续更新</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G45" s="2" t="n">
@@ -2822,7 +2822,7 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>https://www.mofcom.gov.cn/zwgk/zcfb/art/2025/art_c03d1e511b2b486e829d68e8f1422aff.html</t>
+          <t>https://comtradeplus.un.org</t>
         </is>
       </c>
     </row>
@@ -2839,7 +2839,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>TRD_001</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -2891,22 +2891,22 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>持续更新</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="G47" s="2" t="n">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org</t>
+          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
         </is>
       </c>
     </row>
@@ -2943,17 +2943,17 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -2978,7 +2978,7 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
+          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
         </is>
       </c>
     </row>
@@ -2995,17 +2995,17 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>CASE_008</t>
+          <t>CASE_004</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>中国基金报</t>
+          <t>国盛证券（经腾讯新闻转载）</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>2024-07-14</t>
+          <t>2025-11-30</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
+          <t>https://news.qq.com/rain/a/20251130A04A7P00</t>
         </is>
       </c>
     </row>
@@ -3146,27 +3146,27 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>蜂巢能源 SVOLT：Market Access Risk</t>
+          <t>蜂巢能源 SVOLT：Operational Risk</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>MOFCOM_001</t>
+          <t>CASE_004</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>商务部、海关总署</t>
+          <t>国盛证券（经腾讯新闻转载）</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2025-11-30</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="G52" s="2" t="n">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>https://www.mofcom.gov.cn/zwgk/zcfb/art/2025/art_c03d1e511b2b486e829d68e8f1422aff.html</t>
+          <t>https://news.qq.com/rain/a/20251130A04A7P00</t>
         </is>
       </c>
     </row>
@@ -3203,17 +3203,17 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>CASE_004</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>国盛证券（经腾讯新闻转载）</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -3238,7 +3238,7 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>https://news.qq.com/rain/a/20251130A04A7P00</t>
+          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
         </is>
       </c>
     </row>
@@ -3255,17 +3255,17 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
+          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
         </is>
       </c>
     </row>
@@ -3302,27 +3302,27 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>蜂巢能源 SVOLT：Regulatory Risk</t>
+          <t>蜂巢能源 SVOLT：Supply Chain Risk</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>MOFCOM_001</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>商务部、海关总署</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>持续更新</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G55" s="2" t="n">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>https://www.mofcom.gov.cn/zwgk/zcfb/art/2025/art_c03d1e511b2b486e829d68e8f1422aff.html</t>
+          <t>https://comtradeplus.un.org</t>
         </is>
       </c>
     </row>
@@ -3359,7 +3359,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>TRD_001</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -3411,22 +3411,22 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>CASE_004</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>国盛证券（经腾讯新闻转载）</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>持续更新</t>
+          <t>2025-11-30</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="G57" s="2" t="n">
@@ -3446,7 +3446,7 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org</t>
+          <t>https://news.qq.com/rain/a/20251130A04A7P00</t>
         </is>
       </c>
     </row>
@@ -3463,17 +3463,17 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>CASE_004</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>国盛证券（经腾讯新闻转载）</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>https://news.qq.com/rain/a/20251130A04A7P00</t>
+          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
         </is>
       </c>
     </row>
@@ -3515,17 +3515,17 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
+          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
         </is>
       </c>
     </row>
@@ -3666,27 +3666,27 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>华友钴业 Huayou Cobalt：Market Access Risk</t>
+          <t>华友钴业 Huayou Cobalt：Operational Risk</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>MOFCOM_001</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>商务部、海关总署</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="G62" s="2" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>https://www.mofcom.gov.cn/zwgk/zcfb/art/2025/art_c03d1e511b2b486e829d68e8f1422aff.html</t>
+          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
         </is>
       </c>
     </row>
@@ -3775,17 +3775,17 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>CASE_008</t>
+          <t>CASE_004</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>中国基金报</t>
+          <t>国盛证券（经腾讯新闻转载）</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>2024-07-14</t>
+          <t>2025-11-30</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -3810,7 +3810,7 @@
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
+          <t>https://news.qq.com/rain/a/20251130A04A7P00</t>
         </is>
       </c>
     </row>
@@ -3822,27 +3822,27 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>华友钴业 Huayou Cobalt：Regulatory Risk</t>
+          <t>华友钴业 Huayou Cobalt：Supply Chain Risk</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>MOFCOM_001</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>商务部、海关总署</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>持续更新</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G65" s="2" t="n">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>https://www.mofcom.gov.cn/zwgk/zcfb/art/2025/art_c03d1e511b2b486e829d68e8f1422aff.html</t>
+          <t>https://comtradeplus.un.org</t>
         </is>
       </c>
     </row>
@@ -3879,22 +3879,22 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>TRD_001</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>持续更新</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="G66" s="2" t="n">
@@ -3914,7 +3914,7 @@
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org</t>
+          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
         </is>
       </c>
     </row>
@@ -3931,22 +3931,22 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>持续更新</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="G67" s="2" t="n">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org</t>
+          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
         </is>
       </c>
     </row>
@@ -3983,22 +3983,22 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>持续更新</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G68" s="2" t="n">
@@ -4018,7 +4018,7 @@
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
+          <t>https://comtradeplus.un.org</t>
         </is>
       </c>
     </row>
@@ -4035,17 +4035,17 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>CASE_008</t>
+          <t>CASE_004</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>中国基金报</t>
+          <t>国盛证券（经腾讯新闻转载）</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>2024-07-14</t>
+          <t>2025-11-30</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
+          <t>https://news.qq.com/rain/a/20251130A04A7P00</t>
         </is>
       </c>
     </row>
@@ -4186,27 +4186,27 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>中伟股份 CNGR Advanced Material：Market Access Risk</t>
+          <t>中伟股份 CNGR Advanced Material：Operational Risk</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>MOFCOM_001</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>商务部、海关总署</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="G72" s="2" t="n">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>https://www.mofcom.gov.cn/zwgk/zcfb/art/2025/art_c03d1e511b2b486e829d68e8f1422aff.html</t>
+          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
         </is>
       </c>
     </row>
@@ -4243,17 +4243,17 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -4278,7 +4278,7 @@
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
+          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
         </is>
       </c>
     </row>
@@ -4295,17 +4295,17 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>CASE_008</t>
+          <t>CASE_004</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>中国基金报</t>
+          <t>国盛证券（经腾讯新闻转载）</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>2024-07-14</t>
+          <t>2025-11-30</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -4330,7 +4330,7 @@
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
+          <t>https://news.qq.com/rain/a/20251130A04A7P00</t>
         </is>
       </c>
     </row>
@@ -4342,27 +4342,27 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>中伟股份 CNGR Advanced Material：Regulatory Risk</t>
+          <t>中伟股份 CNGR Advanced Material：Supply Chain Risk</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>MOFCOM_001</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>商务部、海关总署</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>持续更新</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G75" s="2" t="n">
@@ -4382,7 +4382,7 @@
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>https://www.mofcom.gov.cn/zwgk/zcfb/art/2025/art_c03d1e511b2b486e829d68e8f1422aff.html</t>
+          <t>https://comtradeplus.un.org</t>
         </is>
       </c>
     </row>
@@ -4399,22 +4399,22 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>TRD_001</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>持续更新</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="G76" s="2" t="n">
@@ -4434,7 +4434,7 @@
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org</t>
+          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
         </is>
       </c>
     </row>
@@ -4451,22 +4451,22 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>持续更新</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="G77" s="2" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org</t>
+          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
         </is>
       </c>
     </row>
@@ -4503,22 +4503,22 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>持续更新</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G78" s="2" t="n">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
+          <t>https://comtradeplus.un.org</t>
         </is>
       </c>
     </row>
@@ -4555,17 +4555,17 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>CASE_008</t>
+          <t>CASE_004</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>中国基金报</t>
+          <t>国盛证券（经腾讯新闻转载）</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>2024-07-14</t>
+          <t>2025-11-30</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -4590,7 +4590,7 @@
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
+          <t>https://news.qq.com/rain/a/20251130A04A7P00</t>
         </is>
       </c>
     </row>
@@ -5283,17 +5283,17 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
@@ -5318,7 +5318,7 @@
       </c>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
+          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
         </is>
       </c>
     </row>
@@ -5335,17 +5335,17 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>CASE_008</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>中国基金报</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>2024-07-14</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
@@ -5370,7 +5370,7 @@
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
+          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
         </is>
       </c>
     </row>
@@ -5491,17 +5491,17 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
+          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
         </is>
       </c>
     </row>
@@ -5543,17 +5543,17 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>CASE_008</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>中国基金报</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>2024-07-14</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
@@ -5578,7 +5578,7 @@
       </c>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
+          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
         </is>
       </c>
     </row>
@@ -6422,27 +6422,27 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>晶科能源 JinkoSolar：Supply Chain Risk</t>
+          <t>晶科能源 JinkoSolar：Operational Risk</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>TRD_001</t>
+          <t>CASE_007</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>C114通信网</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>持续更新</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="G115" s="2" t="n">
@@ -6462,7 +6462,7 @@
       </c>
       <c r="L115" s="2" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org</t>
+          <t>https://www.c114.com.cn/other/241/a1307528.html</t>
         </is>
       </c>
     </row>
@@ -6479,7 +6479,7 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
@@ -6526,27 +6526,27 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>晶科能源 JinkoSolar：Trade Risk</t>
+          <t>晶科能源 JinkoSolar：Supply Chain Risk</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>CASE_010</t>
+          <t>CASE_007</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>美国白宫（经律所解读）</t>
+          <t>C114通信网</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="G117" s="2" t="n">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="L117" s="2" t="inlineStr">
         <is>
-          <t>https://www.alvarezandmarsal.com/node/97806</t>
+          <t>https://www.c114.com.cn/other/241/a1307528.html</t>
         </is>
       </c>
     </row>
@@ -6583,17 +6583,17 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>CASE_003</t>
+          <t>CASE_010</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>美国白宫（经律所解读）</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>2023-08-18</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr">
@@ -6618,7 +6618,7 @@
       </c>
       <c r="L118" s="2" t="inlineStr">
         <is>
-          <t>https://www.internationaltradeinsights.com/2023/08/commerce-issues-final-determination-on-circumvention-of-solar-cells-and-modules-from-cambodia-malaysia-thailand-and-vietnam/</t>
+          <t>https://www.alvarezandmarsal.com/node/97806</t>
         </is>
       </c>
     </row>
@@ -6635,22 +6635,22 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>TRD_001</t>
+          <t>CASE_003</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>持续更新</t>
+          <t>2023-08-18</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G119" s="2" t="n">
@@ -6670,7 +6670,7 @@
       </c>
       <c r="L119" s="2" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org</t>
+          <t>https://www.internationaltradeinsights.com/2023/08/commerce-issues-final-determination-on-circumvention-of-solar-cells-and-modules-from-cambodia-malaysia-thailand-and-vietnam/</t>
         </is>
       </c>
     </row>
@@ -6687,22 +6687,22 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>WH_002</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>美国白宫贸易与制造业政策办公室</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>持续更新</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G120" s="2" t="n">
@@ -6722,7 +6722,7 @@
       </c>
       <c r="L120" s="2" t="inlineStr">
         <is>
-          <t>https://www.whitehouse.gov/wp-content/uploads/2026/08/The-Great-Transshipment-Scam.pdf</t>
+          <t>https://comtradeplus.un.org</t>
         </is>
       </c>
     </row>
@@ -6739,22 +6739,22 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>WH_002</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>美国白宫贸易与制造业政策办公室</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>持续更新</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G121" s="2" t="n">
@@ -6774,7 +6774,7 @@
       </c>
       <c r="L121" s="2" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org</t>
+          <t>https://www.whitehouse.gov/wp-content/uploads/2026/08/The-Great-Transshipment-Scam.pdf</t>
         </is>
       </c>
     </row>
@@ -6838,27 +6838,27 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>三星电子 Samsung Electronics：Operational Risk</t>
+          <t>三星电子 Samsung Electronics：Market Access Risk</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>CASE_003</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2023-08-18</t>
         </is>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G123" s="2" t="n">
@@ -6878,7 +6878,7 @@
       </c>
       <c r="L123" s="2" t="inlineStr">
         <is>
-          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
+          <t>https://www.internationaltradeinsights.com/2023/08/commerce-issues-final-determination-on-circumvention-of-solar-cells-and-modules-from-cambodia-malaysia-thailand-and-vietnam/</t>
         </is>
       </c>
     </row>
@@ -6895,17 +6895,17 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>CASE_008</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>中国基金报</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>2024-07-14</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="L124" s="2" t="inlineStr">
         <is>
-          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
+          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
         </is>
       </c>
     </row>
@@ -6942,22 +6942,22 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>三星电子 Samsung Electronics：Supply Chain Risk</t>
+          <t>三星电子 Samsung Electronics：Operational Risk</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr">
@@ -6982,7 +6982,7 @@
       </c>
       <c r="L125" s="2" t="inlineStr">
         <is>
-          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
+          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
         </is>
       </c>
     </row>
@@ -6994,27 +6994,27 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>三星电子 Samsung Electronics：Supply Chain Risk</t>
+          <t>三星电子 Samsung Electronics：Operational Risk</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>CASE_004</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>国盛证券（经腾讯新闻转载）</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>持续更新</t>
+          <t>2025-11-30</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="G126" s="2" t="n">
@@ -7034,7 +7034,7 @@
       </c>
       <c r="L126" s="2" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org</t>
+          <t>https://news.qq.com/rain/a/20251130A04A7P00</t>
         </is>
       </c>
     </row>
@@ -7051,17 +7051,17 @@
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>CASE_008</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>中国基金报</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>2024-07-14</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr">
@@ -7086,7 +7086,7 @@
       </c>
       <c r="L127" s="2" t="inlineStr">
         <is>
-          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
+          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
         </is>
       </c>
     </row>
@@ -7103,22 +7103,22 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>TRD_001</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>持续更新</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="G128" s="2" t="n">
@@ -7138,7 +7138,7 @@
       </c>
       <c r="L128" s="2" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org</t>
+          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
         </is>
       </c>
     </row>
@@ -7150,27 +7150,27 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>三星电子 Samsung Electronics：Trade Risk</t>
+          <t>三星电子 Samsung Electronics：Supply Chain Risk</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>CASE_010</t>
+          <t>CASE_004</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>美国白宫（经律所解读）</t>
+          <t>国盛证券（经腾讯新闻转载）</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2025-11-30</t>
         </is>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="G129" s="2" t="n">
@@ -7190,7 +7190,7 @@
       </c>
       <c r="L129" s="2" t="inlineStr">
         <is>
-          <t>https://www.alvarezandmarsal.com/node/97806</t>
+          <t>https://news.qq.com/rain/a/20251130A04A7P00</t>
         </is>
       </c>
     </row>
@@ -7207,22 +7207,22 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>CASE_010</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>美国白宫（经律所解读）</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>持续更新</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G130" s="2" t="n">
@@ -7242,7 +7242,7 @@
       </c>
       <c r="L130" s="2" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org</t>
+          <t>https://www.alvarezandmarsal.com/node/97806</t>
         </is>
       </c>
     </row>
@@ -7259,22 +7259,22 @@
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>TRD_001</t>
+          <t>CASE_003</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>持续更新</t>
+          <t>2023-08-18</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G131" s="2" t="n">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="L131" s="2" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org</t>
+          <t>https://www.internationaltradeinsights.com/2023/08/commerce-issues-final-determination-on-circumvention-of-solar-cells-and-modules-from-cambodia-malaysia-thailand-and-vietnam/</t>
         </is>
       </c>
     </row>
@@ -7311,17 +7311,17 @@
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>WH_002</t>
+          <t>EU_003</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>美国白宫贸易与制造业政策办公室</t>
+          <t>欧盟委员会（EUR-Lex / Official Journal）</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr">
@@ -7346,7 +7346,7 @@
       </c>
       <c r="L132" s="2" t="inlineStr">
         <is>
-          <t>https://www.whitehouse.gov/wp-content/uploads/2026/08/The-Great-Transshipment-Scam.pdf</t>
+          <t>https://eur-lex.europa.eu/legal-content/EN/TXT/?uri=CELEX%3A32024R2754</t>
         </is>
       </c>
     </row>
@@ -7571,22 +7571,22 @@
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>持续更新</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="G137" s="2" t="n">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="L137" s="2" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org</t>
+          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
         </is>
       </c>
     </row>
@@ -7623,17 +7623,17 @@
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>CASE_008</t>
+          <t>CASE_004</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>中国基金报</t>
+          <t>国盛证券（经腾讯新闻转载）</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>2024-07-14</t>
+          <t>2025-11-30</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr">
@@ -7658,7 +7658,7 @@
       </c>
       <c r="L138" s="2" t="inlineStr">
         <is>
-          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
+          <t>https://news.qq.com/rain/a/20251130A04A7P00</t>
         </is>
       </c>
     </row>
@@ -7675,22 +7675,22 @@
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>CASE_004</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>国盛证券（经腾讯新闻转载）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
+          <t>持续更新</t>
         </is>
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G139" s="2" t="n">
@@ -7710,7 +7710,7 @@
       </c>
       <c r="L139" s="2" t="inlineStr">
         <is>
-          <t>https://news.qq.com/rain/a/20251130A04A7P00</t>
+          <t>https://comtradeplus.un.org</t>
         </is>
       </c>
     </row>
@@ -7727,22 +7727,22 @@
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>EU_003</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>欧盟委员会（EUR-Lex / Official Journal）</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>持续更新</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G140" s="2" t="n">
@@ -7762,7 +7762,7 @@
       </c>
       <c r="L140" s="2" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org</t>
+          <t>https://eur-lex.europa.eu/legal-content/EN/TXT/?uri=CELEX%3A32024R2754</t>
         </is>
       </c>
     </row>
@@ -7779,22 +7779,22 @@
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>WH_002</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>美国白宫贸易与制造业政策办公室</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>持续更新</t>
         </is>
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G141" s="2" t="n">
@@ -7814,7 +7814,7 @@
       </c>
       <c r="L141" s="2" t="inlineStr">
         <is>
-          <t>https://www.whitehouse.gov/wp-content/uploads/2026/08/The-Great-Transshipment-Scam.pdf</t>
+          <t>https://comtradeplus.un.org</t>
         </is>
       </c>
     </row>
@@ -7831,17 +7831,17 @@
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>WH_002</t>
+          <t>EU_003</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>美国白宫贸易与制造业政策办公室</t>
+          <t>欧盟委员会（EUR-Lex / Official Journal）</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr">
@@ -7866,7 +7866,7 @@
       </c>
       <c r="L142" s="2" t="inlineStr">
         <is>
-          <t>https://www.whitehouse.gov/wp-content/uploads/2026/08/The-Great-Transshipment-Scam.pdf</t>
+          <t>https://eur-lex.europa.eu/legal-content/EN/TXT/?uri=CELEX%3A32024R2754</t>
         </is>
       </c>
     </row>
@@ -8091,22 +8091,22 @@
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>持续更新</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="G147" s="2" t="n">
@@ -8126,7 +8126,7 @@
       </c>
       <c r="L147" s="2" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org</t>
+          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
         </is>
       </c>
     </row>
@@ -8143,17 +8143,17 @@
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>CASE_008</t>
+          <t>CASE_004</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>中国基金报</t>
+          <t>国盛证券（经腾讯新闻转载）</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>2024-07-14</t>
+          <t>2025-11-30</t>
         </is>
       </c>
       <c r="F148" s="2" t="inlineStr">
@@ -8178,7 +8178,7 @@
       </c>
       <c r="L148" s="2" t="inlineStr">
         <is>
-          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
+          <t>https://news.qq.com/rain/a/20251130A04A7P00</t>
         </is>
       </c>
     </row>
@@ -8195,22 +8195,22 @@
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>CASE_004</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>国盛证券（经腾讯新闻转载）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
+          <t>持续更新</t>
         </is>
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G149" s="2" t="n">
@@ -8230,7 +8230,7 @@
       </c>
       <c r="L149" s="2" t="inlineStr">
         <is>
-          <t>https://news.qq.com/rain/a/20251130A04A7P00</t>
+          <t>https://comtradeplus.un.org</t>
         </is>
       </c>
     </row>
@@ -8247,22 +8247,22 @@
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>EU_003</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>欧盟委员会（EUR-Lex / Official Journal）</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>持续更新</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G150" s="2" t="n">
@@ -8282,7 +8282,7 @@
       </c>
       <c r="L150" s="2" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org</t>
+          <t>https://eur-lex.europa.eu/legal-content/EN/TXT/?uri=CELEX%3A32024R2754</t>
         </is>
       </c>
     </row>
@@ -8299,22 +8299,22 @@
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>WH_002</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>美国白宫贸易与制造业政策办公室</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>持续更新</t>
         </is>
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G151" s="2" t="n">
@@ -8334,7 +8334,7 @@
       </c>
       <c r="L151" s="2" t="inlineStr">
         <is>
-          <t>https://www.whitehouse.gov/wp-content/uploads/2026/08/The-Great-Transshipment-Scam.pdf</t>
+          <t>https://comtradeplus.un.org</t>
         </is>
       </c>
     </row>
@@ -8351,17 +8351,17 @@
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>WH_002</t>
+          <t>EU_003</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>美国白宫贸易与制造业政策办公室</t>
+          <t>欧盟委员会（EUR-Lex / Official Journal）</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="F152" s="2" t="inlineStr">
@@ -8386,7 +8386,7 @@
       </c>
       <c r="L152" s="2" t="inlineStr">
         <is>
-          <t>https://www.whitehouse.gov/wp-content/uploads/2026/08/The-Great-Transshipment-Scam.pdf</t>
+          <t>https://eur-lex.europa.eu/legal-content/EN/TXT/?uri=CELEX%3A32024R2754</t>
         </is>
       </c>
     </row>
@@ -8554,22 +8554,22 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>制造业外迁企业（行业层面）：Supply Chain Risk</t>
+          <t>制造业外迁企业（行业层面）：Operational Risk</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>CASE_007</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>C114通信网</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="F156" s="2" t="inlineStr">
@@ -8594,7 +8594,7 @@
       </c>
       <c r="L156" s="2" t="inlineStr">
         <is>
-          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
+          <t>https://www.c114.com.cn/other/241/a1307528.html</t>
         </is>
       </c>
     </row>
@@ -8611,22 +8611,22 @@
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>持续更新</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="G157" s="2" t="n">
@@ -8646,7 +8646,7 @@
       </c>
       <c r="L157" s="2" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org</t>
+          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
         </is>
       </c>
     </row>
@@ -8762,27 +8762,27 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>制造业外迁企业（行业层面）：Trade Risk</t>
+          <t>制造业外迁企业（行业层面）：Supply Chain Risk</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>CASE_007</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>C114通信网</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>持续更新</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="G160" s="2" t="n">
@@ -8802,7 +8802,7 @@
       </c>
       <c r="L160" s="2" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org</t>
+          <t>https://www.c114.com.cn/other/241/a1307528.html</t>
         </is>
       </c>
     </row>
@@ -8819,17 +8819,17 @@
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>WH_002</t>
+          <t>EU_003</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>美国白宫贸易与制造业政策办公室</t>
+          <t>欧盟委员会（EUR-Lex / Official Journal）</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="F161" s="2" t="inlineStr">
@@ -8854,7 +8854,7 @@
       </c>
       <c r="L161" s="2" t="inlineStr">
         <is>
-          <t>https://www.whitehouse.gov/wp-content/uploads/2026/08/The-Great-Transshipment-Scam.pdf</t>
+          <t>https://eur-lex.europa.eu/legal-content/EN/TXT/?uri=CELEX%3A32024R2754</t>
         </is>
       </c>
     </row>
@@ -8871,17 +8871,17 @@
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>WH_002</t>
+          <t>EU_003</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>美国白宫贸易与制造业政策办公室</t>
+          <t>欧盟委员会（EUR-Lex / Official Journal）</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="F162" s="2" t="inlineStr">
@@ -8906,7 +8906,7 @@
       </c>
       <c r="L162" s="2" t="inlineStr">
         <is>
-          <t>https://www.whitehouse.gov/wp-content/uploads/2026/08/The-Great-Transshipment-Scam.pdf</t>
+          <t>https://eur-lex.europa.eu/legal-content/EN/TXT/?uri=CELEX%3A32024R2754</t>
         </is>
       </c>
     </row>
@@ -9131,22 +9131,22 @@
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>持续更新</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="F167" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="G167" s="2" t="n">
@@ -9166,7 +9166,7 @@
       </c>
       <c r="L167" s="2" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org</t>
+          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
         </is>
       </c>
     </row>
@@ -9183,17 +9183,17 @@
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>CASE_008</t>
+          <t>CASE_004</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>中国基金报</t>
+          <t>国盛证券（经腾讯新闻转载）</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>2024-07-14</t>
+          <t>2025-11-30</t>
         </is>
       </c>
       <c r="F168" s="2" t="inlineStr">
@@ -9218,7 +9218,7 @@
       </c>
       <c r="L168" s="2" t="inlineStr">
         <is>
-          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
+          <t>https://news.qq.com/rain/a/20251130A04A7P00</t>
         </is>
       </c>
     </row>
@@ -9235,22 +9235,22 @@
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>CASE_004</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>国盛证券（经腾讯新闻转载）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
+          <t>持续更新</t>
         </is>
       </c>
       <c r="F169" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G169" s="2" t="n">
@@ -9270,7 +9270,7 @@
       </c>
       <c r="L169" s="2" t="inlineStr">
         <is>
-          <t>https://news.qq.com/rain/a/20251130A04A7P00</t>
+          <t>https://comtradeplus.un.org</t>
         </is>
       </c>
     </row>
@@ -9287,22 +9287,22 @@
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>EU_003</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>欧盟委员会（EUR-Lex / Official Journal）</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>持续更新</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="F170" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G170" s="2" t="n">
@@ -9322,7 +9322,7 @@
       </c>
       <c r="L170" s="2" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org</t>
+          <t>https://eur-lex.europa.eu/legal-content/EN/TXT/?uri=CELEX%3A32024R2754</t>
         </is>
       </c>
     </row>
@@ -9339,22 +9339,22 @@
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>WH_002</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>美国白宫贸易与制造业政策办公室</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>持续更新</t>
         </is>
       </c>
       <c r="F171" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G171" s="2" t="n">
@@ -9374,7 +9374,7 @@
       </c>
       <c r="L171" s="2" t="inlineStr">
         <is>
-          <t>https://www.whitehouse.gov/wp-content/uploads/2026/08/The-Great-Transshipment-Scam.pdf</t>
+          <t>https://comtradeplus.un.org</t>
         </is>
       </c>
     </row>
@@ -9390,7 +9390,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:L37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -10312,22 +10312,22 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>FR_001</t>
+          <t>EU_001</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Federal Register API（美国联邦公报）</t>
+          <t>Regulation (EU) 2023/1542 concerning batteries and waste batteries（欧盟电池与废电池法规）</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>美国国家档案馆联邦公报办公室</t>
+          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>持续更新（每日）</t>
+          <t>2023-07-28</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -10342,7 +10342,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>出口管制/关税</t>
+          <t>市场准入</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -10352,12 +10352,12 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Regulatory Risk; Trade Risk; Market Access Risk</t>
+          <t>Regulatory Risk; Market Access Risk</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>https://www.federalregister.gov</t>
+          <t>https://eur-lex.europa.eu/legal-content/EN/TXT/?uri=CELEX%3A32023R1542</t>
         </is>
       </c>
       <c r="K17" s="2" t="n">
@@ -10368,27 +10368,27 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>IMF_001</t>
+          <t>EU_002</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>World Economic Outlook, April 2023, Chapter 4: Geoeconomic Fragmentation and Foreign Direct Investment</t>
+          <t>Regulation (EU) 2024/1252 establishing a framework for ensuring a secure and sustainable supply of critical raw materials（欧盟关键原材料法案 CRMA）</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>国际货币基金组织（IMF）</t>
+          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2023-04</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -10398,22 +10398,22 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>本地化政策</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Industry Report</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Political Risk; Regulatory Risk</t>
+          <t>Market Access Risk; Supply Chain Risk; Political Risk</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>https://www.imf.org/-/media/files/publications/weo/2023/april/english/ch4.pdf</t>
+          <t>https://eur-lex.europa.eu/legal-content/EN/TXT/?uri=CELEX%3A32024R1252</t>
         </is>
       </c>
       <c r="K18" s="2" t="n">
@@ -10424,22 +10424,22 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>ITA_001</t>
+          <t>EU_003</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Consolidated Screening List API（美国合并筛查清单）</t>
+          <t>Commission Implementing Regulation (EU) 2024/2754 imposing a definitive countervailing duty on imports of new battery electric vehicles originating in China（对华纯电动车最终反补贴税）</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>美国国际贸易管理局（ITA）</t>
+          <t>欧盟委员会（EUR-Lex / Official Journal）</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>持续更新（每日）</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -10454,7 +10454,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>出口管制</t>
+          <t>关税</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -10464,12 +10464,12 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>Regulatory Risk; Market Access Risk</t>
+          <t>Trade Risk; Market Access Risk</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>https://www.trade.gov/consolidated-screening-list</t>
+          <t>https://eur-lex.europa.eu/legal-content/EN/TXT/?uri=CELEX%3A32024R2754</t>
         </is>
       </c>
       <c r="K19" s="2" t="n">
@@ -10480,27 +10480,27 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>KPMG_001</t>
+          <t>EU_004</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>KPMG 2026 US Supply Chain Survey</t>
+          <t>Regulation (EU) 2019/452 establishing a framework for the screening of foreign direct investments into the Union（欧盟外资安全审查框架条例）</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>毕马威（KPMG）</t>
+          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2019-03-21</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -10510,22 +10510,22 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Industry Report</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Supply Chain Risk; Operational Risk</t>
+          <t>Political Risk; Regulatory Risk</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>https://kpmg.com/us/en/articles/2026/2026-supply-chain-survey.html</t>
+          <t>https://eur-lex.europa.eu/legal-content/EN/TXT/?uri=CELEX%3A32019R0452</t>
         </is>
       </c>
       <c r="K20" s="2" t="n">
@@ -10536,27 +10536,27 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>MCK_001</t>
+          <t>FR_001</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>The art, science, and technology of geopolitical scenario planning</t>
+          <t>Federal Register API（美国联邦公报）</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>麦肯锡（McKinsey）</t>
+          <t>美国国家档案馆联邦公报办公室</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>持续更新（每日）</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -10566,22 +10566,22 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>出口管制/关税</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Industry Report</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>Political Risk; Trade Risk</t>
+          <t>Regulatory Risk; Trade Risk; Market Access Risk</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>https://www.mckinsey.com/capabilities/geopolitics/our-insights/the-art-science-and-technology-of-geopolitical-scenario-planning</t>
+          <t>https://www.federalregister.gov</t>
         </is>
       </c>
       <c r="K21" s="2" t="n">
@@ -10592,27 +10592,27 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>MOFCOM_001</t>
+          <t>IMF_001</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>2026年度《两用物项和技术进出口许可证管理目录》</t>
+          <t>World Economic Outlook, April 2023, Chapter 4: Geoeconomic Fragmentation and Foreign Direct Investment</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>商务部、海关总署</t>
+          <t>国际货币基金组织（IMF）</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2023-04</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -10622,22 +10622,22 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>出口管制</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Industry Report</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Regulatory Risk; Market Access Risk</t>
+          <t>Political Risk; Regulatory Risk</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>https://www.mofcom.gov.cn/zwgk/zcfb/art/2025/art_c03d1e511b2b486e829d68e8f1422aff.html</t>
+          <t>https://www.imf.org/-/media/files/publications/weo/2023/april/english/ch4.pdf</t>
         </is>
       </c>
       <c r="K22" s="2" t="n">
@@ -10648,22 +10648,22 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>MOFCOM_002</t>
+          <t>IRS_001</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制）</t>
+          <t>Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则）</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>商务部</t>
+          <t>美国财政部/国税局（Federal Register）</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -10678,7 +10678,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>出口管制</t>
+          <t>本地化政策</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -10688,12 +10688,12 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>Regulatory Risk; Market Access Risk</t>
+          <t>Market Access Risk; Supply Chain Risk; Political Risk</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>https://www.mofcom.gov.cn/zwgk/zcfb/art/2025/art_5c68985a6b1a46778e2e8dbff1bb1601.html</t>
+          <t>https://www.federalregister.gov/documents/2024/05/06/2024-09094/clean-vehicle-credits-under-sections-25e-and-30d-transfer-of-credits-critical-minerals-and-battery</t>
         </is>
       </c>
       <c r="K23" s="2" t="n">
@@ -10704,52 +10704,52 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>TRD_001</t>
+          <t>ITA_001</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度</t>
+          <t>Consolidated Screening List API（美国合并筛查清单）</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>美国国际贸易管理局（ITA）</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>持续更新</t>
+          <t>持续更新（每日）</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Electronics_Manufacturing</t>
+          <t>EV_Battery</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>出口管制</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Trade Data</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Trade Risk; Supply Chain Risk</t>
+          <t>Regulatory Risk; Market Access Risk</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org</t>
+          <t>https://www.trade.gov/consolidated-screening-list</t>
         </is>
       </c>
       <c r="K24" s="2" t="n">
@@ -10760,52 +10760,52 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>TRD_002</t>
+          <t>KPMG_001</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>美国自越南、泰国、马来西亚、柬埔寨进口光伏组件HS 854140，2018–2025年度</t>
+          <t>KPMG 2026 US Supply Chain Survey</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>毕马威（KPMG）</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>持续更新</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Energy_Storage</t>
+          <t>EV_Battery</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>供应链布局</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Trade Data</t>
+          <t>Industry Report</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>Trade Risk; Supply Chain Risk</t>
+          <t>Supply Chain Risk; Operational Risk</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org</t>
+          <t>https://kpmg.com/us/en/articles/2026/2026-supply-chain-survey.html</t>
         </is>
       </c>
       <c r="K25" s="2" t="n">
@@ -10816,52 +10816,52 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>MCK_001</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度</t>
+          <t>The art, science, and technology of geopolitical scenario planning</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>麦肯锡（McKinsey）</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>持续更新</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Electronics_Manufacturing</t>
+          <t>EV_Battery</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Trade Data</t>
+          <t>Industry Report</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Trade Risk; Supply Chain Risk</t>
+          <t>Political Risk; Trade Risk</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org</t>
+          <t>https://www.mckinsey.com/capabilities/geopolitics/our-insights/the-art-science-and-technology-of-geopolitical-scenario-planning</t>
         </is>
       </c>
       <c r="K26" s="2" t="n">
@@ -10872,27 +10872,27 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>MOFCOM_001</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>World Investment Report 2026: International Investment in a Turbulent Era</t>
+          <t>2026年度《两用物项和技术进出口许可证管理目录》</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>联合国贸易和发展会议（UNCTAD）</t>
+          <t>商务部、海关总署</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -10902,22 +10902,22 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>出口管制</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Industry Report</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>Political Risk; Regulatory Risk</t>
+          <t>Regulatory Risk; Market Access Risk</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>https://unctad.org/publication/world-investment-report-2026</t>
+          <t>https://www.mofcom.gov.cn/zwgk/zcfb/art/2025/art_c03d1e511b2b486e829d68e8f1422aff.html</t>
         </is>
       </c>
       <c r="K27" s="2" t="n">
@@ -10928,27 +10928,27 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>MOFCOM_002</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Global Risks Report 2026（全球风险报告2026，第21版）</t>
+          <t>商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制）</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>世界经济论坛（WEF）</t>
+          <t>商务部</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -10958,22 +10958,22 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>出口管制</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Industry Report</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Political Risk; Trade Risk</t>
+          <t>Regulatory Risk; Market Access Risk</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>https://www.weforum.org/publications/global-risks-report-2026</t>
+          <t>https://www.mofcom.gov.cn/zwgk/zcfb/art/2025/art_5c68985a6b1a46778e2e8dbff1bb1601.html</t>
         </is>
       </c>
       <c r="K28" s="2" t="n">
@@ -10984,52 +10984,52 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>WH_001</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Executive Order 14411: Strengthening Customs Enforcement（加强海关执法行政令）</t>
+          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>美国白宫</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>持续更新</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>EV_Battery</t>
+          <t>Electronics_Manufacturing</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Trade Data</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>Trade Risk; Market Access Risk</t>
+          <t>Trade Risk; Supply Chain Risk</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>https://www.govinfo.gov/content/pkg/FR-2026-06-10/pdf/2026-11595.pdf</t>
+          <t>https://comtradeplus.un.org</t>
         </is>
       </c>
       <c r="K29" s="2" t="n">
@@ -11040,52 +11040,52 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>WH_002</t>
+          <t>TRD_002</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告）</t>
+          <t>美国自越南、泰国、马来西亚、柬埔寨进口光伏组件HS 854140，2018–2025年度</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>美国白宫贸易与制造业政策办公室</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>持续更新</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>EV_Battery</t>
+          <t>Energy_Storage</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Trade Data</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>Trade Risk; Market Access Risk</t>
+          <t>Trade Risk; Supply Chain Risk</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>https://www.whitehouse.gov/wp-content/uploads/2026/08/The-Great-Transshipment-Scam.pdf</t>
+          <t>https://comtradeplus.un.org</t>
         </is>
       </c>
       <c r="K30" s="2" t="n">
@@ -11096,61 +11096,397 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>TRD_003</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>持续更新</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Electronics_Manufacturing</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>贸易流</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>Trade Data</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>Trade Risk; Supply Chain Risk</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>https://comtradeplus.un.org</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>UNCTAD_001</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>World Investment Report 2026: International Investment in a Turbulent Era</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>联合国贸易和发展会议（UNCTAD）</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>EV_Battery</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>Industry Report</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>Political Risk; Regulatory Risk</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>https://unctad.org/publication/world-investment-report-2026</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>UST_001</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Notice of Modification: China's Acts, Policies and Practices Related to Technology Transfer, Intellectual Property and Innovation（Section 301 对华关税调整通知）</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>美国贸易代表办公室（USTR，Federal Register）</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>EV_Battery</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>关税</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>Policy</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>Trade Risk; Market Access Risk</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.federalregister.gov/documents/2024/09/18/2024-21217/notice-of-modification-chinas-acts-policies-and-practices-related-to-technology-transfer</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>WEF_001</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Global Risks Report 2026（全球风险报告2026，第21版）</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>世界经济论坛（WEF）</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>EV_Battery</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>宏观风险</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>Industry Report</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>Political Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.weforum.org/publications/global-risks-report-2026</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>WH_001</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Executive Order 14411: Strengthening Customs Enforcement（加强海关执法行政令）</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>美国白宫</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>EV_Battery</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>原产地与转运</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>Policy</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>Trade Risk; Market Access Risk</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.govinfo.gov/content/pkg/FR-2026-06-10/pdf/2026-11595.pdf</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>WH_002</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告）</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>美国白宫贸易与制造业政策办公室</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>EV_Battery</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>原产地与转运</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>Policy</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>Trade Risk; Market Access Risk</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.whitehouse.gov/wp-content/uploads/2026/08/The-Great-Transshipment-Scam.pdf</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
           <t>WTO_001</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>Global Trade Outlook and Statistics（2026年3月版）</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
         <is>
           <t>世界贸易组织（WTO）</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>A+</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>EV_Battery</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr">
         <is>
           <t>贸易流</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>Industry Report</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
+      <c r="I37" s="2" t="inlineStr">
         <is>
           <t>Trade Risk; Supply Chain Risk</t>
         </is>
       </c>
-      <c r="J31" s="2" t="inlineStr">
+      <c r="J37" s="2" t="inlineStr">
         <is>
           <t>https://www.astrid-online.it/static/upload/wto-/wto-global-trade-outlook-2026.pdf</t>
         </is>
       </c>
-      <c r="K31" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L31" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L37" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L31"/>
+  <autoFilter ref="A1:L37"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -14535,7 +14871,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>

--- a/data/evaluation/evidence_quality_test.xlsx
+++ b/data/evaluation/evidence_quality_test.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Citation Test'!$A$1:$L$171</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Corpus Citation Coverage'!$A$1:$L$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Corpus Citation Coverage'!$A$1:$L$50</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Conclusion Audit'!$A$1:$H$86</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -603,22 +603,22 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>CASE_004</t>
+          <t>SNE_001</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>国盛证券（经腾讯新闻转载）</t>
+          <t>SNE Research</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G3" s="2" t="n">
@@ -638,7 +638,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>https://news.qq.com/rain/a/20251130A04A7P00</t>
+          <t>https://www.sneresearch.com/en/insight/release_view/744/page/0</t>
         </is>
       </c>
     </row>
@@ -655,17 +655,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>CASE_004</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>国盛证券（经腾讯新闻转载）</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2025-11-30</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
+          <t>https://news.qq.com/rain/a/20251130A04A7P00</t>
         </is>
       </c>
     </row>
@@ -707,22 +707,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>TRD_001</t>
+          <t>SNE_001</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>SNE Research</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>持续更新</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G5" s="2" t="n">
@@ -742,7 +742,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org</t>
+          <t>https://www.sneresearch.com/en/insight/release_view/744/page/0</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -811,22 +811,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>CASE_004</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>国盛证券（经腾讯新闻转载）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
+          <t>持续更新</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G7" s="2" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>https://news.qq.com/rain/a/20251130A04A7P00</t>
+          <t>https://comtradeplus.un.org</t>
         </is>
       </c>
     </row>
@@ -863,17 +863,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>CASE_004</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>国盛证券（经腾讯新闻转载）</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2025-11-30</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
+          <t>https://news.qq.com/rain/a/20251130A04A7P00</t>
         </is>
       </c>
     </row>
@@ -1591,22 +1591,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>WB_001</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>世界银行（World Bank）</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2023-04-28</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G22" s="2" t="n">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
+          <t>https://documents.worldbank.org/curated/en/099042123145531599/pdf/P17146804a6a570ac0a4f80895e320dda1e.pdf</t>
         </is>
       </c>
     </row>
@@ -1643,17 +1643,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>CASE_008</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>中国基金报</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2024-07-14</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
+          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
         </is>
       </c>
     </row>
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>CASE_004</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>国盛证券（经腾讯新闻转载）</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>https://news.qq.com/rain/a/20251130A04A7P00</t>
+          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
         </is>
       </c>
     </row>
@@ -1851,22 +1851,22 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>WB_001</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>世界银行（World Bank）</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2023-04-28</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G27" s="2" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
+          <t>https://documents.worldbank.org/curated/en/099042123145531599/pdf/P17146804a6a570ac0a4f80895e320dda1e.pdf</t>
         </is>
       </c>
     </row>
@@ -1903,17 +1903,17 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>CASE_008</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>中国基金报</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2024-07-14</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
+          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
         </is>
       </c>
     </row>
@@ -1955,17 +1955,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>CASE_004</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>国盛证券（经腾讯新闻转载）</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -1990,7 +1990,7 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>https://news.qq.com/rain/a/20251130A04A7P00</t>
+          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
         </is>
       </c>
     </row>
@@ -2163,22 +2163,22 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>WB_001</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>世界银行（World Bank）</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2023-04-28</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G33" s="2" t="n">
@@ -2198,7 +2198,7 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
+          <t>https://documents.worldbank.org/curated/en/099042123145531599/pdf/P17146804a6a570ac0a4f80895e320dda1e.pdf</t>
         </is>
       </c>
     </row>
@@ -2215,22 +2215,22 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>CASE_008</t>
+          <t>DHS_001</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>中国基金报</t>
+          <t>美国国土安全部（DHS，Federal Register）</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2024-07-14</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G34" s="2" t="n">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
+          <t>https://www.federalregister.gov/documents/2026/08/03/2026-15628/notice-regarding-the-uyghur-forced-labor-prevention-act-entity-list</t>
         </is>
       </c>
     </row>
@@ -2262,27 +2262,27 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>亿纬锂能 EVE Energy：Supply Chain Risk</t>
+          <t>亿纬锂能 EVE Energy：Regulatory Risk</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>TRD_001</t>
+          <t>DHS_001</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>美国国土安全部（DHS，Federal Register）</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>持续更新</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G35" s="2" t="n">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org</t>
+          <t>https://www.federalregister.gov/documents/2026/08/03/2026-15628/notice-regarding-the-uyghur-forced-labor-prevention-act-entity-list</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -2371,22 +2371,22 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>CASE_007</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>C114通信网</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>持续更新</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G37" s="2" t="n">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>https://www.c114.com.cn/other/241/a1307528.html</t>
+          <t>https://comtradeplus.un.org</t>
         </is>
       </c>
     </row>
@@ -2423,17 +2423,17 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>CASE_007</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>C114通信网</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2458,7 +2458,7 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
+          <t>https://www.c114.com.cn/other/241/a1307528.html</t>
         </is>
       </c>
     </row>
@@ -2475,22 +2475,22 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>CASE_008</t>
+          <t>WB_001</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>中国基金报</t>
+          <t>世界银行（World Bank）</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>2024-07-14</t>
+          <t>2023-04-28</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G39" s="2" t="n">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
+          <t>https://documents.worldbank.org/curated/en/099042123145531599/pdf/P17146804a6a570ac0a4f80895e320dda1e.pdf</t>
         </is>
       </c>
     </row>
@@ -2631,22 +2631,22 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>WB_001</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>世界银行（World Bank）</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2023-04-28</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G42" s="2" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
+          <t>https://documents.worldbank.org/curated/en/099042123145531599/pdf/P17146804a6a570ac0a4f80895e320dda1e.pdf</t>
         </is>
       </c>
     </row>
@@ -2683,17 +2683,17 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>CASE_008</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>中国基金报</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>2024-07-14</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
+          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
         </is>
       </c>
     </row>
@@ -2735,17 +2735,17 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>CASE_004</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>国盛证券（经腾讯新闻转载）</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -2770,7 +2770,7 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>https://news.qq.com/rain/a/20251130A04A7P00</t>
+          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
         </is>
       </c>
     </row>
@@ -2891,22 +2891,22 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>WB_001</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>世界银行（World Bank）</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2023-04-28</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G47" s="2" t="n">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
+          <t>https://documents.worldbank.org/curated/en/099042123145531599/pdf/P17146804a6a570ac0a4f80895e320dda1e.pdf</t>
         </is>
       </c>
     </row>
@@ -2943,17 +2943,17 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>CASE_008</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>中国基金报</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>2024-07-14</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -2978,7 +2978,7 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
+          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
         </is>
       </c>
     </row>
@@ -2995,17 +2995,17 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>CASE_004</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>国盛证券（经腾讯新闻转载）</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>https://news.qq.com/rain/a/20251130A04A7P00</t>
+          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
         </is>
       </c>
     </row>
@@ -3671,22 +3671,22 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>CASE_008</t>
+          <t>WB_001</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>中国基金报</t>
+          <t>世界银行（World Bank）</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>2024-07-14</t>
+          <t>2023-04-28</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G62" s="2" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
+          <t>https://documents.worldbank.org/curated/en/099042123145531599/pdf/P17146804a6a570ac0a4f80895e320dda1e.pdf</t>
         </is>
       </c>
     </row>
@@ -3775,17 +3775,17 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>CASE_004</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>国盛证券（经腾讯新闻转载）</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -3810,7 +3810,7 @@
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>https://news.qq.com/rain/a/20251130A04A7P00</t>
+          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
         </is>
       </c>
     </row>
@@ -3879,22 +3879,22 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>CASE_008</t>
+          <t>WB_001</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>中国基金报</t>
+          <t>世界银行（World Bank）</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>2024-07-14</t>
+          <t>2023-04-28</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G66" s="2" t="n">
@@ -3914,7 +3914,7 @@
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
+          <t>https://documents.worldbank.org/curated/en/099042123145531599/pdf/P17146804a6a570ac0a4f80895e320dda1e.pdf</t>
         </is>
       </c>
     </row>
@@ -4035,17 +4035,17 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>CASE_004</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>国盛证券（经腾讯新闻转载）</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>https://news.qq.com/rain/a/20251130A04A7P00</t>
+          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
         </is>
       </c>
     </row>
@@ -4191,22 +4191,22 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>WB_001</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>世界银行（World Bank）</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2023-04-28</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G72" s="2" t="n">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
+          <t>https://documents.worldbank.org/curated/en/099042123145531599/pdf/P17146804a6a570ac0a4f80895e320dda1e.pdf</t>
         </is>
       </c>
     </row>
@@ -4243,17 +4243,17 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>CASE_008</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>中国基金报</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>2024-07-14</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -4278,7 +4278,7 @@
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
+          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
         </is>
       </c>
     </row>
@@ -4295,17 +4295,17 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>CASE_004</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>国盛证券（经腾讯新闻转载）</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -4330,7 +4330,7 @@
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>https://news.qq.com/rain/a/20251130A04A7P00</t>
+          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
         </is>
       </c>
     </row>
@@ -4399,22 +4399,22 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>WB_001</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>世界银行（World Bank）</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2023-04-28</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G76" s="2" t="n">
@@ -4434,7 +4434,7 @@
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
+          <t>https://documents.worldbank.org/curated/en/099042123145531599/pdf/P17146804a6a570ac0a4f80895e320dda1e.pdf</t>
         </is>
       </c>
     </row>
@@ -4451,17 +4451,17 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>CASE_008</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>中国基金报</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>2024-07-14</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
+          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
         </is>
       </c>
     </row>
@@ -4555,17 +4555,17 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>CASE_004</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>国盛证券（经腾讯新闻转载）</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -4590,7 +4590,7 @@
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>https://news.qq.com/rain/a/20251130A04A7P00</t>
+          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
         </is>
       </c>
     </row>
@@ -4763,22 +4763,22 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>CASE_008</t>
+          <t>SNE_001</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>中国基金报</t>
+          <t>SNE Research</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>2024-07-14</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G83" s="2" t="n">
@@ -4798,7 +4798,7 @@
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
+          <t>https://www.sneresearch.com/en/insight/release_view/744/page/0</t>
         </is>
       </c>
     </row>
@@ -4867,17 +4867,17 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>CASE_004</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>国盛证券（经腾讯新闻转载）</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -4902,7 +4902,7 @@
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>https://news.qq.com/rain/a/20251130A04A7P00</t>
+          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
         </is>
       </c>
     </row>
@@ -4919,22 +4919,22 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>CASE_007</t>
+          <t>TSLA_001</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>C114通信网</t>
+          <t>特斯拉公司（Tesla, Inc.，SEC EDGAR）</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G86" s="2" t="n">
@@ -4954,7 +4954,7 @@
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>https://www.c114.com.cn/other/241/a1307528.html</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1318605/000162828026003952/tsla-20251231.htm</t>
         </is>
       </c>
     </row>
@@ -4971,22 +4971,22 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>CASE_008</t>
+          <t>SNE_001</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>中国基金报</t>
+          <t>SNE Research</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>2024-07-14</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G87" s="2" t="n">
@@ -5006,7 +5006,7 @@
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
+          <t>https://www.sneresearch.com/en/insight/release_view/744/page/0</t>
         </is>
       </c>
     </row>
@@ -5075,17 +5075,17 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>CASE_004</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>国盛证券（经腾讯新闻转载）</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
@@ -5110,7 +5110,7 @@
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>https://news.qq.com/rain/a/20251130A04A7P00</t>
+          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
         </is>
       </c>
     </row>
@@ -5127,22 +5127,22 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>CASE_007</t>
+          <t>TSLA_001</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>C114通信网</t>
+          <t>特斯拉公司（Tesla, Inc.，SEC EDGAR）</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G90" s="2" t="n">
@@ -5162,7 +5162,7 @@
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>https://www.c114.com.cn/other/241/a1307528.html</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1318605/000162828026003952/tsla-20251231.htm</t>
         </is>
       </c>
     </row>
@@ -5283,22 +5283,22 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>CASE_008</t>
+          <t>SNE_001</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>中国基金报</t>
+          <t>SNE Research</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>2024-07-14</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G93" s="2" t="n">
@@ -5318,7 +5318,7 @@
       </c>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
+          <t>https://www.sneresearch.com/en/insight/release_view/744/page/0</t>
         </is>
       </c>
     </row>
@@ -5387,17 +5387,17 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>CASE_004</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>国盛证券（经腾讯新闻转载）</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
@@ -5422,7 +5422,7 @@
       </c>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>https://news.qq.com/rain/a/20251130A04A7P00</t>
+          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
         </is>
       </c>
     </row>
@@ -5439,22 +5439,22 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>CASE_007</t>
+          <t>TSLA_001</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>C114通信网</t>
+          <t>特斯拉公司（Tesla, Inc.，SEC EDGAR）</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G96" s="2" t="n">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>https://www.c114.com.cn/other/241/a1307528.html</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1318605/000162828026003952/tsla-20251231.htm</t>
         </is>
       </c>
     </row>
@@ -5491,22 +5491,22 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>CASE_008</t>
+          <t>SNE_001</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>中国基金报</t>
+          <t>SNE Research</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>2024-07-14</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G97" s="2" t="n">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
+          <t>https://www.sneresearch.com/en/insight/release_view/744/page/0</t>
         </is>
       </c>
     </row>
@@ -5595,17 +5595,17 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>CASE_004</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>国盛证券（经腾讯新闻转载）</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
@@ -5630,7 +5630,7 @@
       </c>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>https://news.qq.com/rain/a/20251130A04A7P00</t>
+          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
         </is>
       </c>
     </row>
@@ -5647,22 +5647,22 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>CASE_007</t>
+          <t>TSLA_001</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>C114通信网</t>
+          <t>特斯拉公司（Tesla, Inc.，SEC EDGAR）</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G100" s="2" t="n">
@@ -5682,7 +5682,7 @@
       </c>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>https://www.c114.com.cn/other/241/a1307528.html</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1318605/000162828026003952/tsla-20251231.htm</t>
         </is>
       </c>
     </row>
@@ -5803,22 +5803,22 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>CASE_008</t>
+          <t>SNE_001</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>中国基金报</t>
+          <t>SNE Research</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>2024-07-14</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G103" s="2" t="n">
@@ -5838,7 +5838,7 @@
       </c>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
+          <t>https://www.sneresearch.com/en/insight/release_view/744/page/0</t>
         </is>
       </c>
     </row>
@@ -5855,17 +5855,17 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
+          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
         </is>
       </c>
     </row>
@@ -5907,17 +5907,17 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>CASE_004</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>国盛证券（经腾讯新闻转载）</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
@@ -5942,7 +5942,7 @@
       </c>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>https://news.qq.com/rain/a/20251130A04A7P00</t>
+          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
         </is>
       </c>
     </row>
@@ -5959,22 +5959,22 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>CASE_007</t>
+          <t>TSLA_001</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>C114通信网</t>
+          <t>特斯拉公司（Tesla, Inc.，SEC EDGAR）</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G106" s="2" t="n">
@@ -5994,7 +5994,7 @@
       </c>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>https://www.c114.com.cn/other/241/a1307528.html</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1318605/000162828026003952/tsla-20251231.htm</t>
         </is>
       </c>
     </row>
@@ -6011,22 +6011,22 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>CASE_008</t>
+          <t>SNE_001</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>中国基金报</t>
+          <t>SNE Research</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>2024-07-14</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G107" s="2" t="n">
@@ -6046,7 +6046,7 @@
       </c>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
+          <t>https://www.sneresearch.com/en/insight/release_view/744/page/0</t>
         </is>
       </c>
     </row>
@@ -6063,17 +6063,17 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
@@ -6098,7 +6098,7 @@
       </c>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
+          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
         </is>
       </c>
     </row>
@@ -6115,17 +6115,17 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>CASE_004</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>国盛证券（经腾讯新闻转载）</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="L109" s="2" t="inlineStr">
         <is>
-          <t>https://news.qq.com/rain/a/20251130A04A7P00</t>
+          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
         </is>
       </c>
     </row>
@@ -6167,22 +6167,22 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>CASE_007</t>
+          <t>TSLA_001</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>C114通信网</t>
+          <t>特斯拉公司（Tesla, Inc.，SEC EDGAR）</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G110" s="2" t="n">
@@ -6202,7 +6202,7 @@
       </c>
       <c r="L110" s="2" t="inlineStr">
         <is>
-          <t>https://www.c114.com.cn/other/241/a1307528.html</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1318605/000162828026003952/tsla-20251231.htm</t>
         </is>
       </c>
     </row>
@@ -6999,22 +6999,22 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>CASE_004</t>
+          <t>TSLA_001</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>国盛证券（经腾讯新闻转载）</t>
+          <t>特斯拉公司（Tesla, Inc.，SEC EDGAR）</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G126" s="2" t="n">
@@ -7034,7 +7034,7 @@
       </c>
       <c r="L126" s="2" t="inlineStr">
         <is>
-          <t>https://news.qq.com/rain/a/20251130A04A7P00</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1318605/000162828026003952/tsla-20251231.htm</t>
         </is>
       </c>
     </row>
@@ -7155,22 +7155,22 @@
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>CASE_004</t>
+          <t>TSLA_001</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>国盛证券（经腾讯新闻转载）</t>
+          <t>特斯拉公司（Tesla, Inc.，SEC EDGAR）</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G129" s="2" t="n">
@@ -7190,7 +7190,7 @@
       </c>
       <c r="L129" s="2" t="inlineStr">
         <is>
-          <t>https://news.qq.com/rain/a/20251130A04A7P00</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1318605/000162828026003952/tsla-20251231.htm</t>
         </is>
       </c>
     </row>
@@ -7306,27 +7306,27 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>恩捷股份 Yunnan Energy New Material (Semcorp)：Market Access Risk</t>
+          <t>恩捷股份 Yunnan Energy New Material (Semcorp)：Operational Risk</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>EU_003</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>欧盟委员会（EUR-Lex / Official Journal）</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="G132" s="2" t="n">
@@ -7346,7 +7346,7 @@
       </c>
       <c r="L132" s="2" t="inlineStr">
         <is>
-          <t>https://eur-lex.europa.eu/legal-content/EN/TXT/?uri=CELEX%3A32024R2754</t>
+          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
         </is>
       </c>
     </row>
@@ -7363,22 +7363,22 @@
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>DHS_001</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>美国国土安全部（DHS，Federal Register）</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G133" s="2" t="n">
@@ -7398,7 +7398,7 @@
       </c>
       <c r="L133" s="2" t="inlineStr">
         <is>
-          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
+          <t>https://www.federalregister.gov/documents/2026/08/03/2026-15628/notice-regarding-the-uyghur-forced-labor-prevention-act-entity-list</t>
         </is>
       </c>
     </row>
@@ -7514,27 +7514,27 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>恩捷股份 Yunnan Energy New Material (Semcorp)：Supply Chain Risk</t>
+          <t>恩捷股份 Yunnan Energy New Material (Semcorp)：Operational Risk</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>SNE_001</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>SNE Research</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G136" s="2" t="n">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="L136" s="2" t="inlineStr">
         <is>
-          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
+          <t>https://www.sneresearch.com/en/insight/release_view/744/page/0</t>
         </is>
       </c>
     </row>
@@ -7566,27 +7566,27 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>恩捷股份 Yunnan Energy New Material (Semcorp)：Supply Chain Risk</t>
+          <t>恩捷股份 Yunnan Energy New Material (Semcorp)：Regulatory Risk</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>CASE_008</t>
+          <t>DHS_001</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>中国基金报</t>
+          <t>美国国土安全部（DHS，Federal Register）</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>2024-07-14</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G137" s="2" t="n">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="L137" s="2" t="inlineStr">
         <is>
-          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
+          <t>https://www.federalregister.gov/documents/2026/08/03/2026-15628/notice-regarding-the-uyghur-forced-labor-prevention-act-entity-list</t>
         </is>
       </c>
     </row>
@@ -7623,17 +7623,17 @@
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>CASE_004</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>国盛证券（经腾讯新闻转载）</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr">
@@ -7658,7 +7658,7 @@
       </c>
       <c r="L138" s="2" t="inlineStr">
         <is>
-          <t>https://news.qq.com/rain/a/20251130A04A7P00</t>
+          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
         </is>
       </c>
     </row>
@@ -7675,22 +7675,22 @@
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>持续更新</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="G139" s="2" t="n">
@@ -7710,7 +7710,7 @@
       </c>
       <c r="L139" s="2" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org</t>
+          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
         </is>
       </c>
     </row>
@@ -7722,27 +7722,27 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>恩捷股份 Yunnan Energy New Material (Semcorp)：Trade Risk</t>
+          <t>恩捷股份 Yunnan Energy New Material (Semcorp)：Supply Chain Risk</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>EU_003</t>
+          <t>CASE_004</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>欧盟委员会（EUR-Lex / Official Journal）</t>
+          <t>国盛证券（经腾讯新闻转载）</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2025-11-30</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="G140" s="2" t="n">
@@ -7762,7 +7762,7 @@
       </c>
       <c r="L140" s="2" t="inlineStr">
         <is>
-          <t>https://eur-lex.europa.eu/legal-content/EN/TXT/?uri=CELEX%3A32024R2754</t>
+          <t>https://news.qq.com/rain/a/20251130A04A7P00</t>
         </is>
       </c>
     </row>
@@ -7774,27 +7774,27 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>恩捷股份 Yunnan Energy New Material (Semcorp)：Trade Risk</t>
+          <t>恩捷股份 Yunnan Energy New Material (Semcorp)：Supply Chain Risk</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>SNE_001</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>SNE Research</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>持续更新</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G141" s="2" t="n">
@@ -7814,7 +7814,7 @@
       </c>
       <c r="L141" s="2" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org</t>
+          <t>https://www.sneresearch.com/en/insight/release_view/744/page/0</t>
         </is>
       </c>
     </row>
@@ -7826,27 +7826,27 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>富士康 Foxconn / 苹果 Apple（供应链）：Market Access Risk</t>
+          <t>富士康 Foxconn / 苹果 Apple（供应链）：Operational Risk</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>EU_003</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>欧盟委员会（EUR-Lex / Official Journal）</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="G142" s="2" t="n">
@@ -7866,7 +7866,7 @@
       </c>
       <c r="L142" s="2" t="inlineStr">
         <is>
-          <t>https://eur-lex.europa.eu/legal-content/EN/TXT/?uri=CELEX%3A32024R2754</t>
+          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
         </is>
       </c>
     </row>
@@ -7883,22 +7883,22 @@
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>DHS_001</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>美国国土安全部（DHS，Federal Register）</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G143" s="2" t="n">
@@ -7918,7 +7918,7 @@
       </c>
       <c r="L143" s="2" t="inlineStr">
         <is>
-          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
+          <t>https://www.federalregister.gov/documents/2026/08/03/2026-15628/notice-regarding-the-uyghur-forced-labor-prevention-act-entity-list</t>
         </is>
       </c>
     </row>
@@ -8034,27 +8034,27 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>富士康 Foxconn / 苹果 Apple（供应链）：Supply Chain Risk</t>
+          <t>富士康 Foxconn / 苹果 Apple（供应链）：Operational Risk</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>SNE_001</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>SNE Research</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G146" s="2" t="n">
@@ -8074,7 +8074,7 @@
       </c>
       <c r="L146" s="2" t="inlineStr">
         <is>
-          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
+          <t>https://www.sneresearch.com/en/insight/release_view/744/page/0</t>
         </is>
       </c>
     </row>
@@ -8086,27 +8086,27 @@
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>富士康 Foxconn / 苹果 Apple（供应链）：Supply Chain Risk</t>
+          <t>富士康 Foxconn / 苹果 Apple（供应链）：Regulatory Risk</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>CASE_008</t>
+          <t>DHS_001</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>中国基金报</t>
+          <t>美国国土安全部（DHS，Federal Register）</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>2024-07-14</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G147" s="2" t="n">
@@ -8126,7 +8126,7 @@
       </c>
       <c r="L147" s="2" t="inlineStr">
         <is>
-          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
+          <t>https://www.federalregister.gov/documents/2026/08/03/2026-15628/notice-regarding-the-uyghur-forced-labor-prevention-act-entity-list</t>
         </is>
       </c>
     </row>
@@ -8143,17 +8143,17 @@
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>CASE_004</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>国盛证券（经腾讯新闻转载）</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F148" s="2" t="inlineStr">
@@ -8178,7 +8178,7 @@
       </c>
       <c r="L148" s="2" t="inlineStr">
         <is>
-          <t>https://news.qq.com/rain/a/20251130A04A7P00</t>
+          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
         </is>
       </c>
     </row>
@@ -8195,22 +8195,22 @@
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>持续更新</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="G149" s="2" t="n">
@@ -8230,7 +8230,7 @@
       </c>
       <c r="L149" s="2" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org</t>
+          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
         </is>
       </c>
     </row>
@@ -8242,27 +8242,27 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>富士康 Foxconn / 苹果 Apple（供应链）：Trade Risk</t>
+          <t>富士康 Foxconn / 苹果 Apple（供应链）：Supply Chain Risk</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>EU_003</t>
+          <t>CASE_004</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>欧盟委员会（EUR-Lex / Official Journal）</t>
+          <t>国盛证券（经腾讯新闻转载）</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2025-11-30</t>
         </is>
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="G150" s="2" t="n">
@@ -8282,7 +8282,7 @@
       </c>
       <c r="L150" s="2" t="inlineStr">
         <is>
-          <t>https://eur-lex.europa.eu/legal-content/EN/TXT/?uri=CELEX%3A32024R2754</t>
+          <t>https://news.qq.com/rain/a/20251130A04A7P00</t>
         </is>
       </c>
     </row>
@@ -8294,27 +8294,27 @@
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>富士康 Foxconn / 苹果 Apple（供应链）：Trade Risk</t>
+          <t>富士康 Foxconn / 苹果 Apple（供应链）：Supply Chain Risk</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>SNE_001</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>SNE Research</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>持续更新</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G151" s="2" t="n">
@@ -8334,7 +8334,7 @@
       </c>
       <c r="L151" s="2" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org</t>
+          <t>https://www.sneresearch.com/en/insight/release_view/744/page/0</t>
         </is>
       </c>
     </row>
@@ -8455,22 +8455,22 @@
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>CASE_008</t>
+          <t>DHS_001</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>中国基金报</t>
+          <t>美国国土安全部（DHS，Federal Register）</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>2024-07-14</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G154" s="2" t="n">
@@ -8490,7 +8490,7 @@
       </c>
       <c r="L154" s="2" t="inlineStr">
         <is>
-          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
+          <t>https://www.federalregister.gov/documents/2026/08/03/2026-15628/notice-regarding-the-uyghur-forced-labor-prevention-act-entity-list</t>
         </is>
       </c>
     </row>
@@ -8507,22 +8507,22 @@
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>CASE_004</t>
+          <t>SNE_001</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>国盛证券（经腾讯新闻转载）</t>
+          <t>SNE Research</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G155" s="2" t="n">
@@ -8542,7 +8542,7 @@
       </c>
       <c r="L155" s="2" t="inlineStr">
         <is>
-          <t>https://news.qq.com/rain/a/20251130A04A7P00</t>
+          <t>https://www.sneresearch.com/en/insight/release_view/744/page/0</t>
         </is>
       </c>
     </row>
@@ -8559,17 +8559,17 @@
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>CASE_007</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>C114通信网</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="F156" s="2" t="inlineStr">
@@ -8594,7 +8594,7 @@
       </c>
       <c r="L156" s="2" t="inlineStr">
         <is>
-          <t>https://www.c114.com.cn/other/241/a1307528.html</t>
+          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
         </is>
       </c>
     </row>
@@ -8606,27 +8606,27 @@
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>制造业外迁企业（行业层面）：Supply Chain Risk</t>
+          <t>制造业外迁企业（行业层面）：Regulatory Risk</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>DHS_001</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>美国国土安全部（DHS，Federal Register）</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G157" s="2" t="n">
@@ -8646,7 +8646,7 @@
       </c>
       <c r="L157" s="2" t="inlineStr">
         <is>
-          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
+          <t>https://www.federalregister.gov/documents/2026/08/03/2026-15628/notice-regarding-the-uyghur-forced-labor-prevention-act-entity-list</t>
         </is>
       </c>
     </row>
@@ -8663,17 +8663,17 @@
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>CASE_008</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>中国基金报</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>2024-07-14</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F158" s="2" t="inlineStr">
@@ -8698,7 +8698,7 @@
       </c>
       <c r="L158" s="2" t="inlineStr">
         <is>
-          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
+          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
         </is>
       </c>
     </row>
@@ -8715,22 +8715,22 @@
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>CASE_004</t>
+          <t>SNE_001</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>国盛证券（经腾讯新闻转载）</t>
+          <t>SNE Research</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G159" s="2" t="n">
@@ -8750,7 +8750,7 @@
       </c>
       <c r="L159" s="2" t="inlineStr">
         <is>
-          <t>https://news.qq.com/rain/a/20251130A04A7P00</t>
+          <t>https://www.sneresearch.com/en/insight/release_view/744/page/0</t>
         </is>
       </c>
     </row>
@@ -8767,17 +8767,17 @@
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>CASE_007</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>C114通信网</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="F160" s="2" t="inlineStr">
@@ -8802,7 +8802,7 @@
       </c>
       <c r="L160" s="2" t="inlineStr">
         <is>
-          <t>https://www.c114.com.cn/other/241/a1307528.html</t>
+          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
         </is>
       </c>
     </row>
@@ -8866,27 +8866,27 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>蜂巢能源 SVOLT（欧洲业务）：Market Access Risk</t>
+          <t>蜂巢能源 SVOLT（欧洲业务）：Operational Risk</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>EU_003</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>欧盟委员会（EUR-Lex / Official Journal）</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="G162" s="2" t="n">
@@ -8906,7 +8906,7 @@
       </c>
       <c r="L162" s="2" t="inlineStr">
         <is>
-          <t>https://eur-lex.europa.eu/legal-content/EN/TXT/?uri=CELEX%3A32024R2754</t>
+          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
         </is>
       </c>
     </row>
@@ -8923,22 +8923,22 @@
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>DHS_001</t>
         </is>
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>美国国土安全部（DHS，Federal Register）</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="F163" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G163" s="2" t="n">
@@ -8958,7 +8958,7 @@
       </c>
       <c r="L163" s="2" t="inlineStr">
         <is>
-          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
+          <t>https://www.federalregister.gov/documents/2026/08/03/2026-15628/notice-regarding-the-uyghur-forced-labor-prevention-act-entity-list</t>
         </is>
       </c>
     </row>
@@ -9074,27 +9074,27 @@
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>蜂巢能源 SVOLT（欧洲业务）：Supply Chain Risk</t>
+          <t>蜂巢能源 SVOLT（欧洲业务）：Operational Risk</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>SNE_001</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>SNE Research</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="F166" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G166" s="2" t="n">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="L166" s="2" t="inlineStr">
         <is>
-          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
+          <t>https://www.sneresearch.com/en/insight/release_view/744/page/0</t>
         </is>
       </c>
     </row>
@@ -9126,27 +9126,27 @@
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>蜂巢能源 SVOLT（欧洲业务）：Supply Chain Risk</t>
+          <t>蜂巢能源 SVOLT（欧洲业务）：Regulatory Risk</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>CASE_008</t>
+          <t>DHS_001</t>
         </is>
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>中国基金报</t>
+          <t>美国国土安全部（DHS，Federal Register）</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>2024-07-14</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="F167" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G167" s="2" t="n">
@@ -9166,7 +9166,7 @@
       </c>
       <c r="L167" s="2" t="inlineStr">
         <is>
-          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
+          <t>https://www.federalregister.gov/documents/2026/08/03/2026-15628/notice-regarding-the-uyghur-forced-labor-prevention-act-entity-list</t>
         </is>
       </c>
     </row>
@@ -9183,17 +9183,17 @@
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>CASE_004</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>国盛证券（经腾讯新闻转载）</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F168" s="2" t="inlineStr">
@@ -9218,7 +9218,7 @@
       </c>
       <c r="L168" s="2" t="inlineStr">
         <is>
-          <t>https://news.qq.com/rain/a/20251130A04A7P00</t>
+          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
         </is>
       </c>
     </row>
@@ -9235,22 +9235,22 @@
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>持续更新</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="F169" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="G169" s="2" t="n">
@@ -9270,7 +9270,7 @@
       </c>
       <c r="L169" s="2" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org</t>
+          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
         </is>
       </c>
     </row>
@@ -9282,27 +9282,27 @@
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>蜂巢能源 SVOLT（欧洲业务）：Trade Risk</t>
+          <t>蜂巢能源 SVOLT（欧洲业务）：Supply Chain Risk</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>EU_003</t>
+          <t>CASE_004</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>欧盟委员会（EUR-Lex / Official Journal）</t>
+          <t>国盛证券（经腾讯新闻转载）</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2025-11-30</t>
         </is>
       </c>
       <c r="F170" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="G170" s="2" t="n">
@@ -9322,7 +9322,7 @@
       </c>
       <c r="L170" s="2" t="inlineStr">
         <is>
-          <t>https://eur-lex.europa.eu/legal-content/EN/TXT/?uri=CELEX%3A32024R2754</t>
+          <t>https://news.qq.com/rain/a/20251130A04A7P00</t>
         </is>
       </c>
     </row>
@@ -9334,27 +9334,27 @@
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>蜂巢能源 SVOLT（欧洲业务）：Trade Risk</t>
+          <t>蜂巢能源 SVOLT（欧洲业务）：Supply Chain Risk</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>SNE_001</t>
         </is>
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>SNE Research</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>持续更新</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="F171" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G171" s="2" t="n">
@@ -9374,7 +9374,7 @@
       </c>
       <c r="L171" s="2" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org</t>
+          <t>https://www.sneresearch.com/en/insight/release_view/744/page/0</t>
         </is>
       </c>
     </row>
@@ -9390,7 +9390,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L37"/>
+  <dimension ref="A1:L50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9472,22 +9472,22 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>BIS_001</t>
+          <t>ALB_001</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Expansion of End-User Controls to Cover Affiliates of Certain Listed Entities（关联企业规则 / 50%穿透规则，临时最终规则）</t>
+          <t>Albemarle Corporation Form 10-K（fiscal year ended December 31, 2025）雅保2025财年年报</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>美国商务部工业与安全局（BIS）</t>
+          <t>雅保公司（Albemarle Corporation，SEC EDGAR）</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -9497,27 +9497,27 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>EV_Battery</t>
+          <t>Battery_Materials</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>出口管制</t>
+          <t>供应链布局</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Company Disclosure</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Regulatory Risk; Market Access Risk</t>
+          <t>Supply Chain Risk; Operational Risk</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>https://www.federalregister.gov/documents/2025/09/30/2025-19001/expansion-of-end-user-controls-to-cover-affiliates-of-certain-listed-entities</t>
+          <t>https://www.sec.gov/Archives/edgar/data/915913/000091591326000018/alb-20251231.htm</t>
         </is>
       </c>
       <c r="K2" s="2" t="n">
@@ -9528,12 +9528,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>BIS_002</t>
+          <t>BIS_001</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>One Year Suspension of Expansion of End-User Controls for Affiliates of Certain Listed Entities（关联企业规则暂停一年）</t>
+          <t>Expansion of End-User Controls to Cover Affiliates of Certain Listed Entities（关联企业规则 / 50%穿透规则，临时最终规则）</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -9543,7 +9543,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -9573,7 +9573,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>https://www.federalregister.gov/documents/2025/11/12/2025-19846/one-year-suspension-of-expansion-of-end-user-controls-for-affiliates-of-certain-listed-entities</t>
+          <t>https://www.federalregister.gov/documents/2025/09/30/2025-19001/expansion-of-end-user-controls-to-cover-affiliates-of-certain-listed-entities</t>
         </is>
       </c>
       <c r="K3" s="2" t="n">
@@ -9584,52 +9584,52 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>BIS_002</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂</t>
+          <t>One Year Suspension of Expansion of End-User Controls for Affiliates of Certain Listed Entities（关联企业规则暂停一年）</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>美国商务部工业与安全局（BIS）</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>General_Manufacturing</t>
+          <t>EV_Battery</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>出口管制</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>News</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Supply Chain Risk; Operational Risk</t>
+          <t>Regulatory Risk; Market Access Risk</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
+          <t>https://www.federalregister.gov/documents/2025/11/12/2025-19846/one-year-suspension-of-expansion-of-end-user-controls-for-affiliates-of-certain-listed-entities</t>
         </is>
       </c>
       <c r="K4" s="2" t="n">
@@ -9640,52 +9640,52 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>CASE_002</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反</t>
+          <t>Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2023-08-18</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Energy_Storage</t>
+          <t>General_Manufacturing</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>反规避</t>
+          <t>供应链布局</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Case Study</t>
+          <t>News</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Trade Risk; Market Access Risk</t>
+          <t>Supply Chain Risk; Operational Risk</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>https://www.whitecase.com/insight-alert/us-department-commerce-determines-imports-southeast-asia-are-circumventing-addcvd</t>
+          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
         </is>
       </c>
       <c r="K5" s="2" t="n">
@@ -9696,12 +9696,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>CASE_003</t>
+          <t>CASE_002</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南）</t>
+          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -9741,7 +9741,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>https://www.internationaltradeinsights.com/2023/08/commerce-issues-final-determination-on-circumvention-of-solar-cells-and-modules-from-cambodia-malaysia-thailand-and-vietnam/</t>
+          <t>https://www.whitecase.com/insight-alert/us-department-commerce-determines-imports-southeast-asia-are-circumventing-addcvd</t>
         </is>
       </c>
       <c r="K6" s="2" t="n">
@@ -9752,52 +9752,52 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>CASE_004</t>
+          <t>CASE_003</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>中际旭创：泰国工厂产能与国内基本齐平</t>
+          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南）</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>国盛证券（经腾讯新闻转载）</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
+          <t>2023-08-18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Electronics_Manufacturing</t>
+          <t>Energy_Storage</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>反规避</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>News</t>
+          <t>Case Study</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Supply Chain Risk; Operational Risk</t>
+          <t>Trade Risk; Market Access Risk</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>https://news.qq.com/rain/a/20251130A04A7P00</t>
+          <t>https://www.internationaltradeinsights.com/2023/08/commerce-issues-final-determination-on-circumvention-of-solar-cells-and-modules-from-cambodia-malaysia-thailand-and-vietnam/</t>
         </is>
       </c>
       <c r="K7" s="2" t="n">
@@ -9808,12 +9808,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>CASE_005</t>
+          <t>CASE_004</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>新易盛：2022年设立泰国基地，一二期已投产</t>
+          <t>中际旭创：泰国工厂产能与国内基本齐平</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -9864,12 +9864,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>CASE_006</t>
+          <t>CASE_005</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>天孚通信：泰国一期投产、二期2025年投入使用</t>
+          <t>新易盛：2022年设立泰国基地，一二期已投产</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -9920,22 +9920,22 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>CASE_007</t>
+          <t>CASE_006</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>华工正源：马来西亚工厂，公开表述为规避地缘风险</t>
+          <t>天孚通信：泰国一期投产、二期2025年投入使用</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>C114通信网</t>
+          <t>国盛证券（经腾讯新闻转载）</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2025-11-30</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -9965,7 +9965,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>https://www.c114.com.cn/other/241/a1307528.html</t>
+          <t>https://news.qq.com/rain/a/20251130A04A7P00</t>
         </is>
       </c>
       <c r="K10" s="2" t="n">
@@ -9976,22 +9976,22 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>CASE_008</t>
+          <t>CASE_007</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>光模块厂商选择东南亚建厂以规避与欧美客户合作风险（中际旭创互动平台回复等）</t>
+          <t>华工正源：马来西亚工厂，公开表述为规避地缘风险</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>中国基金报</t>
+          <t>C114通信网</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2024-07-14</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -10021,7 +10021,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
+          <t>https://www.c114.com.cn/other/241/a1307528.html</t>
         </is>
       </c>
       <c r="K11" s="2" t="n">
@@ -10032,52 +10032,52 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>CASE_009</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>BIS 50%穿透规则：发布→暂停→2026-11-10恢复的完整时间线</t>
+          <t>光模块厂商选择东南亚建厂以规避与欧美客户合作风险（中际旭创互动平台回复等）</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>美国商务部工业与安全局（BIS）</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>EV_Battery</t>
+          <t>Electronics_Manufacturing</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>出口管制</t>
+          <t>供应链布局</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Case Study</t>
+          <t>News</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Regulatory Risk; Market Access Risk</t>
+          <t>Supply Chain Risk; Operational Risk</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>https://www.federalregister.gov/documents/2025/11/12/2025-19846/one-year-suspension-of-expansion-of-end-user-controls-for-affiliates-of-certain-listed-entities</t>
+          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
         </is>
       </c>
       <c r="K12" s="2" t="n">
@@ -10088,22 +10088,22 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>CASE_010</t>
+          <t>CASE_009</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>白宫点名东南亚为非法转运高风险地区，并推出AI执法工具</t>
+          <t>BIS 50%穿透规则：发布→暂停→2026-11-10恢复的完整时间线</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>美国白宫（经律所解读）</t>
+          <t>美国商务部工业与安全局（BIS）</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -10118,7 +10118,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>出口管制</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>Trade Risk; Market Access Risk</t>
+          <t>Regulatory Risk; Market Access Risk</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>https://www.alvarezandmarsal.com/node/97806</t>
+          <t>https://www.federalregister.gov/documents/2025/11/12/2025-19846/one-year-suspension-of-expansion-of-end-user-controls-for-affiliates-of-certain-listed-entities</t>
         </is>
       </c>
       <c r="K13" s="2" t="n">
@@ -10144,22 +10144,22 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>CASE_010</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>国务院关于对外投资的规定（国务院令第837号）</t>
+          <t>白宫点名东南亚为非法转运高风险地区，并推出AI执法工具</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>中华人民共和国国务院</t>
+          <t>美国白宫（经律所解读）</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -10174,22 +10174,22 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Case Study</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Political Risk; Regulatory Risk</t>
+          <t>Trade Risk; Market Access Risk</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>https://www.gov.cn/gongbao/2026/issue_12786/202606/content_7071618.html</t>
+          <t>https://www.alvarezandmarsal.com/node/97806</t>
         </is>
       </c>
       <c r="K14" s="2" t="n">
@@ -10200,27 +10200,27 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>CSIS_001</t>
+          <t>CNGOV_001</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA</t>
+          <t>国务院关于对外投资的规定（国务院令第837号）</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>战略与国际研究中心（CSIS）</t>
+          <t>中华人民共和国国务院</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -10230,22 +10230,22 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Industry Report</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>Trade Risk; Market Access Risk</t>
+          <t>Political Risk; Regulatory Risk</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>https://www.csis.org/analysis/visibility-gap-how-ai-can-stop-chinese-transshipment-under-usmca</t>
+          <t>https://www.gov.cn/gongbao/2026/issue_12786/202606/content_7071618.html</t>
         </is>
       </c>
       <c r="K15" s="2" t="n">
@@ -10256,42 +10256,42 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>DOC_001</t>
+          <t>CSIS_001</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Final Circumvention Determinations: Crystalline Silicon Photovoltaic Cells from Cambodia, Malaysia, Thailand and Vietnam（东南亚四国光伏反规避终裁）</t>
+          <t>The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>美国商务部</t>
+          <t>战略与国际研究中心（CSIS）</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2023-08-23</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Energy_Storage</t>
+          <t>EV_Battery</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>反规避</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Industry Report</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -10301,7 +10301,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>https://www.govinfo.gov/content/pkg/FR-2023-08-23/pdf/2023-18161.pdf</t>
+          <t>https://www.csis.org/analysis/visibility-gap-how-ai-can-stop-chinese-transshipment-under-usmca</t>
         </is>
       </c>
       <c r="K16" s="2" t="n">
@@ -10312,22 +10312,22 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>EU_001</t>
+          <t>DHS_001</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Regulation (EU) 2023/1542 concerning batteries and waste batteries（欧盟电池与废电池法规）</t>
+          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告）</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）</t>
+          <t>美国国土安全部（DHS，Federal Register）</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2023-07-28</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -10342,7 +10342,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>市场准入</t>
+          <t>劳工</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -10352,12 +10352,12 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Regulatory Risk; Market Access Risk</t>
+          <t>Operational Risk; Regulatory Risk</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>https://eur-lex.europa.eu/legal-content/EN/TXT/?uri=CELEX%3A32023R1542</t>
+          <t>https://www.federalregister.gov/documents/2026/08/03/2026-15628/notice-regarding-the-uyghur-forced-labor-prevention-act-entity-list</t>
         </is>
       </c>
       <c r="K17" s="2" t="n">
@@ -10368,22 +10368,22 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>EU_002</t>
+          <t>DOC_001</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Regulation (EU) 2024/1252 establishing a framework for ensuring a secure and sustainable supply of critical raw materials（欧盟关键原材料法案 CRMA）</t>
+          <t>Final Circumvention Determinations: Crystalline Silicon Photovoltaic Cells from Cambodia, Malaysia, Thailand and Vietnam（东南亚四国光伏反规避终裁）</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）</t>
+          <t>美国商务部</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>2023-08-23</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -10393,12 +10393,12 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>EV_Battery</t>
+          <t>Energy_Storage</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>本地化政策</t>
+          <t>反规避</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -10408,12 +10408,12 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Supply Chain Risk; Political Risk</t>
+          <t>Trade Risk; Market Access Risk</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>https://eur-lex.europa.eu/legal-content/EN/TXT/?uri=CELEX%3A32024R1252</t>
+          <t>https://www.govinfo.gov/content/pkg/FR-2023-08-23/pdf/2023-18161.pdf</t>
         </is>
       </c>
       <c r="K18" s="2" t="n">
@@ -10424,22 +10424,22 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>EU_003</t>
+          <t>EU_001</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Commission Implementing Regulation (EU) 2024/2754 imposing a definitive countervailing duty on imports of new battery electric vehicles originating in China（对华纯电动车最终反补贴税）</t>
+          <t>Regulation (EU) 2023/1542 concerning batteries and waste batteries（欧盟电池与废电池法规）</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>欧盟委员会（EUR-Lex / Official Journal）</t>
+          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2023-07-28</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -10454,7 +10454,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>关税</t>
+          <t>市场准入</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -10464,12 +10464,12 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>Trade Risk; Market Access Risk</t>
+          <t>Regulatory Risk; Market Access Risk</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>https://eur-lex.europa.eu/legal-content/EN/TXT/?uri=CELEX%3A32024R2754</t>
+          <t>https://eur-lex.europa.eu/legal-content/EN/TXT/?uri=CELEX%3A32023R1542</t>
         </is>
       </c>
       <c r="K19" s="2" t="n">
@@ -10480,12 +10480,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>EU_004</t>
+          <t>EU_002</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Regulation (EU) 2019/452 establishing a framework for the screening of foreign direct investments into the Union（欧盟外资安全审查框架条例）</t>
+          <t>Regulation (EU) 2024/1252 establishing a framework for ensuring a secure and sustainable supply of critical raw materials（欧盟关键原材料法案 CRMA）</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -10495,7 +10495,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>2019-03-21</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -10510,7 +10510,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>本地化政策</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -10520,12 +10520,12 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Political Risk; Regulatory Risk</t>
+          <t>Market Access Risk; Supply Chain Risk; Political Risk</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>https://eur-lex.europa.eu/legal-content/EN/TXT/?uri=CELEX%3A32019R0452</t>
+          <t>https://eur-lex.europa.eu/legal-content/EN/TXT/?uri=CELEX%3A32024R1252</t>
         </is>
       </c>
       <c r="K20" s="2" t="n">
@@ -10536,22 +10536,22 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>FR_001</t>
+          <t>EU_003</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Federal Register API（美国联邦公报）</t>
+          <t>Commission Implementing Regulation (EU) 2024/2754 imposing a definitive countervailing duty on imports of new battery electric vehicles originating in China（对华纯电动车最终反补贴税）</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>美国国家档案馆联邦公报办公室</t>
+          <t>欧盟委员会（EUR-Lex / Official Journal）</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>持续更新（每日）</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -10566,7 +10566,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>出口管制/关税</t>
+          <t>关税</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>Regulatory Risk; Trade Risk; Market Access Risk</t>
+          <t>Trade Risk; Market Access Risk</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>https://www.federalregister.gov</t>
+          <t>https://eur-lex.europa.eu/legal-content/EN/TXT/?uri=CELEX%3A32024R2754</t>
         </is>
       </c>
       <c r="K21" s="2" t="n">
@@ -10592,27 +10592,27 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>IMF_001</t>
+          <t>EU_004</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>World Economic Outlook, April 2023, Chapter 4: Geoeconomic Fragmentation and Foreign Direct Investment</t>
+          <t>Regulation (EU) 2019/452 establishing a framework for the screening of foreign direct investments into the Union（欧盟外资安全审查框架条例）</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>国际货币基金组织（IMF）</t>
+          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>2023-04</t>
+          <t>2019-03-21</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -10627,7 +10627,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Industry Report</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -10637,7 +10637,7 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>https://www.imf.org/-/media/files/publications/weo/2023/april/english/ch4.pdf</t>
+          <t>https://eur-lex.europa.eu/legal-content/EN/TXT/?uri=CELEX%3A32019R0452</t>
         </is>
       </c>
       <c r="K22" s="2" t="n">
@@ -10648,22 +10648,22 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>IRS_001</t>
+          <t>FR_001</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则）</t>
+          <t>Federal Register API（美国联邦公报）</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>美国财政部/国税局（Federal Register）</t>
+          <t>美国国家档案馆联邦公报办公室</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>持续更新（每日）</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -10678,7 +10678,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>本地化政策</t>
+          <t>出口管制/关税</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -10688,12 +10688,12 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Supply Chain Risk; Political Risk</t>
+          <t>Regulatory Risk; Trade Risk; Market Access Risk</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>https://www.federalregister.gov/documents/2024/05/06/2024-09094/clean-vehicle-credits-under-sections-25e-and-30d-transfer-of-credits-critical-minerals-and-battery</t>
+          <t>https://www.federalregister.gov</t>
         </is>
       </c>
       <c r="K23" s="2" t="n">
@@ -10704,27 +10704,27 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>ITA_001</t>
+          <t>IEA_001</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Consolidated Screening List API（美国合并筛查清单）</t>
+          <t>Global EV Outlook 2025（全球电动汽车展望2025）</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>美国国际贸易管理局（ITA）</t>
+          <t>国际能源署（IEA）</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>持续更新（每日）</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -10734,22 +10734,22 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>出口管制</t>
+          <t>供应链布局</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Industry Report</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Regulatory Risk; Market Access Risk</t>
+          <t>Supply Chain Risk; Operational Risk</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>https://www.trade.gov/consolidated-screening-list</t>
+          <t>https://www.iea.org/reports/global-ev-outlook-2025</t>
         </is>
       </c>
       <c r="K24" s="2" t="n">
@@ -10760,27 +10760,27 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>KPMG_001</t>
+          <t>IMF_001</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>KPMG 2026 US Supply Chain Survey</t>
+          <t>World Economic Outlook, April 2023, Chapter 4: Geoeconomic Fragmentation and Foreign Direct Investment</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>毕马威（KPMG）</t>
+          <t>国际货币基金组织（IMF）</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2023-04</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -10790,7 +10790,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -10800,12 +10800,12 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>Supply Chain Risk; Operational Risk</t>
+          <t>Political Risk; Regulatory Risk</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>https://kpmg.com/us/en/articles/2026/2026-supply-chain-survey.html</t>
+          <t>https://www.imf.org/-/media/files/publications/weo/2023/april/english/ch4.pdf</t>
         </is>
       </c>
       <c r="K25" s="2" t="n">
@@ -10816,27 +10816,27 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>MCK_001</t>
+          <t>IRS_001</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>The art, science, and technology of geopolitical scenario planning</t>
+          <t>Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则）</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>麦肯锡（McKinsey）</t>
+          <t>美国财政部/国税局（Federal Register）</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -10846,22 +10846,22 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>本地化政策</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Industry Report</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Political Risk; Trade Risk</t>
+          <t>Market Access Risk; Supply Chain Risk; Political Risk</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>https://www.mckinsey.com/capabilities/geopolitics/our-insights/the-art-science-and-technology-of-geopolitical-scenario-planning</t>
+          <t>https://www.federalregister.gov/documents/2024/05/06/2024-09094/clean-vehicle-credits-under-sections-25e-and-30d-transfer-of-credits-critical-minerals-and-battery</t>
         </is>
       </c>
       <c r="K26" s="2" t="n">
@@ -10872,22 +10872,22 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>MOFCOM_001</t>
+          <t>ITA_001</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>2026年度《两用物项和技术进出口许可证管理目录》</t>
+          <t>Consolidated Screening List API（美国合并筛查清单）</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>商务部、海关总署</t>
+          <t>美国国际贸易管理局（ITA）</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>持续更新（每日）</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -10917,7 +10917,7 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>https://www.mofcom.gov.cn/zwgk/zcfb/art/2025/art_c03d1e511b2b486e829d68e8f1422aff.html</t>
+          <t>https://www.trade.gov/consolidated-screening-list</t>
         </is>
       </c>
       <c r="K27" s="2" t="n">
@@ -10928,27 +10928,27 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>MOFCOM_002</t>
+          <t>KPMG_001</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制）</t>
+          <t>KPMG 2026 US Supply Chain Survey</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>商务部</t>
+          <t>毕马威（KPMG）</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -10958,22 +10958,22 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>出口管制</t>
+          <t>供应链布局</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Industry Report</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Regulatory Risk; Market Access Risk</t>
+          <t>Supply Chain Risk; Operational Risk</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>https://www.mofcom.gov.cn/zwgk/zcfb/art/2025/art_5c68985a6b1a46778e2e8dbff1bb1601.html</t>
+          <t>https://kpmg.com/us/en/articles/2026/2026-supply-chain-survey.html</t>
         </is>
       </c>
       <c r="K28" s="2" t="n">
@@ -10984,52 +10984,52 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>TRD_001</t>
+          <t>LI_001</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度</t>
+          <t>Li Auto Inc. Form 20-F（fiscal year ended December 31, 2025）理想汽车2025财年年报</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>理想汽车（Li Auto Inc.，SEC EDGAR）</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>持续更新</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Electronics_Manufacturing</t>
+          <t>Automotive</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>关税</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Trade Data</t>
+          <t>Company Disclosure</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>Trade Risk; Supply Chain Risk</t>
+          <t>Trade Risk; Market Access Risk</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1791706/000110465926041705/li-20251231x20f.htm</t>
         </is>
       </c>
       <c r="K29" s="2" t="n">
@@ -11040,52 +11040,52 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>TRD_002</t>
+          <t>MCK_001</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>美国自越南、泰国、马来西亚、柬埔寨进口光伏组件HS 854140，2018–2025年度</t>
+          <t>The art, science, and technology of geopolitical scenario planning</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>麦肯锡（McKinsey）</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>持续更新</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Energy_Storage</t>
+          <t>EV_Battery</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Trade Data</t>
+          <t>Industry Report</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>Trade Risk; Supply Chain Risk</t>
+          <t>Political Risk; Trade Risk</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org</t>
+          <t>https://www.mckinsey.com/capabilities/geopolitics/our-insights/the-art-science-and-technology-of-geopolitical-scenario-planning</t>
         </is>
       </c>
       <c r="K30" s="2" t="n">
@@ -11096,52 +11096,52 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>MOFCOM_001</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度</t>
+          <t>2026年度《两用物项和技术进出口许可证管理目录》</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>商务部、海关总署</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>持续更新</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Electronics_Manufacturing</t>
+          <t>EV_Battery</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>出口管制</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Trade Data</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>Trade Risk; Supply Chain Risk</t>
+          <t>Regulatory Risk; Market Access Risk</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org</t>
+          <t>https://www.mofcom.gov.cn/zwgk/zcfb/art/2025/art_c03d1e511b2b486e829d68e8f1422aff.html</t>
         </is>
       </c>
       <c r="K31" s="2" t="n">
@@ -11152,27 +11152,27 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>MOFCOM_002</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>World Investment Report 2026: International Investment in a Turbulent Era</t>
+          <t>商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制）</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>联合国贸易和发展会议（UNCTAD）</t>
+          <t>商务部</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -11182,22 +11182,22 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>出口管制</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Industry Report</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>Political Risk; Regulatory Risk</t>
+          <t>Regulatory Risk; Market Access Risk</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>https://unctad.org/publication/world-investment-report-2026</t>
+          <t>https://www.mofcom.gov.cn/zwgk/zcfb/art/2025/art_5c68985a6b1a46778e2e8dbff1bb1601.html</t>
         </is>
       </c>
       <c r="K32" s="2" t="n">
@@ -11208,22 +11208,22 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>UST_001</t>
+          <t>NIO_001</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Notice of Modification: China's Acts, Policies and Practices Related to Technology Transfer, Intellectual Property and Innovation（Section 301 对华关税调整通知）</t>
+          <t>NIO Inc. Form 20-F（fiscal year ended December 31, 2025）蔚来2025财年年报</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>美国贸易代表办公室（USTR，Federal Register）</t>
+          <t>蔚来（NIO Inc.，SEC EDGAR）</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -11233,27 +11233,27 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>EV_Battery</t>
+          <t>Automotive</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>关税</t>
+          <t>出口管制</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Company Disclosure</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>Trade Risk; Market Access Risk</t>
+          <t>Regulatory Risk; Market Access Risk</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>https://www.federalregister.gov/documents/2024/09/18/2024-21217/notice-of-modification-chinas-acts-policies-and-practices-related-to-technology-transfer</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1736541/000110465926041765/nio-20251231x20f.htm</t>
         </is>
       </c>
       <c r="K33" s="2" t="n">
@@ -11264,27 +11264,27 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>SNE_001</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Global Risks Report 2026（全球风险报告2026，第21版）</t>
+          <t>January-August 2026 Global EV Battery Usage Reaches 844.2 GWh, Up 19.7% Year-on-Year（2026年1–8月全球动力电池装车量快报）</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>世界经济论坛（WEF）</t>
+          <t>SNE Research</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -11294,7 +11294,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>供应链布局</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -11304,12 +11304,12 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Political Risk; Trade Risk</t>
+          <t>Supply Chain Risk; Operational Risk</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>https://www.weforum.org/publications/global-risks-report-2026</t>
+          <t>https://www.sneresearch.com/en/insight/release_view/744/page/0</t>
         </is>
       </c>
       <c r="K34" s="2" t="n">
@@ -11320,52 +11320,52 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>WH_001</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Executive Order 14411: Strengthening Customs Enforcement（加强海关执法行政令）</t>
+          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>美国白宫</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>持续更新</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>EV_Battery</t>
+          <t>Electronics_Manufacturing</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Trade Data</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>Trade Risk; Market Access Risk</t>
+          <t>Trade Risk; Supply Chain Risk</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>https://www.govinfo.gov/content/pkg/FR-2026-06-10/pdf/2026-11595.pdf</t>
+          <t>https://comtradeplus.un.org</t>
         </is>
       </c>
       <c r="K35" s="2" t="n">
@@ -11376,52 +11376,52 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>WH_002</t>
+          <t>TRD_002</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告）</t>
+          <t>美国自越南、泰国、马来西亚、柬埔寨进口光伏组件HS 854140，2018–2025年度</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>美国白宫贸易与制造业政策办公室</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>持续更新</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>EV_Battery</t>
+          <t>Energy_Storage</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Trade Data</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>Trade Risk; Market Access Risk</t>
+          <t>Trade Risk; Supply Chain Risk</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>https://www.whitehouse.gov/wp-content/uploads/2026/08/The-Great-Transshipment-Scam.pdf</t>
+          <t>https://comtradeplus.un.org</t>
         </is>
       </c>
       <c r="K36" s="2" t="n">
@@ -11432,61 +11432,789 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>TRD_003</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>持续更新</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Electronics_Manufacturing</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>贸易流</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>Trade Data</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>Trade Risk; Supply Chain Risk</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>https://comtradeplus.un.org</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>TSLA_001</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Tesla, Inc. Form 10-K（fiscal year ended December 31, 2025）特斯拉2025财年年报</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>特斯拉公司（Tesla, Inc.，SEC EDGAR）</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-29</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Automotive</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>供应链布局</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>Company Disclosure</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>Supply Chain Risk; Operational Risk</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1318605/000162828026003952/tsla-20251231.htm</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>UNCTAD_001</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>World Investment Report 2026: International Investment in a Turbulent Era</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>联合国贸易和发展会议（UNCTAD）</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>EV_Battery</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>Industry Report</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>Political Risk; Regulatory Risk</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>https://unctad.org/publication/world-investment-report-2026</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>USMCA_001</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>USMCA Chapter 4: Rules of Origin（美墨加协定第4章原产地规则）</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>美国贸易代表办公室（USTR）</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>2020-07-01</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>EV_Battery</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>原产地与转运</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>Policy</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>Trade Risk; Market Access Risk</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>https://ustr.gov/trade-agreements/free-trade-agreements/united-states-mexico-canada-agreement/agreement-between</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>UST_001</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Notice of Modification: China's Acts, Policies and Practices Related to Technology Transfer, Intellectual Property and Innovation（Section 301 对华关税调整通知）</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>美国贸易代表办公室（USTR，Federal Register）</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>EV_Battery</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>关税</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>Policy</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>Trade Risk; Market Access Risk</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>https://www.federalregister.gov/documents/2024/09/18/2024-21217/notice-of-modification-chinas-acts-policies-and-practices-related-to-technology-transfer</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>WB_001</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Connecting to Compete 2023: Trade Logistics in an Uncertain Global Economy（2023年物流绩效指数报告）</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>世界银行（World Bank）</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>2023-04-28</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>EV_Battery</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>物流</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>Industry Report</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>Supply Chain Risk; Operational Risk</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>https://documents.worldbank.org/curated/en/099042123145531599/pdf/P17146804a6a570ac0a4f80895e320dda1e.pdf</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>WEF_001</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Global Risks Report 2026（全球风险报告2026，第21版）</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>世界经济论坛（WEF）</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>EV_Battery</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>宏观风险</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>Industry Report</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>Political Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>https://www.weforum.org/publications/global-risks-report-2026</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>WH_001</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Executive Order 14411: Strengthening Customs Enforcement（加强海关执法行政令）</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>美国白宫</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>EV_Battery</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>原产地与转运</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>Policy</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>Trade Risk; Market Access Risk</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>https://www.govinfo.gov/content/pkg/FR-2026-06-10/pdf/2026-11595.pdf</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>WH_002</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告）</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>美国白宫贸易与制造业政策办公室</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>EV_Battery</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>原产地与转运</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>Policy</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>Trade Risk; Market Access Risk</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>https://www.whitehouse.gov/wp-content/uploads/2026/08/The-Great-Transshipment-Scam.pdf</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
           <t>WTO_001</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>Global Trade Outlook and Statistics（2026年3月版）</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
         <is>
           <t>世界贸易组织（WTO）</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>A+</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>EV_Battery</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t>贸易流</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>Industry Report</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr">
+      <c r="I46" s="2" t="inlineStr">
         <is>
           <t>Trade Risk; Supply Chain Risk</t>
         </is>
       </c>
-      <c r="J37" s="2" t="inlineStr">
+      <c r="J46" s="2" t="inlineStr">
         <is>
           <t>https://www.astrid-online.it/static/upload/wto-/wto-global-trade-outlook-2026.pdf</t>
         </is>
       </c>
-      <c r="K37" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L37" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>WTO_002</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Trade Policy Review: Report by the Secretariat — India（WT/TPR/S/403）印度第七次贸易政策审议秘书处报告</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>世界贸易组织（WTO）</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>2020-11-25</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>EV_Battery</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>贸易流</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>Policy</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>Trade Risk; Supply Chain Risk</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wto.org/english/tratop_e/tpr_e/s403_e.pdf</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>WTO_003</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>WTO Tariff Profile: India — Tariffs and Imports Summary（WTO国别关税快照：印度）</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>世界贸易组织（WTO）</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>EV_Battery</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>贸易流</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>Trade Data</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>Trade Risk; Supply Chain Risk</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wto.org/english/res_e/statis_e/daily_update_e/tariff_profiles/IN_E.pdf</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>WTO_004</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Trade Policy Review: Report by the Secretariat — Indonesia（WT/TPR/S/401）印尼第七次贸易政策审议秘书处报告</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>世界贸易组织（WTO）</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>2020-11-04</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>EV_Battery</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>本地化政策</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>Policy</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk; Supply Chain Risk; Political Risk</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wto.org/english/tratop_e/tpr_e/s401_e.pdf</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>XPEV_001</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>XPeng Inc. Form 20-F（fiscal year ended December 31, 2025）小鹏汽车2025财年年报</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>小鹏汽车（XPeng Inc.，SEC EDGAR）</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>Automotive</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>出口管制</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>Company Disclosure</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>Regulatory Risk; Market Access Risk</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1810997/000119312526157849/d36361d20f.htm</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L50" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L37"/>
+  <autoFilter ref="A1:L50"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -14871,7 +15599,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>

--- a/data/evaluation/evidence_quality_test.xlsx
+++ b/data/evaluation/evidence_quality_test.xlsx
@@ -11177,7 +11177,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>EV_Battery</t>
+          <t>Battery_Materials</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11345,7 +11345,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Electronics_Manufacturing</t>
+          <t>EV_Battery</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">

--- a/data/evaluation/evidence_quality_test.xlsx
+++ b/data/evaluation/evidence_quality_test.xlsx
@@ -12225,17 +12225,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H86"/>
+  <dimension ref="A1:I86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -12261,20 +12262,25 @@
       </c>
       <c r="E1" s="4" t="inlineStr">
         <is>
+          <t>external_source_refs</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
           <t>all_citable</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="G1" s="4" t="inlineStr">
         <is>
           <t>sources</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="H1" s="4" t="inlineStr">
         <is>
           <t>has_date</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="I1" s="4" t="inlineStr">
         <is>
           <t>verdict</t>
         </is>
@@ -12298,21 +12304,26 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
+          <t>TRD_001; EU_003; IEA_001; CASE_004; WB_001</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
           <t>NEWS_001</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>东方财富网</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="F2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>世界银行（World Bank）; 国盛证券（经腾讯新闻转载）; 国际能源署（IEA）; 欧盟委员会（EUR-Lex / Official Journal）; 联合国商品贸易统计数据库（UN Comtrade）</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>可追溯</t>
         </is>
@@ -12336,21 +12347,26 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
+          <t>TRD_001; EU_003; IEA_001; CASE_004; WB_001</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
           <t>NEWS_001</t>
         </is>
       </c>
-      <c r="E3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>东方财富网</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="F3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>世界银行（World Bank）; 国盛证券（经腾讯新闻转载）; 国际能源署（IEA）; 欧盟委员会（EUR-Lex / Official Journal）; 联合国商品贸易统计数据库（UN Comtrade）</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>可追溯</t>
         </is>
@@ -12374,21 +12390,26 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>TRD_001; EU_003; IEA_001; CASE_004; WB_001</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>NEWS_001</t>
         </is>
       </c>
-      <c r="E4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>东方财富网</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>世界银行（World Bank）; 国盛证券（经腾讯新闻转载）; 国际能源署（IEA）; 欧盟委员会（EUR-Lex / Official Journal）; 联合国商品贸易统计数据库（UN Comtrade）</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>可追溯</t>
         </is>
@@ -12412,21 +12433,26 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>TRD_001; EU_003; IEA_001; CASE_004; WB_001</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
           <t>NEWS_001</t>
         </is>
       </c>
-      <c r="E5" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>东方财富网</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="F5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>世界银行（World Bank）; 国盛证券（经腾讯新闻转载）; 国际能源署（IEA）; 欧盟委员会（EUR-Lex / Official Journal）; 联合国商品贸易统计数据库（UN Comtrade）</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>可追溯</t>
         </is>
@@ -12450,21 +12476,26 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>TRD_001; EU_003; IEA_001; CASE_004; WB_001</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>NEWS_001</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>东方财富网</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>世界银行（World Bank）; 国盛证券（经腾讯新闻转载）; 国际能源署（IEA）; 欧盟委员会（EUR-Lex / Official Journal）; 联合国商品贸易统计数据库（UN Comtrade）</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>可追溯</t>
         </is>
@@ -12488,21 +12519,26 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>TRD_001; CASE_004; IEA_001; WB_001</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>NEWS_002; COMPANY_REPORT_001</t>
         </is>
       </c>
-      <c r="E7" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>易车; 证券之星（长安汽车投资者互动平台回复）</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>世界银行（World Bank）; 国盛证券（经腾讯新闻转载）; 国际能源署（IEA）; 联合国商品贸易统计数据库（UN Comtrade）</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>可追溯</t>
         </is>
@@ -12526,21 +12562,26 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>TRD_001; CASE_004; IEA_001; WB_001</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>NEWS_002; COMPANY_REPORT_001</t>
         </is>
       </c>
-      <c r="E8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>易车; 证券之星（长安汽车投资者互动平台回复）</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>世界银行（World Bank）; 国盛证券（经腾讯新闻转载）; 国际能源署（IEA）; 联合国商品贸易统计数据库（UN Comtrade）</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>可追溯</t>
         </is>
@@ -12564,21 +12605,26 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
+          <t>TRD_001; CASE_004; IEA_001; WB_001</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
           <t>NEWS_002; COMPANY_REPORT_001</t>
         </is>
       </c>
-      <c r="E9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>易车; 证券之星（长安汽车投资者互动平台回复）</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="F9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>世界银行（World Bank）; 国盛证券（经腾讯新闻转载）; 国际能源署（IEA）; 联合国商品贸易统计数据库（UN Comtrade）</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>可追溯</t>
         </is>
@@ -12602,21 +12648,26 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>TRD_001; CASE_004; IEA_001; WB_001</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>NEWS_002; COMPANY_REPORT_001</t>
         </is>
       </c>
-      <c r="E10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>易车; 证券之星（长安汽车投资者互动平台回复）</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>世界银行（World Bank）; 国盛证券（经腾讯新闻转载）; 国际能源署（IEA）; 联合国商品贸易统计数据库（UN Comtrade）</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>可追溯</t>
         </is>
@@ -12640,21 +12691,26 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>TRD_001; CASE_004; IEA_001; WB_001</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
           <t>NEWS_002; COMPANY_REPORT_001</t>
         </is>
       </c>
-      <c r="E11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>易车; 证券之星（长安汽车投资者互动平台回复）</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="F11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>世界银行（World Bank）; 国盛证券（经腾讯新闻转载）; 国际能源署（IEA）; 联合国商品贸易统计数据库（UN Comtrade）</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>可追溯</t>
         </is>
@@ -12678,21 +12734,26 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>TRD_001; TRD_003; SNE_001; WB_001; CASE_007</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>NEWS_003; NEWS_004</t>
         </is>
       </c>
-      <c r="E12" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>澎湃新闻; 盖世汽车社区 / CBC金属网</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>C114通信网; SNE Research; 世界银行（World Bank）; 联合国商品贸易统计数据库（UN Comtrade）</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>可追溯</t>
         </is>
@@ -12716,21 +12777,26 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>TRD_001; TRD_003; SNE_001; WB_001; CASE_007</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>NEWS_003; NEWS_004</t>
         </is>
       </c>
-      <c r="E13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>澎湃新闻; 盖世汽车社区 / CBC金属网</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>C114通信网; SNE Research; 世界银行（World Bank）; 联合国商品贸易统计数据库（UN Comtrade）</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>可追溯</t>
         </is>
@@ -12754,21 +12820,26 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>TRD_001; TRD_003; SNE_001; WB_001; CASE_007</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>NEWS_003; NEWS_004</t>
         </is>
       </c>
-      <c r="E14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>澎湃新闻; 盖世汽车社区 / CBC金属网</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>C114通信网; SNE Research; 世界银行（World Bank）; 联合国商品贸易统计数据库（UN Comtrade）</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>可追溯</t>
         </is>
@@ -12792,21 +12863,26 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
+          <t>TRD_001; TRD_003; SNE_001; WB_001; CASE_007</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
           <t>NEWS_003; NEWS_004</t>
         </is>
       </c>
-      <c r="E15" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>澎湃新闻; 盖世汽车社区 / CBC金属网</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="F15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>C114通信网; SNE Research; 世界银行（World Bank）; 联合国商品贸易统计数据库（UN Comtrade）</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
         <is>
           <t>可追溯</t>
         </is>
@@ -12830,21 +12906,26 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>TRD_001; TRD_003; SNE_001; WB_001; CASE_007</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>NEWS_003; NEWS_004</t>
         </is>
       </c>
-      <c r="E16" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>澎湃新闻; 盖世汽车社区 / CBC金属网</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>C114通信网; SNE Research; 世界银行（World Bank）; 联合国商品贸易统计数据库（UN Comtrade）</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>可追溯</t>
         </is>
@@ -12868,21 +12949,26 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>TRD_001; TRD_003; CASE_007; SNE_001; WB_001</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
           <t>NEWS_005</t>
         </is>
       </c>
-      <c r="E17" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>新浪财经</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="F17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>C114通信网; SNE Research; 世界银行（World Bank）; 联合国商品贸易统计数据库（UN Comtrade）</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>可追溯</t>
         </is>
@@ -12906,21 +12992,26 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>TRD_001; TRD_003; CASE_007; SNE_001; WB_001</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>NEWS_005</t>
         </is>
       </c>
-      <c r="E18" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>新浪财经</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>C114通信网; SNE Research; 世界银行（World Bank）; 联合国商品贸易统计数据库（UN Comtrade）</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>可追溯</t>
         </is>
@@ -12944,21 +13035,26 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>TRD_001; TRD_003; CASE_007; SNE_001; WB_001</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
           <t>NEWS_005</t>
         </is>
       </c>
-      <c r="E19" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>新浪财经</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="F19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>C114通信网; SNE Research; 世界银行（World Bank）; 联合国商品贸易统计数据库（UN Comtrade）</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>可追溯</t>
         </is>
@@ -12982,21 +13078,26 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
+          <t>TRD_001; TRD_003; CASE_007; SNE_001; WB_001</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>NEWS_005</t>
         </is>
       </c>
-      <c r="E20" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>新浪财经</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>C114通信网; SNE Research; 世界银行（World Bank）; 联合国商品贸易统计数据库（UN Comtrade）</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>可追溯</t>
         </is>
@@ -13020,21 +13121,26 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
+          <t>TRD_001; TRD_003; CASE_007; SNE_001; WB_001</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
           <t>NEWS_005</t>
         </is>
       </c>
-      <c r="E21" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>新浪财经</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="F21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>C114通信网; SNE Research; 世界银行（World Bank）; 联合国商品贸易统计数据库（UN Comtrade）</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
         <is>
           <t>可追溯</t>
         </is>
@@ -13058,21 +13164,26 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
+          <t>TRD_001; TRD_003; CASE_007; SNE_001; WB_001</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>NEWS_006; NEWS_007</t>
         </is>
       </c>
-      <c r="E22" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>东方财富网; 腾讯新闻</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="F22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>C114通信网; SNE Research; 世界银行（World Bank）; 联合国商品贸易统计数据库（UN Comtrade）</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>可追溯</t>
         </is>
@@ -13096,21 +13207,26 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
+          <t>TRD_001; TRD_003; CASE_007; SNE_001; WB_001</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
           <t>NEWS_006; NEWS_007</t>
         </is>
       </c>
-      <c r="E23" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>东方财富网; 腾讯新闻</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="F23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>C114通信网; SNE Research; 世界银行（World Bank）; 联合国商品贸易统计数据库（UN Comtrade）</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>可追溯</t>
         </is>
@@ -13134,21 +13250,26 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
+          <t>TRD_001; TRD_003; CASE_007; SNE_001; WB_001</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
           <t>NEWS_006; NEWS_007</t>
         </is>
       </c>
-      <c r="E24" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>东方财富网; 腾讯新闻</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="F24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>C114通信网; SNE Research; 世界银行（World Bank）; 联合国商品贸易统计数据库（UN Comtrade）</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
         <is>
           <t>可追溯</t>
         </is>
@@ -13172,21 +13293,26 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
+          <t>TRD_001; TRD_003; CASE_007; SNE_001; WB_001</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
           <t>NEWS_006; NEWS_007</t>
         </is>
       </c>
-      <c r="E25" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>东方财富网; 腾讯新闻</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="F25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>C114通信网; SNE Research; 世界银行（World Bank）; 联合国商品贸易统计数据库（UN Comtrade）</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>可追溯</t>
         </is>
@@ -13210,21 +13336,26 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
+          <t>TRD_001; TRD_003; CASE_007; SNE_001; WB_001</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
           <t>NEWS_006; NEWS_007</t>
         </is>
       </c>
-      <c r="E26" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>东方财富网; 腾讯新闻</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="F26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>C114通信网; SNE Research; 世界银行（World Bank）; 联合国商品贸易统计数据库（UN Comtrade）</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>可追溯</t>
         </is>
@@ -13248,21 +13379,26 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
+          <t>TRD_001; CASE_004; EU_003; IEA_001; WB_001</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
           <t>NEWS_008</t>
         </is>
       </c>
-      <c r="E27" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>澎湃新闻</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="F27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>世界银行（World Bank）; 国盛证券（经腾讯新闻转载）; 国际能源署（IEA）; 欧盟委员会（EUR-Lex / Official Journal）; 联合国商品贸易统计数据库（UN Comtrade）</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
         <is>
           <t>可追溯</t>
         </is>
@@ -13286,21 +13422,26 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
+          <t>TRD_001; CASE_004; EU_003; IEA_001; WB_001</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
           <t>NEWS_008</t>
         </is>
       </c>
-      <c r="E28" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>澎湃新闻</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="F28" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>世界银行（World Bank）; 国盛证券（经腾讯新闻转载）; 国际能源署（IEA）; 欧盟委员会（EUR-Lex / Official Journal）; 联合国商品贸易统计数据库（UN Comtrade）</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>可追溯</t>
         </is>
@@ -13324,21 +13465,26 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
+          <t>TRD_001; CASE_004; EU_003; IEA_001; WB_001</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
           <t>NEWS_008</t>
         </is>
       </c>
-      <c r="E29" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>澎湃新闻</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="F29" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>世界银行（World Bank）; 国盛证券（经腾讯新闻转载）; 国际能源署（IEA）; 欧盟委员会（EUR-Lex / Official Journal）; 联合国商品贸易统计数据库（UN Comtrade）</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>可追溯</t>
         </is>
@@ -13362,21 +13508,26 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
+          <t>TRD_001; CASE_004; EU_003; IEA_001; WB_001</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
           <t>NEWS_008</t>
         </is>
       </c>
-      <c r="E30" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>澎湃新闻</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="F30" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>世界银行（World Bank）; 国盛证券（经腾讯新闻转载）; 国际能源署（IEA）; 欧盟委员会（EUR-Lex / Official Journal）; 联合国商品贸易统计数据库（UN Comtrade）</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
         <is>
           <t>可追溯</t>
         </is>
@@ -13400,21 +13551,26 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
+          <t>TRD_001; CASE_004; EU_003; IEA_001; WB_001</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
           <t>NEWS_008</t>
         </is>
       </c>
-      <c r="E31" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>澎湃新闻</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="F31" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>世界银行（World Bank）; 国盛证券（经腾讯新闻转载）; 国际能源署（IEA）; 欧盟委员会（EUR-Lex / Official Journal）; 联合国商品贸易统计数据库（UN Comtrade）</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
         <is>
           <t>可追溯</t>
         </is>
@@ -13438,21 +13594,26 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
+          <t>WTO_004; TRD_003; SNE_001; WB_001</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
           <t>NEWS_009</t>
         </is>
       </c>
-      <c r="E32" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>新浪财经</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="F32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>SNE Research; 世界贸易组织（WTO）; 世界银行（World Bank）; 联合国商品贸易统计数据库（UN Comtrade）</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
         <is>
           <t>可追溯</t>
         </is>
@@ -13476,21 +13637,26 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
+          <t>WTO_004; TRD_003; SNE_001; WB_001</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
           <t>NEWS_009</t>
         </is>
       </c>
-      <c r="E33" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>新浪财经</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="F33" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>SNE Research; 世界贸易组织（WTO）; 世界银行（World Bank）; 联合国商品贸易统计数据库（UN Comtrade）</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
         <is>
           <t>可追溯</t>
         </is>
@@ -13514,21 +13680,26 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
+          <t>WTO_004; TRD_003; SNE_001; WB_001</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
           <t>NEWS_009</t>
         </is>
       </c>
-      <c r="E34" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>新浪财经</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="F34" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>SNE Research; 世界贸易组织（WTO）; 世界银行（World Bank）; 联合国商品贸易统计数据库（UN Comtrade）</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
         <is>
           <t>可追溯</t>
         </is>
@@ -13552,21 +13723,26 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
+          <t>WTO_004; TRD_003; SNE_001; WB_001</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
           <t>NEWS_009</t>
         </is>
       </c>
-      <c r="E35" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>新浪财经</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="F35" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>SNE Research; 世界贸易组织（WTO）; 世界银行（World Bank）; 联合国商品贸易统计数据库（UN Comtrade）</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
         <is>
           <t>可追溯</t>
         </is>
@@ -13590,21 +13766,26 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
+          <t>WTO_004; TRD_003; SNE_001; WB_001</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
           <t>NEWS_009</t>
         </is>
       </c>
-      <c r="E36" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>新浪财经</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="F36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>SNE Research; 世界贸易组织（WTO）; 世界银行（World Bank）; 联合国商品贸易统计数据库（UN Comtrade）</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
         <is>
           <t>可追溯</t>
         </is>
@@ -13628,21 +13809,26 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
+          <t>WTO_004; TRD_003; SNE_001; WB_001</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
           <t>NEWS_010; NEWS_011</t>
         </is>
       </c>
-      <c r="E37" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>和讯网; 网易</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="F37" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>SNE Research; 世界贸易组织（WTO）; 世界银行（World Bank）; 联合国商品贸易统计数据库（UN Comtrade）</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
         <is>
           <t>可追溯</t>
         </is>
@@ -13666,21 +13852,26 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
+          <t>WTO_004; TRD_003; SNE_001; WB_001</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
           <t>NEWS_010; NEWS_011</t>
         </is>
       </c>
-      <c r="E38" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>和讯网; 网易</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="F38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>SNE Research; 世界贸易组织（WTO）; 世界银行（World Bank）; 联合国商品贸易统计数据库（UN Comtrade）</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
         <is>
           <t>可追溯</t>
         </is>
@@ -13704,21 +13895,26 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
+          <t>WTO_004; TRD_003; SNE_001; WB_001</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
           <t>NEWS_010; NEWS_011</t>
         </is>
       </c>
-      <c r="E39" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>和讯网; 网易</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="F39" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>SNE Research; 世界贸易组织（WTO）; 世界银行（World Bank）; 联合国商品贸易统计数据库（UN Comtrade）</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
         <is>
           <t>可追溯</t>
         </is>
@@ -13742,21 +13938,26 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
+          <t>WTO_004; TRD_003; SNE_001; WB_001</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
           <t>NEWS_010; NEWS_011</t>
         </is>
       </c>
-      <c r="E40" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>和讯网; 网易</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="F40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>SNE Research; 世界贸易组织（WTO）; 世界银行（World Bank）; 联合国商品贸易统计数据库（UN Comtrade）</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
         <is>
           <t>可追溯</t>
         </is>
@@ -13780,21 +13981,26 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
+          <t>WTO_004; TRD_003; SNE_001; WB_001</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
           <t>NEWS_010; NEWS_011</t>
         </is>
       </c>
-      <c r="E41" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>和讯网; 网易</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="F41" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>SNE Research; 世界贸易组织（WTO）; 世界银行（World Bank）; 联合国商品贸易统计数据库（UN Comtrade）</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
         <is>
           <t>可追溯</t>
         </is>
@@ -13818,21 +14024,26 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
+          <t>EU_003; EU_001; EU_004; EU_002; SNE_001; IEA_001</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
           <t>NEWS_012; NEWS_013</t>
         </is>
       </c>
-      <c r="E42" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>新浪财经; 每日经济新闻</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="F42" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>SNE Research; 国际能源署（IEA）; 欧洲议会与欧盟理事会（EUR-Lex / Official Journal）; 欧盟委员会（EUR-Lex / Official Journal）</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
         <is>
           <t>可追溯</t>
         </is>
@@ -13856,21 +14067,26 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
+          <t>EU_003; EU_001; EU_004; EU_002; SNE_001; IEA_001</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
           <t>NEWS_012; NEWS_013</t>
         </is>
       </c>
-      <c r="E43" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>新浪财经; 每日经济新闻</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="F43" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>SNE Research; 国际能源署（IEA）; 欧洲议会与欧盟理事会（EUR-Lex / Official Journal）; 欧盟委员会（EUR-Lex / Official Journal）</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
         <is>
           <t>可追溯</t>
         </is>
@@ -13894,21 +14110,26 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
+          <t>EU_003; EU_001; EU_004; EU_002; SNE_001; IEA_001</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
           <t>NEWS_012; NEWS_013</t>
         </is>
       </c>
-      <c r="E44" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>新浪财经; 每日经济新闻</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="F44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>SNE Research; 国际能源署（IEA）; 欧洲议会与欧盟理事会（EUR-Lex / Official Journal）; 欧盟委员会（EUR-Lex / Official Journal）</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
         <is>
           <t>可追溯</t>
         </is>
@@ -13932,21 +14153,26 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
+          <t>EU_003; EU_001; EU_004; EU_002; SNE_001; IEA_001</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
           <t>NEWS_012; NEWS_013</t>
         </is>
       </c>
-      <c r="E45" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>新浪财经; 每日经济新闻</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="F45" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>SNE Research; 国际能源署（IEA）; 欧洲议会与欧盟理事会（EUR-Lex / Official Journal）; 欧盟委员会（EUR-Lex / Official Journal）</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
         <is>
           <t>可追溯</t>
         </is>
@@ -13970,21 +14196,26 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
+          <t>EU_003; EU_001; EU_004; EU_002; SNE_001; IEA_001</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
           <t>NEWS_012; NEWS_013</t>
         </is>
       </c>
-      <c r="E46" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>新浪财经; 每日经济新闻</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="F46" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>SNE Research; 国际能源署（IEA）; 欧洲议会与欧盟理事会（EUR-Lex / Official Journal）; 欧盟委员会（EUR-Lex / Official Journal）</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
         <is>
           <t>可追溯</t>
         </is>
@@ -14008,21 +14239,26 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
+          <t>WTO_004; TRD_003; SNE_001; IEA_001</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
           <t>NEWS_014</t>
         </is>
       </c>
-      <c r="E47" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>东方财富网</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="F47" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>SNE Research; 世界贸易组织（WTO）; 国际能源署（IEA）; 联合国商品贸易统计数据库（UN Comtrade）</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
         <is>
           <t>可追溯</t>
         </is>
@@ -14046,21 +14282,26 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
+          <t>WTO_004; TRD_003; SNE_001; IEA_001</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
           <t>NEWS_014</t>
         </is>
       </c>
-      <c r="E48" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>东方财富网</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="F48" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>SNE Research; 世界贸易组织（WTO）; 国际能源署（IEA）; 联合国商品贸易统计数据库（UN Comtrade）</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
         <is>
           <t>可追溯</t>
         </is>
@@ -14084,21 +14325,26 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
+          <t>WTO_004; TRD_003; SNE_001; IEA_001</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
           <t>NEWS_014</t>
         </is>
       </c>
-      <c r="E49" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>东方财富网</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="F49" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>SNE Research; 世界贸易组织（WTO）; 国际能源署（IEA）; 联合国商品贸易统计数据库（UN Comtrade）</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
         <is>
           <t>可追溯</t>
         </is>
@@ -14122,21 +14368,26 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
+          <t>WTO_004; TRD_003; SNE_001; IEA_001</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
           <t>NEWS_014</t>
         </is>
       </c>
-      <c r="E50" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>东方财富网</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="F50" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>SNE Research; 世界贸易组织（WTO）; 国际能源署（IEA）; 联合国商品贸易统计数据库（UN Comtrade）</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
         <is>
           <t>可追溯</t>
         </is>
@@ -14160,21 +14411,26 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
+          <t>WTO_004; TRD_003; SNE_001; IEA_001</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
           <t>NEWS_014</t>
         </is>
       </c>
-      <c r="E51" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>东方财富网</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="F51" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>SNE Research; 世界贸易组织（WTO）; 国际能源署（IEA）; 联合国商品贸易统计数据库（UN Comtrade）</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
         <is>
           <t>可追溯</t>
         </is>
@@ -14198,21 +14454,26 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
+          <t>WTO_004; IEA_001; SNE_001; TRD_003; EU_003</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
           <t>NEWS_015; NEWS_024; NEWS_025</t>
         </is>
       </c>
-      <c r="E52" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>ANTARA（印尼国家通讯社）; 凤凰科技</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="F52" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>SNE Research; 世界贸易组织（WTO）; 国际能源署（IEA）; 欧盟委员会（EUR-Lex / Official Journal）; 联合国商品贸易统计数据库（UN Comtrade）</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
         <is>
           <t>可追溯</t>
         </is>
@@ -14236,21 +14497,26 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
+          <t>WTO_004; IEA_001; SNE_001; TRD_003; EU_003</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
           <t>NEWS_015; NEWS_024; NEWS_025</t>
         </is>
       </c>
-      <c r="E53" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>ANTARA（印尼国家通讯社）; 凤凰科技</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="F53" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>SNE Research; 世界贸易组织（WTO）; 国际能源署（IEA）; 欧盟委员会（EUR-Lex / Official Journal）; 联合国商品贸易统计数据库（UN Comtrade）</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
         <is>
           <t>可追溯</t>
         </is>
@@ -14274,21 +14540,26 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
+          <t>WTO_004; IEA_001; SNE_001; TRD_003; EU_003</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
           <t>NEWS_015; NEWS_024; NEWS_025</t>
         </is>
       </c>
-      <c r="E54" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>ANTARA（印尼国家通讯社）; 凤凰科技</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="F54" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>SNE Research; 世界贸易组织（WTO）; 国际能源署（IEA）; 欧盟委员会（EUR-Lex / Official Journal）; 联合国商品贸易统计数据库（UN Comtrade）</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
         <is>
           <t>可追溯</t>
         </is>
@@ -14312,21 +14583,26 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
+          <t>WTO_004; IEA_001; SNE_001; TRD_003; EU_003</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
           <t>NEWS_015; NEWS_024; NEWS_025</t>
         </is>
       </c>
-      <c r="E55" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>ANTARA（印尼国家通讯社）; 凤凰科技</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="F55" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>SNE Research; 世界贸易组织（WTO）; 国际能源署（IEA）; 欧盟委员会（EUR-Lex / Official Journal）; 联合国商品贸易统计数据库（UN Comtrade）</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
         <is>
           <t>可追溯</t>
         </is>
@@ -14350,21 +14626,26 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
+          <t>WTO_004; IEA_001; SNE_001; TRD_003; EU_003</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
           <t>NEWS_015; NEWS_024; NEWS_025</t>
         </is>
       </c>
-      <c r="E56" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>ANTARA（印尼国家通讯社）; 凤凰科技</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="F56" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>SNE Research; 世界贸易组织（WTO）; 国际能源署（IEA）; 欧盟委员会（EUR-Lex / Official Journal）; 联合国商品贸易统计数据库（UN Comtrade）</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
         <is>
           <t>可追溯</t>
         </is>
@@ -14388,21 +14669,26 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
+          <t>DOC_001; CASE_002; CASE_003; TRD_002</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
           <t>NEWS_016</t>
         </is>
       </c>
-      <c r="E57" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>东方财富财富号</t>
-        </is>
-      </c>
-      <c r="G57" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="F57" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>美国商务部; 美国商务部（经律所解读）; 联合国商品贸易统计数据库（UN Comtrade）</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
         <is>
           <t>可追溯</t>
         </is>
@@ -14426,21 +14712,26 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
+          <t>DOC_001; CASE_002; CASE_003; TRD_002</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
           <t>NEWS_016</t>
         </is>
       </c>
-      <c r="E58" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>东方财富财富号</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="F58" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>美国商务部; 美国商务部（经律所解读）; 联合国商品贸易统计数据库（UN Comtrade）</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
         <is>
           <t>可追溯</t>
         </is>
@@ -14464,21 +14755,26 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
+          <t>DOC_001; CASE_002; CASE_003; TRD_002</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
           <t>NEWS_016</t>
         </is>
       </c>
-      <c r="E59" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>东方财富财富号</t>
-        </is>
-      </c>
-      <c r="G59" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="F59" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>美国商务部; 美国商务部（经律所解读）; 联合国商品贸易统计数据库（UN Comtrade）</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
         <is>
           <t>可追溯</t>
         </is>
@@ -14502,21 +14798,26 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
+          <t>DOC_001; CASE_002; CASE_003; TRD_002</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
           <t>NEWS_016</t>
         </is>
       </c>
-      <c r="E60" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>东方财富财富号</t>
-        </is>
-      </c>
-      <c r="G60" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="F60" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>美国商务部; 美国商务部（经律所解读）; 联合国商品贸易统计数据库（UN Comtrade）</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
         <is>
           <t>可追溯</t>
         </is>
@@ -14540,21 +14841,26 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
+          <t>DOC_001; CASE_002; CASE_003; TRD_002</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
           <t>NEWS_016</t>
         </is>
       </c>
-      <c r="E61" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>东方财富财富号</t>
-        </is>
-      </c>
-      <c r="G61" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="F61" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>美国商务部; 美国商务部（经律所解读）; 联合国商品贸易统计数据库（UN Comtrade）</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
         <is>
           <t>可追溯</t>
         </is>
@@ -14578,21 +14884,26 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
+          <t>UNCTAD_001; TRD_003; WB_001; IMF_001</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
           <t>NEWS_017</t>
         </is>
       </c>
-      <c r="E62" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F62" s="2" t="inlineStr">
-        <is>
-          <t>新浪财经</t>
-        </is>
-      </c>
-      <c r="G62" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="F62" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>世界银行（World Bank）; 国际货币基金组织（IMF）; 联合国商品贸易统计数据库（UN Comtrade）; 联合国贸易和发展会议（UNCTAD）</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
         <is>
           <t>可追溯</t>
         </is>
@@ -14616,21 +14927,26 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
+          <t>UNCTAD_001; TRD_003; WB_001; IMF_001</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
           <t>NEWS_017</t>
         </is>
       </c>
-      <c r="E63" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F63" s="2" t="inlineStr">
-        <is>
-          <t>新浪财经</t>
-        </is>
-      </c>
-      <c r="G63" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="F63" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>世界银行（World Bank）; 国际货币基金组织（IMF）; 联合国商品贸易统计数据库（UN Comtrade）; 联合国贸易和发展会议（UNCTAD）</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
         <is>
           <t>可追溯</t>
         </is>
@@ -14654,21 +14970,26 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
+          <t>UNCTAD_001; TRD_003; WB_001; IMF_001</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
           <t>NEWS_017</t>
         </is>
       </c>
-      <c r="E64" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>新浪财经</t>
-        </is>
-      </c>
-      <c r="G64" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="F64" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>世界银行（World Bank）; 国际货币基金组织（IMF）; 联合国商品贸易统计数据库（UN Comtrade）; 联合国贸易和发展会议（UNCTAD）</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
         <is>
           <t>可追溯</t>
         </is>
@@ -14692,21 +15013,26 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
+          <t>UNCTAD_001; TRD_003; WB_001; IMF_001</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
           <t>NEWS_017</t>
         </is>
       </c>
-      <c r="E65" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F65" s="2" t="inlineStr">
-        <is>
-          <t>新浪财经</t>
-        </is>
-      </c>
-      <c r="G65" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="F65" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>世界银行（World Bank）; 国际货币基金组织（IMF）; 联合国商品贸易统计数据库（UN Comtrade）; 联合国贸易和发展会议（UNCTAD）</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
         <is>
           <t>可追溯</t>
         </is>
@@ -14730,21 +15056,26 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
+          <t>UNCTAD_001; TRD_003; WB_001; IMF_001</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
           <t>NEWS_017</t>
         </is>
       </c>
-      <c r="E66" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F66" s="2" t="inlineStr">
-        <is>
-          <t>新浪财经</t>
-        </is>
-      </c>
-      <c r="G66" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="F66" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>世界银行（World Bank）; 国际货币基金组织（IMF）; 联合国商品贸易统计数据库（UN Comtrade）; 联合国贸易和发展会议（UNCTAD）</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
         <is>
           <t>可追溯</t>
         </is>
@@ -14768,21 +15099,26 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
+          <t>CASE_001; TRD_003; WB_001; SNE_001</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
           <t>COMPANY_FILING_001; NEWS_018</t>
         </is>
       </c>
-      <c r="E67" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F67" s="2" t="inlineStr">
-        <is>
-          <t>央广网; 恩捷股份公告（经东方财富网报道）</t>
-        </is>
-      </c>
-      <c r="G67" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="F67" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>SNE Research; 世界银行（World Bank）; 联合国商品贸易统计数据库（UN Comtrade）; 路透社（Reuters）</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
         <is>
           <t>可追溯</t>
         </is>
@@ -14806,21 +15142,26 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
+          <t>CASE_001; TRD_003; WB_001; SNE_001</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
           <t>COMPANY_FILING_001; NEWS_018</t>
         </is>
       </c>
-      <c r="E68" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F68" s="2" t="inlineStr">
-        <is>
-          <t>央广网; 恩捷股份公告（经东方财富网报道）</t>
-        </is>
-      </c>
-      <c r="G68" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="F68" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>SNE Research; 世界银行（World Bank）; 联合国商品贸易统计数据库（UN Comtrade）; 路透社（Reuters）</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
         <is>
           <t>可追溯</t>
         </is>
@@ -14844,21 +15185,26 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
+          <t>CASE_001; TRD_003; WB_001; SNE_001</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
           <t>COMPANY_FILING_001; NEWS_018</t>
         </is>
       </c>
-      <c r="E69" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F69" s="2" t="inlineStr">
-        <is>
-          <t>央广网; 恩捷股份公告（经东方财富网报道）</t>
-        </is>
-      </c>
-      <c r="G69" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="F69" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>SNE Research; 世界银行（World Bank）; 联合国商品贸易统计数据库（UN Comtrade）; 路透社（Reuters）</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
         <is>
           <t>可追溯</t>
         </is>
@@ -14882,21 +15228,26 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
+          <t>CASE_001; TRD_003; WB_001; SNE_001</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
           <t>COMPANY_FILING_001; NEWS_018</t>
         </is>
       </c>
-      <c r="E70" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t>央广网; 恩捷股份公告（经东方财富网报道）</t>
-        </is>
-      </c>
-      <c r="G70" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="F70" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>SNE Research; 世界银行（World Bank）; 联合国商品贸易统计数据库（UN Comtrade）; 路透社（Reuters）</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
         <is>
           <t>可追溯</t>
         </is>
@@ -14920,21 +15271,26 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
+          <t>CASE_001; TRD_003; WB_001; SNE_001</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
           <t>COMPANY_FILING_001; NEWS_018</t>
         </is>
       </c>
-      <c r="E71" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F71" s="2" t="inlineStr">
-        <is>
-          <t>央广网; 恩捷股份公告（经东方财富网报道）</t>
-        </is>
-      </c>
-      <c r="G71" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="F71" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>SNE Research; 世界银行（World Bank）; 联合国商品贸易统计数据库（UN Comtrade）; 路透社（Reuters）</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
         <is>
           <t>可追溯</t>
         </is>
@@ -14958,21 +15314,26 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
+          <t>UNCTAD_001; WTO_002; WTO_003; CASE_001</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
           <t>NEWS_019; NEWS_020</t>
         </is>
       </c>
-      <c r="E72" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>中关村在线; 新浪科技</t>
-        </is>
-      </c>
-      <c r="G72" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="F72" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>世界贸易组织（WTO）; 联合国贸易和发展会议（UNCTAD）; 路透社（Reuters）</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
         <is>
           <t>可追溯</t>
         </is>
@@ -14996,21 +15357,26 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
+          <t>UNCTAD_001; WTO_002; WTO_003; CASE_001</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
           <t>NEWS_019; NEWS_020</t>
         </is>
       </c>
-      <c r="E73" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F73" s="2" t="inlineStr">
-        <is>
-          <t>中关村在线; 新浪科技</t>
-        </is>
-      </c>
-      <c r="G73" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="F73" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>世界贸易组织（WTO）; 联合国贸易和发展会议（UNCTAD）; 路透社（Reuters）</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
         <is>
           <t>可追溯</t>
         </is>
@@ -15034,21 +15400,26 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
+          <t>UNCTAD_001; WTO_002; WTO_003; CASE_001</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
           <t>NEWS_019; NEWS_020</t>
         </is>
       </c>
-      <c r="E74" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F74" s="2" t="inlineStr">
-        <is>
-          <t>中关村在线; 新浪科技</t>
-        </is>
-      </c>
-      <c r="G74" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="F74" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>世界贸易组织（WTO）; 联合国贸易和发展会议（UNCTAD）; 路透社（Reuters）</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
         <is>
           <t>可追溯</t>
         </is>
@@ -15072,21 +15443,26 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
+          <t>UNCTAD_001; WTO_002; WTO_003; CASE_001</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
           <t>NEWS_019; NEWS_020</t>
         </is>
       </c>
-      <c r="E75" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F75" s="2" t="inlineStr">
-        <is>
-          <t>中关村在线; 新浪科技</t>
-        </is>
-      </c>
-      <c r="G75" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="F75" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>世界贸易组织（WTO）; 联合国贸易和发展会议（UNCTAD）; 路透社（Reuters）</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
         <is>
           <t>可追溯</t>
         </is>
@@ -15110,21 +15486,26 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
+          <t>UNCTAD_001; WTO_002; WTO_003; CASE_001</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
           <t>NEWS_019; NEWS_020</t>
         </is>
       </c>
-      <c r="E76" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F76" s="2" t="inlineStr">
-        <is>
-          <t>中关村在线; 新浪科技</t>
-        </is>
-      </c>
-      <c r="G76" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="F76" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>世界贸易组织（WTO）; 联合国贸易和发展会议（UNCTAD）; 路透社（Reuters）</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
         <is>
           <t>可追溯</t>
         </is>
@@ -15148,21 +15529,26 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
+          <t>CASE_001; WB_001; TRD_001; KPMG_001</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
           <t>REUTERS_001; NEWS_023</t>
         </is>
       </c>
-      <c r="E77" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F77" s="2" t="inlineStr">
-        <is>
-          <t>中国储能网; 路透社（经环球网转载）</t>
-        </is>
-      </c>
-      <c r="G77" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="F77" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>世界银行（World Bank）; 毕马威（KPMG）; 联合国商品贸易统计数据库（UN Comtrade）; 路透社（Reuters）</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
         <is>
           <t>可追溯</t>
         </is>
@@ -15186,21 +15572,26 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
+          <t>CASE_001; WB_001; TRD_001; KPMG_001</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
           <t>REUTERS_001; NEWS_023</t>
         </is>
       </c>
-      <c r="E78" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F78" s="2" t="inlineStr">
-        <is>
-          <t>中国储能网; 路透社（经环球网转载）</t>
-        </is>
-      </c>
-      <c r="G78" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="F78" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>世界银行（World Bank）; 毕马威（KPMG）; 联合国商品贸易统计数据库（UN Comtrade）; 路透社（Reuters）</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
         <is>
           <t>可追溯</t>
         </is>
@@ -15224,21 +15615,26 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
+          <t>CASE_001; WB_001; TRD_001; KPMG_001</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
           <t>REUTERS_001; NEWS_023</t>
         </is>
       </c>
-      <c r="E79" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F79" s="2" t="inlineStr">
-        <is>
-          <t>中国储能网; 路透社（经环球网转载）</t>
-        </is>
-      </c>
-      <c r="G79" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="F79" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>世界银行（World Bank）; 毕马威（KPMG）; 联合国商品贸易统计数据库（UN Comtrade）; 路透社（Reuters）</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
         <is>
           <t>可追溯</t>
         </is>
@@ -15262,21 +15658,26 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
+          <t>CASE_001; WB_001; TRD_001; KPMG_001</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
           <t>REUTERS_001; NEWS_023</t>
         </is>
       </c>
-      <c r="E80" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F80" s="2" t="inlineStr">
-        <is>
-          <t>中国储能网; 路透社（经环球网转载）</t>
-        </is>
-      </c>
-      <c r="G80" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="F80" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>世界银行（World Bank）; 毕马威（KPMG）; 联合国商品贸易统计数据库（UN Comtrade）; 路透社（Reuters）</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
         <is>
           <t>可追溯</t>
         </is>
@@ -15300,21 +15701,26 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
+          <t>CASE_001; WB_001; TRD_001; KPMG_001</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
           <t>REUTERS_001; NEWS_023</t>
         </is>
       </c>
-      <c r="E81" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F81" s="2" t="inlineStr">
-        <is>
-          <t>中国储能网; 路透社（经环球网转载）</t>
-        </is>
-      </c>
-      <c r="G81" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="F81" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>世界银行（World Bank）; 毕马威（KPMG）; 联合国商品贸易统计数据库（UN Comtrade）; 路透社（Reuters）</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
         <is>
           <t>可追溯</t>
         </is>
@@ -15338,21 +15744,26 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
+          <t>EU_003; EU_001; EU_004; CASE_001</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
           <t>NEWS_021; NEWS_022</t>
         </is>
       </c>
-      <c r="E82" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F82" s="2" t="inlineStr">
-        <is>
-          <t>36氪; 财新网</t>
-        </is>
-      </c>
-      <c r="G82" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="F82" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）; 欧盟委员会（EUR-Lex / Official Journal）; 路透社（Reuters）</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
         <is>
           <t>可追溯</t>
         </is>
@@ -15376,21 +15787,26 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
+          <t>EU_003; EU_001; EU_004; CASE_001</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
           <t>NEWS_021; NEWS_022</t>
         </is>
       </c>
-      <c r="E83" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F83" s="2" t="inlineStr">
-        <is>
-          <t>36氪; 财新网</t>
-        </is>
-      </c>
-      <c r="G83" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="F83" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）; 欧盟委员会（EUR-Lex / Official Journal）; 路透社（Reuters）</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
         <is>
           <t>可追溯</t>
         </is>
@@ -15414,21 +15830,26 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
+          <t>EU_003; EU_001; EU_004; CASE_001</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
           <t>NEWS_021; NEWS_022</t>
         </is>
       </c>
-      <c r="E84" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F84" s="2" t="inlineStr">
-        <is>
-          <t>36氪; 财新网</t>
-        </is>
-      </c>
-      <c r="G84" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="F84" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）; 欧盟委员会（EUR-Lex / Official Journal）; 路透社（Reuters）</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
         <is>
           <t>可追溯</t>
         </is>
@@ -15452,21 +15873,26 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
+          <t>EU_003; EU_001; EU_004; CASE_001</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
           <t>NEWS_021; NEWS_022</t>
         </is>
       </c>
-      <c r="E85" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F85" s="2" t="inlineStr">
-        <is>
-          <t>36氪; 财新网</t>
-        </is>
-      </c>
-      <c r="G85" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="F85" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）; 欧盟委员会（EUR-Lex / Official Journal）; 路透社（Reuters）</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
         <is>
           <t>可追溯</t>
         </is>
@@ -15490,21 +15916,26 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
+          <t>EU_003; EU_001; EU_004; CASE_001</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
           <t>NEWS_021; NEWS_022</t>
         </is>
       </c>
-      <c r="E86" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F86" s="2" t="inlineStr">
-        <is>
-          <t>36氪; 财新网</t>
-        </is>
-      </c>
-      <c r="G86" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="F86" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）; 欧盟委员会（EUR-Lex / Official Journal）; 路透社（Reuters）</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
         <is>
           <t>可追溯</t>
         </is>

--- a/data/evaluation/evidence_quality_test.xlsx
+++ b/data/evaluation/evidence_quality_test.xlsx
@@ -655,17 +655,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>CASE_004</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>国盛证券（经腾讯新闻转载）</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>https://news.qq.com/rain/a/20251130A04A7P00</t>
+          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
         </is>
       </c>
     </row>
@@ -769,7 +769,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>持续更新</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -794,7 +794,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org</t>
+          <t>https://comtradeplus.un.org/TradeFlow?Frequency=A&amp;Flows=X&amp;CommodityCodes=850760,870380&amp;Partners=842&amp;Reporters=156,458,764,704&amp;period=2018,2019,2020,2021,2022,2023,2024,2025&amp;partner2=0&amp;output=default&amp;AggregateBy=none&amp;BreakdownMode=plus</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>持续更新</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org</t>
+          <t>https://comtradeplus.un.org/TradeFlow?Frequency=A&amp;Flows=X&amp;CommodityCodes=8541,8542&amp;Partners=842&amp;Reporters=156,458,764,704&amp;period=2018,2019,2020,2021,2022,2023,2024,2025&amp;partner2=0&amp;output=default&amp;AggregateBy=none&amp;BreakdownMode=plus</t>
         </is>
       </c>
     </row>
@@ -863,17 +863,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>CASE_004</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>国盛证券（经腾讯新闻转载）</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>https://news.qq.com/rain/a/20251130A04A7P00</t>
+          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
         </is>
       </c>
     </row>
@@ -925,7 +925,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>持续更新</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -950,7 +950,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org</t>
+          <t>https://comtradeplus.un.org/TradeFlow?Frequency=A&amp;Flows=X&amp;CommodityCodes=850760,870380&amp;Partners=842&amp;Reporters=156,458,764,704&amp;period=2018,2019,2020,2021,2022,2023,2024,2025&amp;partner2=0&amp;output=default&amp;AggregateBy=none&amp;BreakdownMode=plus</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>持续更新</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org</t>
+          <t>https://comtradeplus.un.org/TradeFlow?Frequency=A&amp;Flows=X&amp;CommodityCodes=8541,8542&amp;Partners=842&amp;Reporters=156,458,764,704&amp;period=2018,2019,2020,2021,2022,2023,2024,2025&amp;partner2=0&amp;output=default&amp;AggregateBy=none&amp;BreakdownMode=plus</t>
         </is>
       </c>
     </row>
@@ -1071,17 +1071,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>CASE_004</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>国盛证券（经腾讯新闻转载）</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>https://news.qq.com/rain/a/20251130A04A7P00</t>
+          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
         </is>
       </c>
     </row>
@@ -1123,17 +1123,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>CASE_004</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>国盛证券（经腾讯新闻转载）</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2025-11-30</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1158,7 +1158,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
+          <t>https://news.qq.com/rain/a/20251130A04A7P00</t>
         </is>
       </c>
     </row>
@@ -1237,7 +1237,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>持续更新</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1262,7 +1262,7 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org</t>
+          <t>https://comtradeplus.un.org/TradeFlow?Frequency=A&amp;Flows=X&amp;CommodityCodes=850760,870380&amp;Partners=842&amp;Reporters=156,458,764,704&amp;period=2018,2019,2020,2021,2022,2023,2024,2025&amp;partner2=0&amp;output=default&amp;AggregateBy=none&amp;BreakdownMode=plus</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>持续更新</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org</t>
+          <t>https://comtradeplus.un.org/TradeFlow?Frequency=A&amp;Flows=X&amp;CommodityCodes=8541,8542&amp;Partners=842&amp;Reporters=156,458,764,704&amp;period=2018,2019,2020,2021,2022,2023,2024,2025&amp;partner2=0&amp;output=default&amp;AggregateBy=none&amp;BreakdownMode=plus</t>
         </is>
       </c>
     </row>
@@ -1331,17 +1331,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>CASE_004</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>国盛证券（经腾讯新闻转载）</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1366,7 +1366,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>https://news.qq.com/rain/a/20251130A04A7P00</t>
+          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
         </is>
       </c>
     </row>
@@ -1383,17 +1383,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>CASE_004</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>国盛证券（经腾讯新闻转载）</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2025-11-30</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
+          <t>https://news.qq.com/rain/a/20251130A04A7P00</t>
         </is>
       </c>
     </row>
@@ -1497,7 +1497,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>持续更新</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1522,7 +1522,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org</t>
+          <t>https://comtradeplus.un.org/TradeFlow?Frequency=A&amp;Flows=X&amp;CommodityCodes=850760,870380&amp;Partners=842&amp;Reporters=156,458,764,704&amp;period=2018,2019,2020,2021,2022,2023,2024,2025&amp;partner2=0&amp;output=default&amp;AggregateBy=none&amp;BreakdownMode=plus</t>
         </is>
       </c>
     </row>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>持续更新</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org</t>
+          <t>https://comtradeplus.un.org/TradeFlow?Frequency=A&amp;Flows=X&amp;CommodityCodes=8541,8542&amp;Partners=842&amp;Reporters=156,458,764,704&amp;period=2018,2019,2020,2021,2022,2023,2024,2025&amp;partner2=0&amp;output=default&amp;AggregateBy=none&amp;BreakdownMode=plus</t>
         </is>
       </c>
     </row>
@@ -1757,7 +1757,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>持续更新</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org</t>
+          <t>https://comtradeplus.un.org/TradeFlow?Frequency=A&amp;Flows=X&amp;CommodityCodes=850760,870380&amp;Partners=842&amp;Reporters=156,458,764,704&amp;period=2018,2019,2020,2021,2022,2023,2024,2025&amp;partner2=0&amp;output=default&amp;AggregateBy=none&amp;BreakdownMode=plus</t>
         </is>
       </c>
     </row>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>持续更新</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org</t>
+          <t>https://comtradeplus.un.org/TradeFlow?Frequency=A&amp;Flows=X&amp;CommodityCodes=8541,8542&amp;Partners=842&amp;Reporters=156,458,764,704&amp;period=2018,2019,2020,2021,2022,2023,2024,2025&amp;partner2=0&amp;output=default&amp;AggregateBy=none&amp;BreakdownMode=plus</t>
         </is>
       </c>
     </row>
@@ -2017,7 +2017,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>持续更新</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2042,7 +2042,7 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org</t>
+          <t>https://comtradeplus.un.org/TradeFlow?Frequency=A&amp;Flows=X&amp;CommodityCodes=850760,870380&amp;Partners=842&amp;Reporters=156,458,764,704&amp;period=2018,2019,2020,2021,2022,2023,2024,2025&amp;partner2=0&amp;output=default&amp;AggregateBy=none&amp;BreakdownMode=plus</t>
         </is>
       </c>
     </row>
@@ -2069,7 +2069,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>持续更新</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -2094,7 +2094,7 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org</t>
+          <t>https://comtradeplus.un.org/TradeFlow?Frequency=A&amp;Flows=X&amp;CommodityCodes=8541,8542&amp;Partners=842&amp;Reporters=156,458,764,704&amp;period=2018,2019,2020,2021,2022,2023,2024,2025&amp;partner2=0&amp;output=default&amp;AggregateBy=none&amp;BreakdownMode=plus</t>
         </is>
       </c>
     </row>
@@ -2215,22 +2215,22 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>DHS_001</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>美国国土安全部（DHS，Federal Register）</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="G34" s="2" t="n">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>https://www.federalregister.gov/documents/2026/08/03/2026-15628/notice-regarding-the-uyghur-forced-labor-prevention-act-entity-list</t>
+          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
         </is>
       </c>
     </row>
@@ -2262,27 +2262,27 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>亿纬锂能 EVE Energy：Regulatory Risk</t>
+          <t>亿纬锂能 EVE Energy：Supply Chain Risk</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>DHS_001</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>美国国土安全部（DHS，Federal Register）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G35" s="2" t="n">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>https://www.federalregister.gov/documents/2026/08/03/2026-15628/notice-regarding-the-uyghur-forced-labor-prevention-act-entity-list</t>
+          <t>https://comtradeplus.un.org/TradeFlow?Frequency=A&amp;Flows=X&amp;CommodityCodes=850760,870380&amp;Partners=842&amp;Reporters=156,458,764,704&amp;period=2018,2019,2020,2021,2022,2023,2024,2025&amp;partner2=0&amp;output=default&amp;AggregateBy=none&amp;BreakdownMode=plus</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>TRD_001</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>持续更新</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org</t>
+          <t>https://comtradeplus.un.org/TradeFlow?Frequency=A&amp;Flows=X&amp;CommodityCodes=8541,8542&amp;Partners=842&amp;Reporters=156,458,764,704&amp;period=2018,2019,2020,2021,2022,2023,2024,2025&amp;partner2=0&amp;output=default&amp;AggregateBy=none&amp;BreakdownMode=plus</t>
         </is>
       </c>
     </row>
@@ -2371,22 +2371,22 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>CASE_007</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>C114通信网</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>持续更新</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="G37" s="2" t="n">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org</t>
+          <t>https://www.c114.com.cn/other/241/a1307528.html</t>
         </is>
       </c>
     </row>
@@ -2423,22 +2423,22 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>CASE_007</t>
+          <t>WB_001</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>C114通信网</t>
+          <t>世界银行（World Bank）</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2023-04-28</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G38" s="2" t="n">
@@ -2458,7 +2458,7 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>https://www.c114.com.cn/other/241/a1307528.html</t>
+          <t>https://documents.worldbank.org/curated/en/099042123145531599/pdf/P17146804a6a570ac0a4f80895e320dda1e.pdf</t>
         </is>
       </c>
     </row>
@@ -2475,22 +2475,22 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>WB_001</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>世界银行（World Bank）</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>2023-04-28</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="G39" s="2" t="n">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>https://documents.worldbank.org/curated/en/099042123145531599/pdf/P17146804a6a570ac0a4f80895e320dda1e.pdf</t>
+          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
         </is>
       </c>
     </row>
@@ -2537,7 +2537,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>持续更新</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org</t>
+          <t>https://comtradeplus.un.org/TradeFlow?Frequency=A&amp;Flows=X&amp;CommodityCodes=850760,870380&amp;Partners=842&amp;Reporters=156,458,764,704&amp;period=2018,2019,2020,2021,2022,2023,2024,2025&amp;partner2=0&amp;output=default&amp;AggregateBy=none&amp;BreakdownMode=plus</t>
         </is>
       </c>
     </row>
@@ -2589,7 +2589,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>持续更新</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -2614,7 +2614,7 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org</t>
+          <t>https://comtradeplus.un.org/TradeFlow?Frequency=A&amp;Flows=X&amp;CommodityCodes=8541,8542&amp;Partners=842&amp;Reporters=156,458,764,704&amp;period=2018,2019,2020,2021,2022,2023,2024,2025&amp;partner2=0&amp;output=default&amp;AggregateBy=none&amp;BreakdownMode=plus</t>
         </is>
       </c>
     </row>
@@ -2797,7 +2797,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>持续更新</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -2822,7 +2822,7 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org</t>
+          <t>https://comtradeplus.un.org/TradeFlow?Frequency=A&amp;Flows=X&amp;CommodityCodes=850760,870380&amp;Partners=842&amp;Reporters=156,458,764,704&amp;period=2018,2019,2020,2021,2022,2023,2024,2025&amp;partner2=0&amp;output=default&amp;AggregateBy=none&amp;BreakdownMode=plus</t>
         </is>
       </c>
     </row>
@@ -2849,7 +2849,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>持续更新</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -2874,7 +2874,7 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org</t>
+          <t>https://comtradeplus.un.org/TradeFlow?Frequency=A&amp;Flows=X&amp;CommodityCodes=8541,8542&amp;Partners=842&amp;Reporters=156,458,764,704&amp;period=2018,2019,2020,2021,2022,2023,2024,2025&amp;partner2=0&amp;output=default&amp;AggregateBy=none&amp;BreakdownMode=plus</t>
         </is>
       </c>
     </row>
@@ -3057,7 +3057,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>持续更新</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -3082,7 +3082,7 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org</t>
+          <t>https://comtradeplus.un.org/TradeFlow?Frequency=A&amp;Flows=X&amp;CommodityCodes=850760,870380&amp;Partners=842&amp;Reporters=156,458,764,704&amp;period=2018,2019,2020,2021,2022,2023,2024,2025&amp;partner2=0&amp;output=default&amp;AggregateBy=none&amp;BreakdownMode=plus</t>
         </is>
       </c>
     </row>
@@ -3109,7 +3109,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>持续更新</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -3134,7 +3134,7 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org</t>
+          <t>https://comtradeplus.un.org/TradeFlow?Frequency=A&amp;Flows=X&amp;CommodityCodes=8541,8542&amp;Partners=842&amp;Reporters=156,458,764,704&amp;period=2018,2019,2020,2021,2022,2023,2024,2025&amp;partner2=0&amp;output=default&amp;AggregateBy=none&amp;BreakdownMode=plus</t>
         </is>
       </c>
     </row>
@@ -3151,17 +3151,17 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>CASE_004</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>国盛证券（经腾讯新闻转载）</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>https://news.qq.com/rain/a/20251130A04A7P00</t>
+          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
         </is>
       </c>
     </row>
@@ -3203,17 +3203,17 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>CASE_004</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>国盛证券（经腾讯新闻转载）</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2025-11-30</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -3238,7 +3238,7 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
+          <t>https://news.qq.com/rain/a/20251130A04A7P00</t>
         </is>
       </c>
     </row>
@@ -3317,7 +3317,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>持续更新</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org</t>
+          <t>https://comtradeplus.un.org/TradeFlow?Frequency=A&amp;Flows=X&amp;CommodityCodes=850760,870380&amp;Partners=842&amp;Reporters=156,458,764,704&amp;period=2018,2019,2020,2021,2022,2023,2024,2025&amp;partner2=0&amp;output=default&amp;AggregateBy=none&amp;BreakdownMode=plus</t>
         </is>
       </c>
     </row>
@@ -3369,7 +3369,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>持续更新</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -3394,7 +3394,7 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org</t>
+          <t>https://comtradeplus.un.org/TradeFlow?Frequency=A&amp;Flows=X&amp;CommodityCodes=8541,8542&amp;Partners=842&amp;Reporters=156,458,764,704&amp;period=2018,2019,2020,2021,2022,2023,2024,2025&amp;partner2=0&amp;output=default&amp;AggregateBy=none&amp;BreakdownMode=plus</t>
         </is>
       </c>
     </row>
@@ -3411,17 +3411,17 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>CASE_004</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>国盛证券（经腾讯新闻转载）</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -3446,7 +3446,7 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>https://news.qq.com/rain/a/20251130A04A7P00</t>
+          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
         </is>
       </c>
     </row>
@@ -3463,17 +3463,17 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>CASE_004</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>国盛证券（经腾讯新闻转载）</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2025-11-30</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
+          <t>https://news.qq.com/rain/a/20251130A04A7P00</t>
         </is>
       </c>
     </row>
@@ -3577,7 +3577,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>持续更新</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org</t>
+          <t>https://comtradeplus.un.org/TradeFlow?Frequency=A&amp;Flows=X&amp;CommodityCodes=850760,870380&amp;Partners=842&amp;Reporters=156,458,764,704&amp;period=2018,2019,2020,2021,2022,2023,2024,2025&amp;partner2=0&amp;output=default&amp;AggregateBy=none&amp;BreakdownMode=plus</t>
         </is>
       </c>
     </row>
@@ -3629,7 +3629,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>持续更新</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org</t>
+          <t>https://comtradeplus.un.org/TradeFlow?Frequency=A&amp;Flows=X&amp;CommodityCodes=8541,8542&amp;Partners=842&amp;Reporters=156,458,764,704&amp;period=2018,2019,2020,2021,2022,2023,2024,2025&amp;partner2=0&amp;output=default&amp;AggregateBy=none&amp;BreakdownMode=plus</t>
         </is>
       </c>
     </row>
@@ -3666,27 +3666,27 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>华友钴业 Huayou Cobalt：Operational Risk</t>
+          <t>华友钴业 Huayou Cobalt：Market Access Risk</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>WB_001</t>
+          <t>MOFCOM_001</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>世界银行（World Bank）</t>
+          <t>商务部、海关总署</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>2023-04-28</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G62" s="2" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>https://documents.worldbank.org/curated/en/099042123145531599/pdf/P17146804a6a570ac0a4f80895e320dda1e.pdf</t>
+          <t>https://www.mofcom.gov.cn/zwgk/zcfb/art/2025/art_c03d1e511b2b486e829d68e8f1422aff.html</t>
         </is>
       </c>
     </row>
@@ -3723,22 +3723,22 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>WB_001</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>世界银行（World Bank）</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2023-04-28</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G63" s="2" t="n">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
+          <t>https://documents.worldbank.org/curated/en/099042123145531599/pdf/P17146804a6a570ac0a4f80895e320dda1e.pdf</t>
         </is>
       </c>
     </row>
@@ -3775,17 +3775,17 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>CASE_008</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>中国基金报</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>2024-07-14</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -3810,7 +3810,7 @@
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
+          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
         </is>
       </c>
     </row>
@@ -3822,27 +3822,27 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>华友钴业 Huayou Cobalt：Supply Chain Risk</t>
+          <t>华友钴业 Huayou Cobalt：Operational Risk</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>TRD_001</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>持续更新</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="G65" s="2" t="n">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org</t>
+          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
         </is>
       </c>
     </row>
@@ -3874,27 +3874,27 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>华友钴业 Huayou Cobalt：Supply Chain Risk</t>
+          <t>华友钴业 Huayou Cobalt：Regulatory Risk</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>WB_001</t>
+          <t>MOFCOM_001</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>世界银行（World Bank）</t>
+          <t>商务部、海关总署</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>2023-04-28</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G66" s="2" t="n">
@@ -3914,7 +3914,7 @@
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>https://documents.worldbank.org/curated/en/099042123145531599/pdf/P17146804a6a570ac0a4f80895e320dda1e.pdf</t>
+          <t>https://www.mofcom.gov.cn/zwgk/zcfb/art/2025/art_c03d1e511b2b486e829d68e8f1422aff.html</t>
         </is>
       </c>
     </row>
@@ -3931,22 +3931,22 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G67" s="2" t="n">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
+          <t>https://comtradeplus.un.org/TradeFlow?Frequency=A&amp;Flows=X&amp;CommodityCodes=850760,870380&amp;Partners=842&amp;Reporters=156,458,764,704&amp;period=2018,2019,2020,2021,2022,2023,2024,2025&amp;partner2=0&amp;output=default&amp;AggregateBy=none&amp;BreakdownMode=plus</t>
         </is>
       </c>
     </row>
@@ -3983,17 +3983,17 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>WB_001</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>世界银行（World Bank）</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>持续更新</t>
+          <t>2023-04-28</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -4018,7 +4018,7 @@
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org</t>
+          <t>https://documents.worldbank.org/curated/en/099042123145531599/pdf/P17146804a6a570ac0a4f80895e320dda1e.pdf</t>
         </is>
       </c>
     </row>
@@ -4035,17 +4035,17 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>CASE_008</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>中国基金报</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>2024-07-14</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
+          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
         </is>
       </c>
     </row>
@@ -4082,27 +4082,27 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>华友钴业 Huayou Cobalt：Trade Risk</t>
+          <t>华友钴业 Huayou Cobalt：Supply Chain Risk</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>TRD_001</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>持续更新</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="G70" s="2" t="n">
@@ -4122,7 +4122,7 @@
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org</t>
+          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
         </is>
       </c>
     </row>
@@ -4139,7 +4139,7 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -4149,7 +4149,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>持续更新</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -4174,7 +4174,7 @@
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org</t>
+          <t>https://comtradeplus.un.org/TradeFlow?Frequency=A&amp;Flows=X&amp;CommodityCodes=850760,870380&amp;Partners=842&amp;Reporters=156,458,764,704&amp;period=2018,2019,2020,2021,2022,2023,2024,2025&amp;partner2=0&amp;output=default&amp;AggregateBy=none&amp;BreakdownMode=plus</t>
         </is>
       </c>
     </row>
@@ -4186,27 +4186,27 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>中伟股份 CNGR Advanced Material：Operational Risk</t>
+          <t>中伟股份 CNGR Advanced Material：Market Access Risk</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>WB_001</t>
+          <t>MOFCOM_001</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>世界银行（World Bank）</t>
+          <t>商务部、海关总署</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>2023-04-28</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G72" s="2" t="n">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>https://documents.worldbank.org/curated/en/099042123145531599/pdf/P17146804a6a570ac0a4f80895e320dda1e.pdf</t>
+          <t>https://www.mofcom.gov.cn/zwgk/zcfb/art/2025/art_c03d1e511b2b486e829d68e8f1422aff.html</t>
         </is>
       </c>
     </row>
@@ -4243,22 +4243,22 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>WB_001</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>世界银行（World Bank）</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2023-04-28</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G73" s="2" t="n">
@@ -4278,7 +4278,7 @@
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
+          <t>https://documents.worldbank.org/curated/en/099042123145531599/pdf/P17146804a6a570ac0a4f80895e320dda1e.pdf</t>
         </is>
       </c>
     </row>
@@ -4295,17 +4295,17 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>CASE_008</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>中国基金报</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>2024-07-14</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -4330,7 +4330,7 @@
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
+          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
         </is>
       </c>
     </row>
@@ -4342,27 +4342,27 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>中伟股份 CNGR Advanced Material：Supply Chain Risk</t>
+          <t>中伟股份 CNGR Advanced Material：Operational Risk</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>TRD_001</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>持续更新</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="G75" s="2" t="n">
@@ -4382,7 +4382,7 @@
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org</t>
+          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
         </is>
       </c>
     </row>
@@ -4394,27 +4394,27 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>中伟股份 CNGR Advanced Material：Supply Chain Risk</t>
+          <t>中伟股份 CNGR Advanced Material：Regulatory Risk</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>WB_001</t>
+          <t>MOFCOM_001</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>世界银行（World Bank）</t>
+          <t>商务部、海关总署</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>2023-04-28</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G76" s="2" t="n">
@@ -4434,7 +4434,7 @@
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>https://documents.worldbank.org/curated/en/099042123145531599/pdf/P17146804a6a570ac0a4f80895e320dda1e.pdf</t>
+          <t>https://www.mofcom.gov.cn/zwgk/zcfb/art/2025/art_c03d1e511b2b486e829d68e8f1422aff.html</t>
         </is>
       </c>
     </row>
@@ -4451,22 +4451,22 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G77" s="2" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
+          <t>https://comtradeplus.un.org/TradeFlow?Frequency=A&amp;Flows=X&amp;CommodityCodes=850760,870380&amp;Partners=842&amp;Reporters=156,458,764,704&amp;period=2018,2019,2020,2021,2022,2023,2024,2025&amp;partner2=0&amp;output=default&amp;AggregateBy=none&amp;BreakdownMode=plus</t>
         </is>
       </c>
     </row>
@@ -4503,17 +4503,17 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>WB_001</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>世界银行（World Bank）</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>持续更新</t>
+          <t>2023-04-28</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org</t>
+          <t>https://documents.worldbank.org/curated/en/099042123145531599/pdf/P17146804a6a570ac0a4f80895e320dda1e.pdf</t>
         </is>
       </c>
     </row>
@@ -4555,17 +4555,17 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>CASE_008</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>中国基金报</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>2024-07-14</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -4590,7 +4590,7 @@
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
+          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
         </is>
       </c>
     </row>
@@ -4602,27 +4602,27 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>中伟股份 CNGR Advanced Material：Trade Risk</t>
+          <t>中伟股份 CNGR Advanced Material：Supply Chain Risk</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>TRD_001</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>持续更新</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="G80" s="2" t="n">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org</t>
+          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
         </is>
       </c>
     </row>
@@ -4659,7 +4659,7 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>持续更新</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -4694,7 +4694,7 @@
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org</t>
+          <t>https://comtradeplus.un.org/TradeFlow?Frequency=A&amp;Flows=X&amp;CommodityCodes=850760,870380&amp;Partners=842&amp;Reporters=156,458,764,704&amp;period=2018,2019,2020,2021,2022,2023,2024,2025&amp;partner2=0&amp;output=default&amp;AggregateBy=none&amp;BreakdownMode=plus</t>
         </is>
       </c>
     </row>
@@ -6489,7 +6489,7 @@
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>持续更新</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr">
@@ -6514,7 +6514,7 @@
       </c>
       <c r="L116" s="2" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org</t>
+          <t>https://comtradeplus.un.org/TradeFlow?Frequency=A&amp;Flows=X&amp;CommodityCodes=850760,870380&amp;Partners=842&amp;Reporters=156,458,764,704&amp;period=2018,2019,2020,2021,2022,2023,2024,2025&amp;partner2=0&amp;output=default&amp;AggregateBy=none&amp;BreakdownMode=plus</t>
         </is>
       </c>
     </row>
@@ -6697,7 +6697,7 @@
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>持续更新</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
@@ -6722,7 +6722,7 @@
       </c>
       <c r="L120" s="2" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org</t>
+          <t>https://comtradeplus.un.org/TradeFlow?Frequency=A&amp;Flows=X&amp;CommodityCodes=850760,870380&amp;Partners=842&amp;Reporters=156,458,764,704&amp;period=2018,2019,2020,2021,2022,2023,2024,2025&amp;partner2=0&amp;output=default&amp;AggregateBy=none&amp;BreakdownMode=plus</t>
         </is>
       </c>
     </row>
@@ -10133,7 +10133,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>https://www.federalregister.gov/documents/2025/11/12/2025-19846/one-year-suspension-of-expansion-of-end-user-controls-for-affiliates-of-certain-listed-entities</t>
+          <t>https://www.federalregister.gov/documents/search?conditions%5Bterm%5D=end-user+controls+affiliates&amp;conditions%5Btype%5D%5B%5D=RULE</t>
         </is>
       </c>
       <c r="K13" s="2" t="n">
@@ -10271,7 +10271,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -10663,7 +10663,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>持续更新（每日）</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -10887,7 +10887,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>持续更新（每日）</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -11335,7 +11335,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>持续更新</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -11365,7 +11365,7 @@
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org</t>
+          <t>https://comtradeplus.un.org/TradeFlow?Frequency=A&amp;Flows=X&amp;CommodityCodes=850760,870380&amp;Partners=842&amp;Reporters=156,458,764,704&amp;period=2018,2019,2020,2021,2022,2023,2024,2025&amp;partner2=0&amp;output=default&amp;AggregateBy=none&amp;BreakdownMode=plus</t>
         </is>
       </c>
       <c r="K35" s="2" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>持续更新</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -11421,7 +11421,7 @@
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org</t>
+          <t>https://comtradeplus.un.org/TradeFlow?Frequency=A&amp;Flows=X&amp;CommodityCodes=854140&amp;Partners=842&amp;Reporters=156,458,764,704&amp;period=2018,2019,2020,2021&amp;partner2=0&amp;output=default&amp;AggregateBy=none&amp;BreakdownMode=plus</t>
         </is>
       </c>
       <c r="K36" s="2" t="n">
@@ -11447,7 +11447,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>持续更新</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -11477,7 +11477,7 @@
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org</t>
+          <t>https://comtradeplus.un.org/TradeFlow?Frequency=A&amp;Flows=X&amp;CommodityCodes=8541,8542&amp;Partners=842&amp;Reporters=156,458,764,704&amp;period=2018,2019,2020,2021,2022,2023,2024,2025&amp;partner2=0&amp;output=default&amp;AggregateBy=none&amp;BreakdownMode=plus</t>
         </is>
       </c>
       <c r="K37" s="2" t="n">

--- a/data/evaluation/evidence_quality_test.xlsx
+++ b/data/evaluation/evidence_quality_test.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Citation Test'!$A$1:$L$171</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Corpus Citation Coverage'!$A$1:$L$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Corpus Citation Coverage'!$A$1:$L$54</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Conclusion Audit'!$A$1:$H$86</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1586,27 +1586,27 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>国轩高科 Gotion High-Tech：Operational Risk</t>
+          <t>国轩高科 Gotion High-Tech：Market Access Risk</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>WB_001</t>
+          <t>MOFCOM_001</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>世界银行（World Bank）</t>
+          <t>商务部、海关总署</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2023-04-28</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G22" s="2" t="n">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>https://documents.worldbank.org/curated/en/099042123145531599/pdf/P17146804a6a570ac0a4f80895e320dda1e.pdf</t>
+          <t>https://www.mofcom.gov.cn/zwgk/zcfb/art/2025/art_c03d1e511b2b486e829d68e8f1422aff.html</t>
         </is>
       </c>
     </row>
@@ -1643,22 +1643,22 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>WB_001</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>世界银行（World Bank）</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2023-04-28</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G23" s="2" t="n">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
+          <t>https://documents.worldbank.org/curated/en/099042123145531599/pdf/P17146804a6a570ac0a4f80895e320dda1e.pdf</t>
         </is>
       </c>
     </row>
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>CASE_008</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>中国基金报</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2024-07-14</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
+          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
         </is>
       </c>
     </row>
@@ -1742,27 +1742,27 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>国轩高科 Gotion High-Tech：Supply Chain Risk</t>
+          <t>国轩高科 Gotion High-Tech：Regulatory Risk</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>TRD_001</t>
+          <t>MOFCOM_001</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>商务部、海关总署</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G25" s="2" t="n">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org/TradeFlow?Frequency=A&amp;Flows=X&amp;CommodityCodes=850760,870380&amp;Partners=842&amp;Reporters=156,458,764,704&amp;period=2018,2019,2020,2021,2022,2023,2024,2025&amp;partner2=0&amp;output=default&amp;AggregateBy=none&amp;BreakdownMode=plus</t>
+          <t>https://www.mofcom.gov.cn/zwgk/zcfb/art/2025/art_c03d1e511b2b486e829d68e8f1422aff.html</t>
         </is>
       </c>
     </row>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org/TradeFlow?Frequency=A&amp;Flows=X&amp;CommodityCodes=8541,8542&amp;Partners=842&amp;Reporters=156,458,764,704&amp;period=2018,2019,2020,2021,2022,2023,2024,2025&amp;partner2=0&amp;output=default&amp;AggregateBy=none&amp;BreakdownMode=plus</t>
+          <t>https://comtradeplus.un.org/TradeFlow?Frequency=A&amp;Flows=X&amp;CommodityCodes=850760,870380&amp;Partners=842&amp;Reporters=156,458,764,704&amp;period=2018,2019,2020,2021,2022,2023,2024,2025&amp;partner2=0&amp;output=default&amp;AggregateBy=none&amp;BreakdownMode=plus</t>
         </is>
       </c>
     </row>
@@ -1851,17 +1851,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>WB_001</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>世界银行（World Bank）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2023-04-28</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>https://documents.worldbank.org/curated/en/099042123145531599/pdf/P17146804a6a570ac0a4f80895e320dda1e.pdf</t>
+          <t>https://comtradeplus.un.org/TradeFlow?Frequency=A&amp;Flows=X&amp;CommodityCodes=8541,8542&amp;Partners=842&amp;Reporters=156,458,764,704&amp;period=2018,2019,2020,2021,2022,2023,2024,2025&amp;partner2=0&amp;output=default&amp;AggregateBy=none&amp;BreakdownMode=plus</t>
         </is>
       </c>
     </row>
@@ -1903,22 +1903,22 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>WB_001</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>世界银行（World Bank）</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2023-04-28</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G28" s="2" t="n">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
+          <t>https://documents.worldbank.org/curated/en/099042123145531599/pdf/P17146804a6a570ac0a4f80895e320dda1e.pdf</t>
         </is>
       </c>
     </row>
@@ -1955,17 +1955,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>CASE_008</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>中国基金报</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2024-07-14</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -1990,7 +1990,7 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
+          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
         </is>
       </c>
     </row>
@@ -2626,27 +2626,27 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>欣旺达 Sunwoda：Operational Risk</t>
+          <t>欣旺达 Sunwoda：Market Access Risk</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>WB_001</t>
+          <t>MOFCOM_001</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>世界银行（World Bank）</t>
+          <t>商务部、海关总署</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>2023-04-28</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G42" s="2" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>https://documents.worldbank.org/curated/en/099042123145531599/pdf/P17146804a6a570ac0a4f80895e320dda1e.pdf</t>
+          <t>https://www.mofcom.gov.cn/zwgk/zcfb/art/2025/art_c03d1e511b2b486e829d68e8f1422aff.html</t>
         </is>
       </c>
     </row>
@@ -2683,22 +2683,22 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>WB_001</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>世界银行（World Bank）</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2023-04-28</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G43" s="2" t="n">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
+          <t>https://documents.worldbank.org/curated/en/099042123145531599/pdf/P17146804a6a570ac0a4f80895e320dda1e.pdf</t>
         </is>
       </c>
     </row>
@@ -2735,17 +2735,17 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>CASE_008</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>中国基金报</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>2024-07-14</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -2770,7 +2770,7 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
+          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
         </is>
       </c>
     </row>
@@ -2782,27 +2782,27 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>欣旺达 Sunwoda：Supply Chain Risk</t>
+          <t>欣旺达 Sunwoda：Regulatory Risk</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>TRD_001</t>
+          <t>MOFCOM_001</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>商务部、海关总署</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G45" s="2" t="n">
@@ -2822,7 +2822,7 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org/TradeFlow?Frequency=A&amp;Flows=X&amp;CommodityCodes=850760,870380&amp;Partners=842&amp;Reporters=156,458,764,704&amp;period=2018,2019,2020,2021,2022,2023,2024,2025&amp;partner2=0&amp;output=default&amp;AggregateBy=none&amp;BreakdownMode=plus</t>
+          <t>https://www.mofcom.gov.cn/zwgk/zcfb/art/2025/art_c03d1e511b2b486e829d68e8f1422aff.html</t>
         </is>
       </c>
     </row>
@@ -2839,7 +2839,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -2874,7 +2874,7 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org/TradeFlow?Frequency=A&amp;Flows=X&amp;CommodityCodes=8541,8542&amp;Partners=842&amp;Reporters=156,458,764,704&amp;period=2018,2019,2020,2021,2022,2023,2024,2025&amp;partner2=0&amp;output=default&amp;AggregateBy=none&amp;BreakdownMode=plus</t>
+          <t>https://comtradeplus.un.org/TradeFlow?Frequency=A&amp;Flows=X&amp;CommodityCodes=850760,870380&amp;Partners=842&amp;Reporters=156,458,764,704&amp;period=2018,2019,2020,2021,2022,2023,2024,2025&amp;partner2=0&amp;output=default&amp;AggregateBy=none&amp;BreakdownMode=plus</t>
         </is>
       </c>
     </row>
@@ -2891,17 +2891,17 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>WB_001</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>世界银行（World Bank）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>2023-04-28</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>https://documents.worldbank.org/curated/en/099042123145531599/pdf/P17146804a6a570ac0a4f80895e320dda1e.pdf</t>
+          <t>https://comtradeplus.un.org/TradeFlow?Frequency=A&amp;Flows=X&amp;CommodityCodes=8541,8542&amp;Partners=842&amp;Reporters=156,458,764,704&amp;period=2018,2019,2020,2021,2022,2023,2024,2025&amp;partner2=0&amp;output=default&amp;AggregateBy=none&amp;BreakdownMode=plus</t>
         </is>
       </c>
     </row>
@@ -2943,22 +2943,22 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>WB_001</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>世界银行（World Bank）</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2023-04-28</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G48" s="2" t="n">
@@ -2978,7 +2978,7 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
+          <t>https://documents.worldbank.org/curated/en/099042123145531599/pdf/P17146804a6a570ac0a4f80895e320dda1e.pdf</t>
         </is>
       </c>
     </row>
@@ -2995,17 +2995,17 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>CASE_008</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>中国基金报</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>2024-07-14</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
+          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
         </is>
       </c>
     </row>
@@ -4186,27 +4186,27 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>中伟股份 CNGR Advanced Material：Market Access Risk</t>
+          <t>中伟股份 CNGR Advanced Material：Operational Risk</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>MOFCOM_001</t>
+          <t>WB_001</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>商务部、海关总署</t>
+          <t>世界银行（World Bank）</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2023-04-28</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G72" s="2" t="n">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>https://www.mofcom.gov.cn/zwgk/zcfb/art/2025/art_c03d1e511b2b486e829d68e8f1422aff.html</t>
+          <t>https://documents.worldbank.org/curated/en/099042123145531599/pdf/P17146804a6a570ac0a4f80895e320dda1e.pdf</t>
         </is>
       </c>
     </row>
@@ -4243,22 +4243,22 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>WB_001</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>世界银行（World Bank）</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>2023-04-28</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="G73" s="2" t="n">
@@ -4278,7 +4278,7 @@
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>https://documents.worldbank.org/curated/en/099042123145531599/pdf/P17146804a6a570ac0a4f80895e320dda1e.pdf</t>
+          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
         </is>
       </c>
     </row>
@@ -4295,17 +4295,17 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -4330,7 +4330,7 @@
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
+          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
         </is>
       </c>
     </row>
@@ -4342,27 +4342,27 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>中伟股份 CNGR Advanced Material：Operational Risk</t>
+          <t>中伟股份 CNGR Advanced Material：Supply Chain Risk</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>CASE_008</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>中国基金报</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>2024-07-14</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G75" s="2" t="n">
@@ -4382,7 +4382,7 @@
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
+          <t>https://comtradeplus.un.org/TradeFlow?Frequency=A&amp;Flows=X&amp;CommodityCodes=850760,870380&amp;Partners=842&amp;Reporters=156,458,764,704&amp;period=2018,2019,2020,2021,2022,2023,2024,2025&amp;partner2=0&amp;output=default&amp;AggregateBy=none&amp;BreakdownMode=plus</t>
         </is>
       </c>
     </row>
@@ -4394,27 +4394,27 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>中伟股份 CNGR Advanced Material：Regulatory Risk</t>
+          <t>中伟股份 CNGR Advanced Material：Supply Chain Risk</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>MOFCOM_001</t>
+          <t>WB_001</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>商务部、海关总署</t>
+          <t>世界银行（World Bank）</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2023-04-28</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G76" s="2" t="n">
@@ -4434,7 +4434,7 @@
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>https://www.mofcom.gov.cn/zwgk/zcfb/art/2025/art_c03d1e511b2b486e829d68e8f1422aff.html</t>
+          <t>https://documents.worldbank.org/curated/en/099042123145531599/pdf/P17146804a6a570ac0a4f80895e320dda1e.pdf</t>
         </is>
       </c>
     </row>
@@ -4451,22 +4451,22 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>TRD_001</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="G77" s="2" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org/TradeFlow?Frequency=A&amp;Flows=X&amp;CommodityCodes=850760,870380&amp;Partners=842&amp;Reporters=156,458,764,704&amp;period=2018,2019,2020,2021,2022,2023,2024,2025&amp;partner2=0&amp;output=default&amp;AggregateBy=none&amp;BreakdownMode=plus</t>
+          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
         </is>
       </c>
     </row>
@@ -4503,17 +4503,17 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>WB_001</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>世界银行（World Bank）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>2023-04-28</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>https://documents.worldbank.org/curated/en/099042123145531599/pdf/P17146804a6a570ac0a4f80895e320dda1e.pdf</t>
+          <t>https://comtradeplus.un.org/TradeFlow?Frequency=A&amp;Flows=X&amp;CommodityCodes=8541,8542&amp;Partners=842&amp;Reporters=156,458,764,704&amp;period=2018,2019,2020,2021,2022,2023,2024,2025&amp;partner2=0&amp;output=default&amp;AggregateBy=none&amp;BreakdownMode=plus</t>
         </is>
       </c>
     </row>
@@ -4555,17 +4555,17 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -4590,7 +4590,7 @@
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
+          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
         </is>
       </c>
     </row>
@@ -4602,27 +4602,27 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>中伟股份 CNGR Advanced Material：Supply Chain Risk</t>
+          <t>中伟股份 CNGR Advanced Material：Trade Risk</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>CASE_008</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>中国基金报</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>2024-07-14</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G80" s="2" t="n">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
+          <t>https://comtradeplus.un.org/TradeFlow?Frequency=A&amp;Flows=X&amp;CommodityCodes=850760,870380&amp;Partners=842&amp;Reporters=156,458,764,704&amp;period=2018,2019,2020,2021,2022,2023,2024,2025&amp;partner2=0&amp;output=default&amp;AggregateBy=none&amp;BreakdownMode=plus</t>
         </is>
       </c>
     </row>
@@ -4659,7 +4659,7 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>TRD_001</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -4694,7 +4694,7 @@
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org/TradeFlow?Frequency=A&amp;Flows=X&amp;CommodityCodes=850760,870380&amp;Partners=842&amp;Reporters=156,458,764,704&amp;period=2018,2019,2020,2021,2022,2023,2024,2025&amp;partner2=0&amp;output=default&amp;AggregateBy=none&amp;BreakdownMode=plus</t>
+          <t>https://comtradeplus.un.org/TradeFlow?Frequency=A&amp;Flows=X&amp;CommodityCodes=8541,8542&amp;Partners=842&amp;Reporters=156,458,764,704&amp;period=2018,2019,2020,2021,2022,2023,2024,2025&amp;partner2=0&amp;output=default&amp;AggregateBy=none&amp;BreakdownMode=plus</t>
         </is>
       </c>
     </row>
@@ -6838,27 +6838,27 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>三星电子 Samsung Electronics：Market Access Risk</t>
+          <t>三星电子 Samsung Electronics：Operational Risk</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>CASE_003</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>2023-08-18</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="G123" s="2" t="n">
@@ -6878,7 +6878,7 @@
       </c>
       <c r="L123" s="2" t="inlineStr">
         <is>
-          <t>https://www.internationaltradeinsights.com/2023/08/commerce-issues-final-determination-on-circumvention-of-solar-cells-and-modules-from-cambodia-malaysia-thailand-and-vietnam/</t>
+          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
         </is>
       </c>
     </row>
@@ -6895,17 +6895,17 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="L124" s="2" t="inlineStr">
         <is>
-          <t>https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/</t>
+          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
         </is>
       </c>
     </row>
@@ -6947,22 +6947,22 @@
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>CASE_008</t>
+          <t>TSLA_001</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>中国基金报</t>
+          <t>特斯拉公司（Tesla, Inc.，SEC EDGAR）</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>2024-07-14</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G125" s="2" t="n">
@@ -6982,7 +6982,7 @@
       </c>
       <c r="L125" s="2" t="inlineStr">
         <is>
-          <t>https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1318605/000162828026003952/tsla-20251231.htm</t>
         </is>
       </c>
     </row>
@@ -6999,22 +6999,22 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>TSLA_001</t>
+          <t>SNE_001</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>特斯拉公司（Tesla, Inc.，SEC EDGAR）</t>
+          <t>SNE Research</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G126" s="2" t="n">
@@ -7034,7 +7034,7 @@
       </c>
       <c r="L126" s="2" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1318605/000162828026003952/tsla-20251231.htm</t>
+          <t>https://www.sneresearch.com/en/insight/release_view/744/page/0</t>
         </is>
       </c>
     </row>
@@ -7202,27 +7202,27 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>三星电子 Samsung Electronics：Trade Risk</t>
+          <t>三星电子 Samsung Electronics：Supply Chain Risk</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>CASE_010</t>
+          <t>SNE_001</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>美国白宫（经律所解读）</t>
+          <t>SNE Research</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G130" s="2" t="n">
@@ -7242,7 +7242,7 @@
       </c>
       <c r="L130" s="2" t="inlineStr">
         <is>
-          <t>https://www.alvarezandmarsal.com/node/97806</t>
+          <t>https://www.sneresearch.com/en/insight/release_view/744/page/0</t>
         </is>
       </c>
     </row>
@@ -7259,17 +7259,17 @@
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>CASE_003</t>
+          <t>CASE_010</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>美国白宫（经律所解读）</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>2023-08-18</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="L131" s="2" t="inlineStr">
         <is>
-          <t>https://www.internationaltradeinsights.com/2023/08/commerce-issues-final-determination-on-circumvention-of-solar-cells-and-modules-from-cambodia-malaysia-thailand-and-vietnam/</t>
+          <t>https://www.alvarezandmarsal.com/node/97806</t>
         </is>
       </c>
     </row>
@@ -9390,7 +9390,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L50"/>
+  <dimension ref="A1:L54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11208,22 +11208,22 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>NIO_001</t>
+          <t>MOFCOM_003</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>NIO Inc. Form 20-F（fiscal year ended December 31, 2025）蔚来2025财年年报</t>
+          <t>对外投资合作国别（地区）指南：越南（2025年版）</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>蔚来（NIO Inc.，SEC EDGAR）</t>
+          <t>商务部对外投资和经济合作司、商务部国际贸易经济合作研究院、中国驻越南大使馆经济商务处</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2025-12</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -11233,27 +11233,27 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>EV_Battery</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>出口管制</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Company Disclosure</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>Regulatory Risk; Market Access Risk</t>
+          <t>Political Risk; Regulatory Risk</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1736541/000110465926041765/nio-20251231x20f.htm</t>
+          <t>https://www.mofcom.gov.cn/dl/gbdqzn/upload/yuenan.pdf</t>
         </is>
       </c>
       <c r="K33" s="2" t="n">
@@ -11264,27 +11264,27 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>SNE_001</t>
+          <t>MOFCOM_004</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>January-August 2026 Global EV Battery Usage Reaches 844.2 GWh, Up 19.7% Year-on-Year（2026年1–8月全球动力电池装车量快报）</t>
+          <t>对外投资合作国别（地区）指南：马来西亚（2025年版）</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>SNE Research</t>
+          <t>商务部对外投资和经济合作司、商务部国际贸易经济合作研究院、中国驻马来西亚大使馆经济商务处</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2025-12</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -11294,22 +11294,22 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Industry Report</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Supply Chain Risk; Operational Risk</t>
+          <t>Political Risk; Regulatory Risk</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>https://www.sneresearch.com/en/insight/release_view/744/page/0</t>
+          <t>https://www.mofcom.gov.cn/dl/gbdqzn/upload/malaixiya.pdf</t>
         </is>
       </c>
       <c r="K34" s="2" t="n">
@@ -11320,27 +11320,27 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>TRD_001</t>
+          <t>MOFCOM_005</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度</t>
+          <t>对外投资合作国别（地区）指南：印度（2025年版）</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>商务部对外投资和经济合作司、商务部国际贸易经济合作研究院、中国驻印度大使馆经济商务处</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2025-12</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -11350,22 +11350,22 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>Trade Data</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>Trade Risk; Supply Chain Risk</t>
+          <t>Political Risk; Regulatory Risk</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org/TradeFlow?Frequency=A&amp;Flows=X&amp;CommodityCodes=850760,870380&amp;Partners=842&amp;Reporters=156,458,764,704&amp;period=2018,2019,2020,2021,2022,2023,2024,2025&amp;partner2=0&amp;output=default&amp;AggregateBy=none&amp;BreakdownMode=plus</t>
+          <t>https://www.mofcom.gov.cn/dl/gbdqzn/upload/yindu.pdf</t>
         </is>
       </c>
       <c r="K35" s="2" t="n">
@@ -11376,52 +11376,52 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>TRD_002</t>
+          <t>MOFCOM_006</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>美国自越南、泰国、马来西亚、柬埔寨进口光伏组件HS 854140，2018–2025年度</t>
+          <t>对外投资合作国别（地区）指南：泰国（2025年版）</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>商务部对外投资和经济合作司、商务部国际贸易经济合作研究院、中国驻泰国大使馆经济商务处</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2025-12</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Energy_Storage</t>
+          <t>EV_Battery</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>Trade Data</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>Trade Risk; Supply Chain Risk</t>
+          <t>Political Risk; Regulatory Risk</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org/TradeFlow?Frequency=A&amp;Flows=X&amp;CommodityCodes=854140&amp;Partners=842&amp;Reporters=156,458,764,704&amp;period=2018,2019,2020,2021&amp;partner2=0&amp;output=default&amp;AggregateBy=none&amp;BreakdownMode=plus</t>
+          <t>https://www.mofcom.gov.cn/dl/gbdqzn/upload/taiguo.pdf</t>
         </is>
       </c>
       <c r="K36" s="2" t="n">
@@ -11432,52 +11432,52 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>NIO_001</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度</t>
+          <t>NIO Inc. Form 20-F（fiscal year ended December 31, 2025）蔚来2025财年年报</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>蔚来（NIO Inc.，SEC EDGAR）</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Electronics_Manufacturing</t>
+          <t>Automotive</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>出口管制</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>Trade Data</t>
+          <t>Company Disclosure</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>Trade Risk; Supply Chain Risk</t>
+          <t>Regulatory Risk; Market Access Risk</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org/TradeFlow?Frequency=A&amp;Flows=X&amp;CommodityCodes=8541,8542&amp;Partners=842&amp;Reporters=156,458,764,704&amp;period=2018,2019,2020,2021,2022,2023,2024,2025&amp;partner2=0&amp;output=default&amp;AggregateBy=none&amp;BreakdownMode=plus</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1736541/000110465926041765/nio-20251231x20f.htm</t>
         </is>
       </c>
       <c r="K37" s="2" t="n">
@@ -11488,32 +11488,32 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>TSLA_001</t>
+          <t>SNE_001</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Tesla, Inc. Form 10-K（fiscal year ended December 31, 2025）特斯拉2025财年年报</t>
+          <t>January-August 2026 Global EV Battery Usage Reaches 844.2 GWh, Up 19.7% Year-on-Year（2026年1–8月全球动力电池装车量快报）</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>特斯拉公司（Tesla, Inc.，SEC EDGAR）</t>
+          <t>SNE Research</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>EV_Battery</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -11523,7 +11523,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>Company Disclosure</t>
+          <t>Industry Report</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -11533,7 +11533,7 @@
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1318605/000162828026003952/tsla-20251231.htm</t>
+          <t>https://www.sneresearch.com/en/insight/release_view/744/page/0</t>
         </is>
       </c>
       <c r="K38" s="2" t="n">
@@ -11544,22 +11544,22 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>World Investment Report 2026: International Investment in a Turbulent Era</t>
+          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>联合国贸易和发展会议（UNCTAD）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -11574,22 +11574,22 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>Industry Report</t>
+          <t>Trade Data</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>Political Risk; Regulatory Risk</t>
+          <t>Trade Risk; Supply Chain Risk</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>https://unctad.org/publication/world-investment-report-2026</t>
+          <t>https://comtradeplus.un.org/TradeFlow?Frequency=A&amp;Flows=X&amp;CommodityCodes=850760,870380&amp;Partners=842&amp;Reporters=156,458,764,704&amp;period=2018,2019,2020,2021,2022,2023,2024,2025&amp;partner2=0&amp;output=default&amp;AggregateBy=none&amp;BreakdownMode=plus</t>
         </is>
       </c>
       <c r="K39" s="2" t="n">
@@ -11600,52 +11600,52 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>USMCA_001</t>
+          <t>TRD_002</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>USMCA Chapter 4: Rules of Origin（美墨加协定第4章原产地规则）</t>
+          <t>美国自越南、泰国、马来西亚、柬埔寨进口光伏组件HS 854140，2018–2025年度</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>美国贸易代表办公室（USTR）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>2020-07-01</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>EV_Battery</t>
+          <t>Energy_Storage</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Trade Data</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>Trade Risk; Market Access Risk</t>
+          <t>Trade Risk; Supply Chain Risk</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>https://ustr.gov/trade-agreements/free-trade-agreements/united-states-mexico-canada-agreement/agreement-between</t>
+          <t>https://comtradeplus.un.org/TradeFlow?Frequency=A&amp;Flows=X&amp;CommodityCodes=854140&amp;Partners=842&amp;Reporters=156,458,764,704&amp;period=2018,2019,2020,2021&amp;partner2=0&amp;output=default&amp;AggregateBy=none&amp;BreakdownMode=plus</t>
         </is>
       </c>
       <c r="K40" s="2" t="n">
@@ -11656,52 +11656,52 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>UST_001</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Notice of Modification: China's Acts, Policies and Practices Related to Technology Transfer, Intellectual Property and Innovation（Section 301 对华关税调整通知）</t>
+          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>美国贸易代表办公室（USTR，Federal Register）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>EV_Battery</t>
+          <t>Electronics_Manufacturing</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>关税</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Trade Data</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>Trade Risk; Market Access Risk</t>
+          <t>Trade Risk; Supply Chain Risk</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>https://www.federalregister.gov/documents/2024/09/18/2024-21217/notice-of-modification-chinas-acts-policies-and-practices-related-to-technology-transfer</t>
+          <t>https://comtradeplus.un.org/TradeFlow?Frequency=A&amp;Flows=X&amp;CommodityCodes=8541,8542&amp;Partners=842&amp;Reporters=156,458,764,704&amp;period=2018,2019,2020,2021,2022,2023,2024,2025&amp;partner2=0&amp;output=default&amp;AggregateBy=none&amp;BreakdownMode=plus</t>
         </is>
       </c>
       <c r="K41" s="2" t="n">
@@ -11712,42 +11712,42 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>WB_001</t>
+          <t>TSLA_001</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Connecting to Compete 2023: Trade Logistics in an Uncertain Global Economy（2023年物流绩效指数报告）</t>
+          <t>Tesla, Inc. Form 10-K（fiscal year ended December 31, 2025）特斯拉2025财年年报</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>世界银行（World Bank）</t>
+          <t>特斯拉公司（Tesla, Inc.，SEC EDGAR）</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>2023-04-28</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>EV_Battery</t>
+          <t>Automotive</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>物流</t>
+          <t>供应链布局</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Industry Report</t>
+          <t>Company Disclosure</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
@@ -11757,7 +11757,7 @@
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>https://documents.worldbank.org/curated/en/099042123145531599/pdf/P17146804a6a570ac0a4f80895e320dda1e.pdf</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1318605/000162828026003952/tsla-20251231.htm</t>
         </is>
       </c>
       <c r="K42" s="2" t="n">
@@ -11768,22 +11768,22 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>UNCTAD_001</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Global Risks Report 2026（全球风险报告2026，第21版）</t>
+          <t>World Investment Report 2026: International Investment in a Turbulent Era</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>世界经济论坛（WEF）</t>
+          <t>联合国贸易和发展会议（UNCTAD）</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -11798,7 +11798,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -11808,12 +11808,12 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>Political Risk; Trade Risk</t>
+          <t>Political Risk; Regulatory Risk</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>https://www.weforum.org/publications/global-risks-report-2026</t>
+          <t>https://unctad.org/publication/world-investment-report-2026</t>
         </is>
       </c>
       <c r="K43" s="2" t="n">
@@ -11824,22 +11824,22 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>WH_001</t>
+          <t>USMCA_001</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Executive Order 14411: Strengthening Customs Enforcement（加强海关执法行政令）</t>
+          <t>USMCA Chapter 4: Rules of Origin（美墨加协定第4章原产地规则）</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>美国白宫</t>
+          <t>美国贸易代表办公室（USTR）</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2020-07-01</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -11869,7 +11869,7 @@
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>https://www.govinfo.gov/content/pkg/FR-2026-06-10/pdf/2026-11595.pdf</t>
+          <t>https://ustr.gov/trade-agreements/free-trade-agreements/united-states-mexico-canada-agreement/agreement-between</t>
         </is>
       </c>
       <c r="K44" s="2" t="n">
@@ -11880,22 +11880,22 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>WH_002</t>
+          <t>UST_001</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告）</t>
+          <t>Notice of Modification: China's Acts, Policies and Practices Related to Technology Transfer, Intellectual Property and Innovation（Section 301 对华关税调整通知）</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>美国白宫贸易与制造业政策办公室</t>
+          <t>美国贸易代表办公室（USTR，Federal Register）</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -11910,7 +11910,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>关税</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -11925,7 +11925,7 @@
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>https://www.whitehouse.gov/wp-content/uploads/2026/08/The-Great-Transshipment-Scam.pdf</t>
+          <t>https://www.federalregister.gov/documents/2024/09/18/2024-21217/notice-of-modification-chinas-acts-policies-and-practices-related-to-technology-transfer</t>
         </is>
       </c>
       <c r="K45" s="2" t="n">
@@ -11936,22 +11936,22 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>WTO_001</t>
+          <t>WB_001</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Global Trade Outlook and Statistics（2026年3月版）</t>
+          <t>Connecting to Compete 2023: Trade Logistics in an Uncertain Global Economy（2023年物流绩效指数报告）</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>世界贸易组织（WTO）</t>
+          <t>世界银行（World Bank）</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2023-04-28</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -11966,7 +11966,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>物流</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -11976,12 +11976,12 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>Trade Risk; Supply Chain Risk</t>
+          <t>Supply Chain Risk; Operational Risk</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>https://www.astrid-online.it/static/upload/wto-/wto-global-trade-outlook-2026.pdf</t>
+          <t>https://documents.worldbank.org/curated/en/099042123145531599/pdf/P17146804a6a570ac0a4f80895e320dda1e.pdf</t>
         </is>
       </c>
       <c r="K46" s="2" t="n">
@@ -11992,22 +11992,22 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>WTO_002</t>
+          <t>WEF_001</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Trade Policy Review: Report by the Secretariat — India（WT/TPR/S/403）印度第七次贸易政策审议秘书处报告</t>
+          <t>Global Risks Report 2026（全球风险报告2026，第21版）</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>世界贸易组织（WTO）</t>
+          <t>世界经济论坛（WEF）</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>2020-11-25</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -12022,22 +12022,22 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Industry Report</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>Trade Risk; Supply Chain Risk</t>
+          <t>Political Risk; Trade Risk</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>https://www.wto.org/english/tratop_e/tpr_e/s403_e.pdf</t>
+          <t>https://www.weforum.org/publications/global-risks-report-2026</t>
         </is>
       </c>
       <c r="K47" s="2" t="n">
@@ -12048,27 +12048,27 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>WTO_003</t>
+          <t>WH_001</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>WTO Tariff Profile: India — Tariffs and Imports Summary（WTO国别关税快照：印度）</t>
+          <t>Executive Order 14411: Strengthening Customs Enforcement（加强海关执法行政令）</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>世界贸易组织（WTO）</t>
+          <t>美国白宫</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -12078,22 +12078,22 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>Trade Data</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>Trade Risk; Supply Chain Risk</t>
+          <t>Trade Risk; Market Access Risk</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>https://www.wto.org/english/res_e/statis_e/daily_update_e/tariff_profiles/IN_E.pdf</t>
+          <t>https://www.govinfo.gov/content/pkg/FR-2026-06-10/pdf/2026-11595.pdf</t>
         </is>
       </c>
       <c r="K48" s="2" t="n">
@@ -12104,27 +12104,27 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>WTO_004</t>
+          <t>WH_002</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Trade Policy Review: Report by the Secretariat — Indonesia（WT/TPR/S/401）印尼第七次贸易政策审议秘书处报告</t>
+          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告）</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>世界贸易组织（WTO）</t>
+          <t>美国白宫贸易与制造业政策办公室</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>2020-11-04</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -12134,7 +12134,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>本地化政策</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Supply Chain Risk; Political Risk</t>
+          <t>Trade Risk; Market Access Risk</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>https://www.wto.org/english/tratop_e/tpr_e/s401_e.pdf</t>
+          <t>https://www.whitehouse.gov/wp-content/uploads/2026/08/The-Great-Transshipment-Scam.pdf</t>
         </is>
       </c>
       <c r="K49" s="2" t="n">
@@ -12160,61 +12160,285 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>WTO_001</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Global Trade Outlook and Statistics（2026年3月版）</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>世界贸易组织（WTO）</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>EV_Battery</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>贸易流</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>Industry Report</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>Trade Risk; Supply Chain Risk</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>https://www.astrid-online.it/static/upload/wto-/wto-global-trade-outlook-2026.pdf</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>WTO_002</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Trade Policy Review: Report by the Secretariat — India（WT/TPR/S/403）印度第七次贸易政策审议秘书处报告</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>世界贸易组织（WTO）</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>2020-11-25</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>EV_Battery</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>贸易流</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>Policy</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>Trade Risk; Supply Chain Risk</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wto.org/english/tratop_e/tpr_e/s403_e.pdf</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>WTO_003</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>WTO Tariff Profile: India — Tariffs and Imports Summary（WTO国别关税快照：印度）</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>世界贸易组织（WTO）</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>EV_Battery</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>贸易流</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>Trade Data</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>Trade Risk; Supply Chain Risk</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wto.org/english/res_e/statis_e/daily_update_e/tariff_profiles/IN_E.pdf</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>WTO_004</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Trade Policy Review: Report by the Secretariat — Indonesia（WT/TPR/S/401）印尼第七次贸易政策审议秘书处报告</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>世界贸易组织（WTO）</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>2020-11-04</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>EV_Battery</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>本地化政策</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>Policy</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk; Supply Chain Risk; Political Risk</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wto.org/english/tratop_e/tpr_e/s401_e.pdf</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
           <t>XPEV_001</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>XPeng Inc. Form 20-F（fiscal year ended December 31, 2025）小鹏汽车2025财年年报</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
         <is>
           <t>小鹏汽车（XPeng Inc.，SEC EDGAR）</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>2026-04-16</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Automotive</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr">
         <is>
           <t>出口管制</t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>Company Disclosure</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr">
+      <c r="I54" s="2" t="inlineStr">
         <is>
           <t>Regulatory Risk; Market Access Risk</t>
         </is>
       </c>
-      <c r="J50" s="2" t="inlineStr">
+      <c r="J54" s="2" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/1810997/000119312526157849/d36361d20f.htm</t>
         </is>
       </c>
-      <c r="K50" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L50" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L54" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L50"/>
+  <autoFilter ref="A1:L54"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -16030,7 +16254,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
